--- a/docs/spells.xlsx
+++ b/docs/spells.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Spells" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Spells'!$A$1:$K$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Spells'!$A$1:$K$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1061,7 +1061,7 @@
       <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Deal 1 damage to the last HP of the target (only if it has 4+ elements).</t>
+          <t>Remove the last (rightmost) Essence of the target (only if it has 4+ Essence).</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1367,7 +1367,7 @@
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Deal 1 damage to the last HP of every enemy (only if it has 4+ elements).</t>
+          <t>Remove the last (rightmost) Essence of every enemy (only if it has 4+ Essence).</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1725,14 +1725,10 @@
       <c r="H24" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Deal 1 Targeted damage to the target (you pick which element).</t>
+          <t>Targeted: remove 1 Essence of your choice from the target.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -1987,7 +1983,7 @@
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Deal 1 damage to the last HP of the target (+1 if it is burning).</t>
+          <t>Remove the last (rightmost) Essence of the target (+1 if it is burning).</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -2297,7 +2293,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Deal 1 damage to the last HP of the target.</t>
+          <t>Remove the last (rightmost) Essence of the target.</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -2348,7 +2344,7 @@
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Deal 1 damage to the first HP of the target.</t>
+          <t>Remove the first (leftmost) Essence of the target.</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2705,7 +2701,7 @@
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Deal 1 damage to the last HP of the target; Weaken the target for 1 turn.</t>
+          <t>Remove the last (rightmost) Essence of the target; Weaken the target for 1 turn.</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -3729,7 +3725,7 @@
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Deal 3 damage to the last HP of the target; Overload 1: 1 fewer element next turn.</t>
+          <t>Remove the last 3 Essence of the target, right to left; Overload 1: 1 fewer element next turn.</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -3882,7 +3878,7 @@
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>Deal 1 damage to the last HP of every enemy; Weaken every enemy for 1 turn.</t>
+          <t>Remove the last (rightmost) Essence of every enemy; Weaken every enemy for 1 turn.</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -4035,7 +4031,7 @@
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Amplify 1: when the chant is Released, every enemy it hits takes 1 more damage to its last HP.</t>
+          <t>Amplify 1: when the chant is Released, every enemy it hits also loses its last 1 Essence, right to left.</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -4086,7 +4082,7 @@
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>Deal 2 damage to the last HP of the target; heal 4.</t>
+          <t>Remove the last 2 Essence of the target, right to left; heal 4.</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -4239,7 +4235,7 @@
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Deal 1 damage to the last HP of every enemy.</t>
+          <t>Remove the last (rightmost) Essence of every enemy.</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -4460,12 +4456,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Thermal Burst</t>
+          <t>Blight Wind</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Fire → Water → Fire</t>
+          <t>Water → Air → Air</t>
         </is>
       </c>
       <c r="C78" s="5">
@@ -4482,41 +4478,41 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F78" s="7" t="n">
+      <c r="F78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="G78" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>Deal 2 damage to the first HP of the target; deal 2 damage to the last HP of the target.</t>
+          <t>Poison 2 on every enemy.</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>Both ends explode.</t>
+          <t>Sickness on the wind, for everyone.</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>FWF</t>
+          <t>WAA</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Blight Wind</t>
+          <t>Mistwalk</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Water → Air → Air</t>
+          <t>Water → Air → Water</t>
         </is>
       </c>
       <c r="C79" s="5">
@@ -4530,39 +4526,39 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Poison 2 on every enemy.</t>
+          <t>You become Ethereal this turn; heal 4.</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Sickness on the wind, for everyone.</t>
+          <t>Step between the drops.</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>WAA</t>
+          <t>WAW</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Mistwalk</t>
+          <t>Tide Thief</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -4581,7 +4577,7 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
@@ -4596,12 +4592,12 @@
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>You become Ethereal this turn; heal 4.</t>
+          <t>Steal 1 element of your choice from the target (they go to your elements).</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>Step between the drops.</t>
+          <t>The current takes what it likes and brings it to you.</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -4868,12 +4864,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Glacier</t>
+          <t>Siren's Call</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Water</t>
+          <t>Water → Water → Fire</t>
         </is>
       </c>
       <c r="C86" s="5">
@@ -4887,14 +4883,14 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>0</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H86" s="5" t="n">
         <v>0</v>
@@ -4902,24 +4898,24 @@
       <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>Freeze the target for 1 turn.</t>
+          <t>Steal up to 2 Fire from the target (they go to your elements).</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Frozen mid-swing.</t>
+          <t>A song so sweet the fire walks into the water.</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>WWW</t>
+          <t>WWF</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Rising Tide</t>
+          <t>Glacier</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -4953,12 +4949,12 @@
       <c r="I87" s="5" t="inlineStr"/>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: gain 4 Shield.</t>
+          <t>Freeze the target for 1 turn.</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>The water rises around you every turn.</t>
+          <t>Frozen mid-swing.</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -4970,12 +4966,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Hurricane</t>
+          <t>Rising Tide</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Air → Air</t>
+          <t>Water → Water → Water</t>
         </is>
       </c>
       <c r="C88" s="5">
@@ -4984,49 +4980,49 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="6" t="n">
-        <v>4</v>
+      <c r="G88" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>Deal 3 damage to the last HP of every enemy.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: gain 4 Shield.</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>The whole row is torn apart.</t>
+          <t>The water rises around you every turn.</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>AAAA</t>
+          <t>WWW</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Storm Crown</t>
+          <t>Hurricane</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Air → Fire</t>
+          <t>Air → Air → Air → Air</t>
         </is>
       </c>
       <c r="C89" s="5">
@@ -5035,49 +5031,49 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="n">
-        <v>1</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G89" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: +2 conjured Air now.</t>
+          <t>Remove the last 3 Essence of every enemy, right to left.</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>A conjured Wind every turn.</t>
+          <t>The whole row is torn apart.</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>AAAF</t>
+          <t>AAAA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Long Chant</t>
+          <t>Storm Crown</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Water → Air</t>
+          <t>Air → Air → Air → Fire</t>
         </is>
       </c>
       <c r="C90" s="5">
@@ -5086,7 +5082,7 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -5094,11 +5090,11 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="8" t="n">
-        <v>1</v>
+      <c r="F90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>3</v>
@@ -5106,29 +5102,29 @@
       <c r="I90" s="5" t="inlineStr"/>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Your chant line gets +2 slots.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: +2 conjured Air now.</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Two more slots in your chant line.</t>
+          <t>A conjured Wind every turn.</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>AAWA</t>
+          <t>AAAF</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Misdirection</t>
+          <t>Long Chant</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Air → Water</t>
+          <t>Air → Air → Water → Air</t>
         </is>
       </c>
       <c r="C91" s="5">
@@ -5142,44 +5138,44 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I91" s="5" t="inlineStr"/>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Redirect the intent of the target: its attacks hit the enemy you choose (it can be itself), and anything aimed at you fizzles; gain Aegis (1 hit).</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Your chant line gets +2 slots.</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Point its anger somewhere else. Anywhere else.</t>
+          <t>Two more slots in your chant line.</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>AWAW</t>
+          <t>AAWA</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Eye of the Storm</t>
+          <t>Misdirection</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Fire → Air</t>
+          <t>Air → Water → Air → Water</t>
         </is>
       </c>
       <c r="C92" s="5">
@@ -5196,11 +5192,11 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F92" s="7" t="n">
-        <v>1</v>
+      <c r="F92" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>2</v>
@@ -5208,29 +5204,29 @@
       <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>Freeze every enemy for 2 turns.</t>
+          <t>Redirect the intent of the target: its attacks hit the enemy you choose (it can be itself), and anything aimed at you fizzles; gain Aegis (1 hit).</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>For one moment, everything stops.</t>
+          <t>Point its anger somewhere else. Anywhere else.</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>AWFA</t>
+          <t>AWAW</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Phoenix Rite</t>
+          <t>Eye of the Storm</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Fire → Air → Fire → Air</t>
+          <t>Air → Water → Fire → Air</t>
         </is>
       </c>
       <c r="C93" s="5">
@@ -5239,7 +5235,7 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -5248,10 +5244,10 @@
         </is>
       </c>
       <c r="F93" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G93" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H93" s="6" t="n">
         <v>2</v>
@@ -5259,29 +5255,29 @@
       <c r="I93" s="5" t="inlineStr"/>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Gain Aegis (1 hit); heal 5.</t>
+          <t>Freeze every enemy for 2 turns.</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Rise from the next blow untouched.</t>
+          <t>For one moment, everything stops.</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>FAFA</t>
+          <t>AWFA</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Pyromancy</t>
+          <t>Phoenix Rite</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Air</t>
+          <t>Fire → Air → Fire → Air</t>
         </is>
       </c>
       <c r="C94" s="5">
@@ -5295,44 +5291,44 @@
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F94" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Your spells that remove elements remove +1.</t>
+          <t>Gain Aegis (1 hit); heal 5.</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Your spells tear out one element more.</t>
+          <t>Rise from the next blow untouched.</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>FFFA</t>
+          <t>FAFA</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Meteor</t>
+          <t>Pyromancy</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Fire</t>
+          <t>Fire → Fire → Fire → Air</t>
         </is>
       </c>
       <c r="C95" s="5">
@@ -5341,7 +5337,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -5350,40 +5346,40 @@
         </is>
       </c>
       <c r="F95" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H95" s="5" t="n">
-        <v>0</v>
+      <c r="H95" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I95" s="5" t="inlineStr"/>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Deal 5 damage to the last HP of the target.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Your spells that remove elements remove +1.</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Very big, very hot.</t>
+          <t>Your spells tear out one element more.</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>FFFF</t>
+          <t>FFFA</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Steam Engine</t>
+          <t>Meteor</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Fire → Water → Fire → Water</t>
+          <t>Fire → Fire → Fire → Fire</t>
         </is>
       </c>
       <c r="C96" s="5">
@@ -5401,10 +5397,10 @@
         </is>
       </c>
       <c r="F96" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G96" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>0</v>
@@ -5412,29 +5408,29 @@
       <c r="I96" s="5" t="inlineStr"/>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>Echo: the chant is Released twice this turn.</t>
+          <t>Remove the last 5 Essence of the target, right to left.</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>The chant strikes again after your spells.</t>
+          <t>Very big, very hot.</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>FWFW</t>
+          <t>FFFF</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Unshackle</t>
+          <t>Thermal Burst</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Water → Air → Fire → Water</t>
+          <t>Fire → Fire → Water → Fire</t>
         </is>
       </c>
       <c r="C97" s="5">
@@ -5448,44 +5444,44 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F97" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G97" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H97" s="6" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I97" s="5" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Break one Lock on your spells.</t>
+          <t>Remove the first 2 Essence of 2 different enemies (you pick both), left to right.</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Break one lock on your spells.</t>
+          <t>Steam bursts two ways at once.</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>WAFW</t>
+          <t>FFWF</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Steam Engine</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Water → Air → Water → Air</t>
+          <t>Fire → Water → Fire → Water</t>
         </is>
       </c>
       <c r="C98" s="5">
@@ -5494,49 +5490,49 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>0</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="G98" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H98" s="6" t="n">
-        <v>2</v>
+      <c r="H98" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I98" s="5" t="inlineStr"/>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>Heal 7; remove all your debuffs (frozen elements, Blind, Confuse, Bleed, Silence); gain 5 Shield.</t>
+          <t>Echo: the chant is Released twice this turn.</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Light over still water.</t>
+          <t>The chant strikes again after your spells.</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>WAWA</t>
+          <t>FWFW</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Open Grimoire</t>
+          <t>Unshackle</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Water → Fire → Water → Air</t>
+          <t>Water → Air → Fire → Water</t>
         </is>
       </c>
       <c r="C99" s="5">
@@ -5545,12 +5541,12 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F99" s="7" t="n">
@@ -5565,29 +5561,29 @@
       <c r="I99" s="5" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Add 2 random spells from your spellbook to your active row for this fight.</t>
+          <t>Break one Lock on your spells.</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Two more pages fall open.</t>
+          <t>Break one lock on your spells.</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>WFWA</t>
+          <t>WAFW</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Stillness</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Water → Water</t>
+          <t>Water → Air → Water → Air</t>
         </is>
       </c>
       <c r="C100" s="5">
@@ -5608,37 +5604,37 @@
         <v>0</v>
       </c>
       <c r="G100" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="H100" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="I100" s="5" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Every enemy permanently deals 25% less damage.</t>
+          <t>Heal 7; remove all your debuffs (frozen elements, Blind, Confuse, Bleed, Silence); gain 5 Shield.</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Every enemy deals 25% less damage, for good.</t>
+          <t>Light over still water.</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>WWWW</t>
+          <t>WAWA</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Tidal Wave</t>
+          <t>Open Grimoire</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Water → Water</t>
+          <t>Water → Fire → Water → Air</t>
         </is>
       </c>
       <c r="C101" s="5">
@@ -5652,44 +5648,44 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>0</v>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G101" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I101" s="5" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>Deal 2 damage to the first HP of every enemy; Weaken every enemy for 3 turns.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Add 2 random spells from your spellbook to your active row for this fight.</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Knock the front off everything.</t>
+          <t>Two more pages fall open.</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>WWWW</t>
+          <t>WFWA</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Convergence</t>
+          <t>Stillness</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Water → Fire → Air</t>
+          <t>Water → Water → Water → Water</t>
         </is>
       </c>
       <c r="C102" s="5">
@@ -5698,49 +5694,49 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="n">
-        <v>2</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Echo: the chant is Released twice this turn; Amplify 1: when the chant is Released, every enemy it hits takes 1 more damage to its last HP.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Every enemy permanently deals 25% less damage.</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>All three elements sing as one.</t>
+          <t>Every enemy deals 25% less damage, for good.</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>AFWFA</t>
+          <t>WWWW</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Triune Chant</t>
+          <t>Tidal Wave</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Fire → Air → Water → Air → Fire</t>
+          <t>Water → Water → Water → Water</t>
         </is>
       </c>
       <c r="C103" s="5">
@@ -5754,44 +5750,44 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="n">
-        <v>2</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G103" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I103" s="5" t="inlineStr"/>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Pick an element in this turn's chant: it becomes 3 in a row.</t>
+          <t>Remove the first 2 Essence of every enemy, left to right; Weaken every enemy for 3 turns.</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Three voices, one word.</t>
+          <t>Knock the front off everything.</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>FAWAF</t>
+          <t>WWWW</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>Avatar of Flame</t>
+          <t>Convergence</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Fire → Air</t>
+          <t>Air → Fire → Water → Fire → Air</t>
         </is>
       </c>
       <c r="C104" s="5">
@@ -5809,40 +5805,40 @@
         </is>
       </c>
       <c r="F104" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G104" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H104" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I104" s="5" t="inlineStr"/>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Every enemy your Release hits gets Burn 1.</t>
+          <t>Echo: the chant is Released twice this turn; Amplify 1: when the chant is Released, every enemy it hits also loses its last 1 Essence, right to left.</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Every enemy your chant touches catches fire.</t>
+          <t>All three elements sing as one.</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>FFFFA</t>
+          <t>AFWFA</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Supernova</t>
+          <t>Triune Chant</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Fire → Fire</t>
+          <t>Fire → Air → Water → Air → Fire</t>
         </is>
       </c>
       <c r="C105" s="5">
@@ -5856,44 +5852,44 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F105" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G105" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="I105" s="5" t="inlineStr"/>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>Deal 3 damage to the last HP of every enemy; Burn 4 on every enemy.</t>
+          <t>Pick an element in this turn's chant: it becomes 3 in a row.</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>A star dies on the battlefield.</t>
+          <t>Three voices, one word.</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>FFFFF</t>
+          <t>FAWAF</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>World Tree's Blessing</t>
+          <t>Avatar of Flame</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Water → Air → Water → Air → Water</t>
+          <t>Fire → Fire → Fire → Fire → Air</t>
         </is>
       </c>
       <c r="C106" s="5">
@@ -5907,44 +5903,44 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="8" t="n">
-        <v>3</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H106" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I106" s="5" t="inlineStr"/>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: heal 7; +3 random elements now.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Every enemy your Release hits gets Burn 1.</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>The Last Tree gives back, every turn.</t>
+          <t>Every enemy your chant touches catches fire.</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>WAWAW</t>
+          <t>FFFFA</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Deluge</t>
+          <t>Supernova</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Water → Water → Water</t>
+          <t>Fire → Fire → Fire → Fire → Fire</t>
         </is>
       </c>
       <c r="C107" s="5">
@@ -5958,14 +5954,14 @@
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="8" t="n">
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="n">
         <v>5</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>0</v>
@@ -5973,22 +5969,175 @@
       <c r="I107" s="5" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr">
         <is>
+          <t>Remove the last 3 Essence of every enemy, right to left; Burn 4 on every enemy.</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>A star dies on the battlefield.</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>FFFFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>World Tree's Blessing</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Water → Air → Water → Air → Water</t>
+        </is>
+      </c>
+      <c r="C108" s="5">
+        <f>LEN(L108)</f>
+        <v/>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" s="5" t="inlineStr"/>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: heal 7; +3 random elements now.</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>The Last Tree gives back, every turn.</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>WAWAW</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Maelstrom Grasp</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Water → Water → Air → Water → Water</t>
+        </is>
+      </c>
+      <c r="C109" s="5">
+        <f>LEN(L109)</f>
+        <v/>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H109" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="5" t="inlineStr"/>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>Steal 2 elements of your choice from the target (they go to your elements); gain 4 Shield.</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>The whirlpool swallows their strength and spits it out at your feet.</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>WWAWW</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>Deluge</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Water → Water → Water → Water → Water</t>
+        </is>
+      </c>
+      <c r="C110" s="5">
+        <f>LEN(L110)</f>
+        <v/>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="5" t="inlineStr"/>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
           <t>Gain 14 Shield; heal 10; Freeze every enemy for 2 turns.</t>
         </is>
       </c>
-      <c r="K107" s="4" t="inlineStr">
+      <c r="K110" s="4" t="inlineStr">
         <is>
           <t>The flood answers.</t>
         </is>
       </c>
-      <c r="L107" s="2" t="inlineStr">
+      <c r="L110" s="2" t="inlineStr">
         <is>
           <t>WWWWW</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K107"/>
+  <autoFilter ref="A1:K110"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/spells.xlsx
+++ b/docs/spells.xlsx
@@ -653,12 +653,12 @@
       <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Take the first 2 elements of the target; you get them next turn as conjured.</t>
+          <t>Remove the 2 leftmost Essence of the target; next turn you gain the removed elements (conjured).</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Pull its first element into your hand.</t>
+          <t>Pull its leftmost element into your hand.</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Burn 1 on the target.</t>
+          <t>Burn 1: set 1 random Essence of the target on fire (removed at the start of your next turn).</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1061,7 +1061,7 @@
       <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Remove the last (rightmost) Essence of the target (only if it has 4+ Essence).</t>
+          <t>Remove the rightmost Essence of the target (only if it has 4+ Essence).</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1316,7 +1316,7 @@
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Turn the last element of the target into Water.</t>
+          <t>Turn the rightmost Essence of the target into Water.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1367,7 +1367,7 @@
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Remove the last (rightmost) Essence of every enemy (only if it has 4+ Essence).</t>
+          <t>Remove the rightmost Essence of every enemy (only if it has 4+ Essence).</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1677,7 +1677,7 @@
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Double the Burn on the target.</t>
+          <t>Set as many more of the target's Essence on fire as are Burning now.</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -1983,7 +1983,7 @@
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Remove the last (rightmost) Essence of the target (+1 if it is burning).</t>
+          <t>Remove the rightmost Essence of the target (+1 if it is burning).</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -2187,7 +2187,7 @@
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Burn 1 on every enemy.</t>
+          <t>Burn 1: set 1 random Essence of every enemy on fire (removed at the start of your next turn).</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Remove the last (rightmost) Essence of the target.</t>
+          <t>Remove the rightmost Essence of the target.</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -2344,7 +2344,7 @@
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Remove the first (leftmost) Essence of the target.</t>
+          <t>Remove the leftmost Essence of the target.</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Burn 2 on the target.</t>
+          <t>Burn 2: set 2 random Essence of the target on fire (removed at the start of your next turn).</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -2497,7 +2497,7 @@
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>Turn the last element of the target into Fire.</t>
+          <t>Turn the rightmost Essence of the target into Fire.</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -2701,7 +2701,7 @@
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Remove the last (rightmost) Essence of the target; Weaken the target for 1 turn.</t>
+          <t>Remove the rightmost Essence of the target; Weaken the target for 1 turn.</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Plant water at its front, then chant it away.</t>
+          <t>Plant water at its leftmost end, then chant it away.</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>+3 random elements next turn; move 2 elements of the target to any position you choose.</t>
+          <t>+2 random elements next turn; Rearrange 1: move one element of your chant to another spot.</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Firestorm</t>
+          <t>Soul Siphon</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -3623,12 +3623,12 @@
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Burn 3 on every enemy.</t>
+          <t>Remove the 3 leftmost Essence of the target; next turn you gain the removed elements (conjured).</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>Burning rain on all of them.</t>
+          <t>Pull its two leftmost elements into your hand.</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Soul Siphon</t>
+          <t>Backdraft</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Air</t>
+          <t>Air → Fire → Fire</t>
         </is>
       </c>
       <c r="C62" s="5">
@@ -3663,40 +3663,40 @@
         </is>
       </c>
       <c r="F62" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>Take the first 3 elements of the target; you get them next turn as conjured.</t>
+          <t>Remove the 3 rightmost Essence of the target; Overload 1: 1 fewer element next turn.</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Pull its first two elements into your hand.</t>
+          <t>Big blast, slow recovery.</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>AFA</t>
+          <t>AFF</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Backdraft</t>
+          <t>Resonance</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Fire</t>
+          <t>Air → Fire → Water</t>
         </is>
       </c>
       <c r="C63" s="5">
@@ -3710,14 +3710,14 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F63" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>1</v>
@@ -3725,29 +3725,29 @@
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Remove the last 3 Essence of the target, right to left; Overload 1: 1 fewer element next turn.</t>
+          <t>Pick an element in this turn's chant: it becomes 2 in a row.</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>Big blast, slow recovery.</t>
+          <t>One note, sung twice.</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>AFF</t>
+          <t>AFW</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Resonance</t>
+          <t>Echo Chamber</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Water</t>
+          <t>Air → Water → Air</t>
         </is>
       </c>
       <c r="C64" s="5">
@@ -3764,36 +3764,36 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F64" s="7" t="n">
-        <v>1</v>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G64" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>Pick an element in this turn's chant: it becomes 2 in a row.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): The first spell you trigger each turn fires twice.</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>One note, sung twice.</t>
+          <t>The first spell each turn rings twice.</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>AFW</t>
+          <t>AWA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Echo Chamber</t>
+          <t>Whirlpool</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
@@ -3827,12 +3827,12 @@
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): The first spell you trigger each turn fires twice.</t>
+          <t>Remove the rightmost Essence of every enemy; Weaken every enemy for 1 turn.</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>The first spell each turn rings twice.</t>
+          <t>Spins them off balance.</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Whirlpool</t>
+          <t>Storm Front</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Air</t>
+          <t>Air → Water → Fire</t>
         </is>
       </c>
       <c r="C66" s="5">
@@ -3863,44 +3863,44 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G66" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>Remove the last (rightmost) Essence of every enemy; Weaken every enemy for 1 turn.</t>
+          <t>Gain 5 Shield; Thorns 2 this turn.</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>Spins them off balance.</t>
+          <t>Touch it and get burned.</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>AWA</t>
+          <t>AWF</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Storm Front</t>
+          <t>Frailty</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Fire</t>
+          <t>Air → Water → Water</t>
         </is>
       </c>
       <c r="C67" s="5">
@@ -3914,14 +3914,14 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="n">
-        <v>1</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G67" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" s="6" t="n">
         <v>1</v>
@@ -3929,29 +3929,29 @@
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Gain 5 Shield; Thorns 2 this turn.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): The target is permanently Exposed.</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>Touch it and get burned.</t>
+          <t>It never recovers its guard.</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>AWF</t>
+          <t>AWW</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Frailty</t>
+          <t>Inferno</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Water</t>
+          <t>Fire → Any → Fire</t>
         </is>
       </c>
       <c r="C68" s="5">
@@ -3968,29 +3968,29 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="8" t="n">
+      <c r="F68" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H68" s="6" t="n">
-        <v>1</v>
+      <c r="G68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): The target is permanently Exposed.</t>
+          <t>Remove the rightmost Essence of every enemy.</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>It never recovers its guard.</t>
+          <t>Everything burns a little.</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>AWW</t>
+          <t>F?F</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Amplify 1: when the chant is Released, every enemy it hits also loses its last 1 Essence, right to left.</t>
+          <t>Amplify 1: when the chant is Released, every enemy it hits also loses its 1 rightmost Essence.</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -4048,7 +4048,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Leech</t>
+          <t>Absorb</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -4082,12 +4082,12 @@
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>Remove the last 2 Essence of the target, right to left; heal 4.</t>
+          <t>Remove the 2 rightmost Essence of the target; if this defeats it, heal 5 HP.</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>Take a piece of it, feel better.</t>
+          <t>Take the last of it, and feel much better.</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -4133,7 +4133,7 @@
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>After casting, 2 of the chant's elements return to your stock.</t>
+          <t>After the Release, the 2 rightmost elements of your chant go back to your elements.</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -4201,12 +4201,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Inferno</t>
+          <t>Ember Crown</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire</t>
+          <t>Fire → Fire → Water</t>
         </is>
       </c>
       <c r="C73" s="5">
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="F73" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H73" s="5" t="n">
         <v>0</v>
@@ -4235,24 +4235,24 @@
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Remove the last (rightmost) Essence of every enemy.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: Burn 2: set 2 random Essence of a random enemy on fire (removed at the start of your next turn).</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>Everything burns a little.</t>
+          <t>A crown that sets something alight each turn.</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>FFF</t>
+          <t>FFW</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Ember Crown</t>
+          <t>Searing Mist</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -4286,12 +4286,12 @@
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: Burn 2 on a random enemy.</t>
+          <t>Remove up to 3 Fire from the target.</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>A crown that sets something alight each turn.</t>
+          <t>Two of its fires go out.</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Searing Mist</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Water</t>
+          <t>Fire → Water → Air</t>
         </is>
       </c>
       <c r="C75" s="5">
@@ -4322,39 +4322,39 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F75" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="5" t="n">
-        <v>0</v>
+      <c r="H75" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Fire from the target.</t>
+          <t>Turn every Water of the target into Fire.</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Two of its fires go out.</t>
+          <t>All its water becomes fire.</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>FFW</t>
+          <t>FWA</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Attunement</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -4388,12 +4388,12 @@
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>Turn every Water of the target into Fire.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Choose an element: one of your draws each turn is always that element.</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>All its water becomes fire.</t>
+          <t>Choose an element; one draw each turn is always it.</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Attunement</t>
+          <t>Blight Wind</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Fire → Water → Air</t>
+          <t>Water → Air → Air</t>
         </is>
       </c>
       <c r="C77" s="5">
@@ -4424,44 +4424,44 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="n">
-        <v>1</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G77" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Choose an element: one of your draws each turn is always that element.</t>
+          <t>Poison 2 on every enemy.</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>Choose an element; one draw each turn is always it.</t>
+          <t>Sickness on the wind, for everyone.</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>FWA</t>
+          <t>WAA</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Blight Wind</t>
+          <t>Mistwalk</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Water → Air → Air</t>
+          <t>Water → Air → Water</t>
         </is>
       </c>
       <c r="C78" s="5">
@@ -4475,39 +4475,39 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>Poison 2 on every enemy.</t>
+          <t>You become Ethereal this turn; heal 4.</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>Sickness on the wind, for everyone.</t>
+          <t>Step between the drops.</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>WAA</t>
+          <t>WAW</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Mistwalk</t>
+          <t>Tide Thief</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
@@ -4541,12 +4541,12 @@
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>You become Ethereal this turn; heal 4.</t>
+          <t>Steal 1 element of your choice from the target (they go to your elements).</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Step between the drops.</t>
+          <t>The current takes what it likes and brings it to you.</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Tide Thief</t>
+          <t>Geyser</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Water → Air → Water</t>
+          <t>Water → Fire → Air</t>
         </is>
       </c>
       <c r="C80" s="5">
@@ -4580,11 +4580,11 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F80" s="5" t="n">
-        <v>0</v>
+      <c r="F80" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" s="6" t="n">
         <v>1</v>
@@ -4592,29 +4592,29 @@
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>Steal 1 element of your choice from the target (they go to your elements).</t>
+          <t>Expose every enemy for 1 turn.</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>The current takes what it likes and brings it to you.</t>
+          <t>Blown wide open.</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>WAW</t>
+          <t>WFA</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Geyser</t>
+          <t>Reforge</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Water → Fire → Air</t>
+          <t>Water → Fire → Fire</t>
         </is>
       </c>
       <c r="C81" s="5">
@@ -4628,44 +4628,44 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F81" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H81" s="6" t="n">
-        <v>1</v>
+      <c r="H81" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Expose every enemy for 1 turn.</t>
+          <t>Turn the 2 leftmost Essence of the target into Fire.</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>Blown wide open.</t>
+          <t>Its two leftmost elements become Fire.</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>WFA</t>
+          <t>WFF</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Reforge</t>
+          <t>Steam Cloud</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Water → Fire → Fire</t>
+          <t>Water → Fire → Water</t>
         </is>
       </c>
       <c r="C82" s="5">
@@ -4679,14 +4679,14 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F82" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="G82" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="H82" s="5" t="n">
         <v>0</v>
@@ -4694,29 +4694,29 @@
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>Turn the first two elements of the target into Fire.</t>
+          <t>Weaken every enemy for 1 turn; gain 4 Shield.</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>Its first two elements become Fire.</t>
+          <t>Nobody can see to aim.</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>WFF</t>
+          <t>WFW</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Steam Cloud</t>
+          <t>Purify</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Water → Fire → Water</t>
+          <t>Water → Water → Air</t>
         </is>
       </c>
       <c r="C83" s="5">
@@ -4733,41 +4733,41 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F83" s="7" t="n">
-        <v>1</v>
+      <c r="F83" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G83" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H83" s="5" t="n">
-        <v>0</v>
+      <c r="H83" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Weaken every enemy for 1 turn; gain 4 Shield.</t>
+          <t>Remove all your debuffs (frozen elements, Blind, Confuse, Bleed, Silence).</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Nobody can see to aim.</t>
+          <t>Every curse washed away.</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>WFW</t>
+          <t>WWA</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Purify</t>
+          <t>Boiling Tide</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Air</t>
+          <t>Water → Water → Fire</t>
         </is>
       </c>
       <c r="C84" s="5">
@@ -4781,39 +4781,39 @@
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>0</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G84" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H84" s="6" t="n">
-        <v>1</v>
+      <c r="H84" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>Remove all your debuffs (frozen elements, Blind, Confuse, Bleed, Silence).</t>
+          <t>Remove up to 3 Water from the target.</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Every curse washed away.</t>
+          <t>Two of its waters boil away.</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>WWA</t>
+          <t>WWF</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Boiling Tide</t>
+          <t>Siren's Call</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -4847,12 +4847,12 @@
       <c r="I85" s="5" t="inlineStr"/>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Water from the target.</t>
+          <t>Steal up to 2 Fire from the target (they go to your elements).</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Two of its waters boil away.</t>
+          <t>A song so sweet the fire walks into the water.</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Siren's Call</t>
+          <t>Glacier</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Fire</t>
+          <t>Water → Water → Water</t>
         </is>
       </c>
       <c r="C86" s="5">
@@ -4883,14 +4883,14 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="n">
-        <v>1</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H86" s="5" t="n">
         <v>0</v>
@@ -4898,24 +4898,24 @@
       <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>Steal up to 2 Fire from the target (they go to your elements).</t>
+          <t>Freeze the target for 1 turn.</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>A song so sweet the fire walks into the water.</t>
+          <t>Frozen mid-swing.</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>WWF</t>
+          <t>WWW</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Glacier</t>
+          <t>Rising Tide</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -4949,12 +4949,12 @@
       <c r="I87" s="5" t="inlineStr"/>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Freeze the target for 1 turn.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: gain 4 Shield.</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Frozen mid-swing.</t>
+          <t>The water rises around you every turn.</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Rising Tide</t>
+          <t>Hurricane</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Water</t>
+          <t>Air → Air → Air → Air</t>
         </is>
       </c>
       <c r="C88" s="5">
@@ -4980,49 +4980,49 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H88" s="5" t="n">
-        <v>0</v>
+      <c r="G88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: gain 4 Shield.</t>
+          <t>Remove the 3 rightmost Essence of every enemy.</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>The water rises around you every turn.</t>
+          <t>The whole row is torn apart.</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>WWW</t>
+          <t>AAAA</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Hurricane</t>
+          <t>Storm Crown</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Air → Air</t>
+          <t>Air → Air → Air → Fire</t>
         </is>
       </c>
       <c r="C89" s="5">
@@ -5031,49 +5031,49 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>0</v>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G89" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Remove the last 3 Essence of every enemy, right to left.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: +2 conjured Air now.</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>The whole row is torn apart.</t>
+          <t>A conjured Wind every turn.</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>AAAA</t>
+          <t>AAAF</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Storm Crown</t>
+          <t>Long Chant</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Air → Fire</t>
+          <t>Air → Air → Water → Air</t>
         </is>
       </c>
       <c r="C90" s="5">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -5090,11 +5090,11 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F90" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>0</v>
+      <c r="F90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>3</v>
@@ -5102,29 +5102,29 @@
       <c r="I90" s="5" t="inlineStr"/>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: +2 conjured Air now.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Your chant line gets +2 slots.</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>A conjured Wind every turn.</t>
+          <t>Two more slots in your chant line.</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>AAAF</t>
+          <t>AAWA</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Long Chant</t>
+          <t>Misdirection</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Water → Air</t>
+          <t>Air → Water → Air → Water</t>
         </is>
       </c>
       <c r="C91" s="5">
@@ -5138,44 +5138,44 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I91" s="5" t="inlineStr"/>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Your chant line gets +2 slots.</t>
+          <t>Redirect the intent of the target: its attacks hit the enemy you choose (it can be itself), and anything aimed at you fizzles; gain Aegis (1 hit).</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Two more slots in your chant line.</t>
+          <t>Point its anger somewhere else. Anywhere else.</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>AAWA</t>
+          <t>AWAW</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Misdirection</t>
+          <t>Eye of the Storm</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Air → Water</t>
+          <t>Air → Water → Fire → Air</t>
         </is>
       </c>
       <c r="C92" s="5">
@@ -5192,11 +5192,11 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>0</v>
+      <c r="F92" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>2</v>
@@ -5204,29 +5204,29 @@
       <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>Redirect the intent of the target: its attacks hit the enemy you choose (it can be itself), and anything aimed at you fizzles; gain Aegis (1 hit).</t>
+          <t>Freeze every enemy for 2 turns.</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Point its anger somewhere else. Anywhere else.</t>
+          <t>For one moment, everything stops.</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>AWAW</t>
+          <t>AWFA</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Eye of the Storm</t>
+          <t>Phoenix Rite</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Fire → Air</t>
+          <t>Fire → Air → Fire → Air</t>
         </is>
       </c>
       <c r="C93" s="5">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="F93" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H93" s="6" t="n">
         <v>2</v>
@@ -5255,29 +5255,29 @@
       <c r="I93" s="5" t="inlineStr"/>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Freeze every enemy for 2 turns.</t>
+          <t>Gain Aegis (1 hit); heal 5.</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>For one moment, everything stops.</t>
+          <t>Rise from the next blow untouched.</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>AWFA</t>
+          <t>FAFA</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Phoenix Rite</t>
+          <t>Pyromancy</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Fire → Air → Fire → Air</t>
+          <t>Fire → Fire → Fire → Air</t>
         </is>
       </c>
       <c r="C94" s="5">
@@ -5291,44 +5291,44 @@
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F94" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>Gain Aegis (1 hit); heal 5.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Your spells that remove elements remove +1.</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Rise from the next blow untouched.</t>
+          <t>Your spells tear out one element more.</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>FAFA</t>
+          <t>FFFA</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Pyromancy</t>
+          <t>Meteor</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Air</t>
+          <t>Fire → Fire → Fire → Fire</t>
         </is>
       </c>
       <c r="C95" s="5">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -5346,40 +5346,40 @@
         </is>
       </c>
       <c r="F95" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H95" s="6" t="n">
-        <v>1</v>
+      <c r="H95" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I95" s="5" t="inlineStr"/>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Your spells that remove elements remove +1.</t>
+          <t>Remove the 5 rightmost Essence of the target.</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Your spells tear out one element more.</t>
+          <t>Very big, very hot.</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>FFFA</t>
+          <t>FFFF</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Meteor</t>
+          <t>Thermal Burst</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Fire</t>
+          <t>Fire → Fire → Water → Fire</t>
         </is>
       </c>
       <c r="C96" s="5">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="F96" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G96" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>0</v>
@@ -5408,29 +5408,29 @@
       <c r="I96" s="5" t="inlineStr"/>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>Remove the last 5 Essence of the target, right to left.</t>
+          <t>Remove the 2 leftmost Essence of 2 different enemies (you pick both).</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Very big, very hot.</t>
+          <t>Steam bursts two ways at once.</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>FFFF</t>
+          <t>FFWF</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Thermal Burst</t>
+          <t>Steam Engine</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Water → Fire</t>
+          <t>Fire → Water → Fire → Water</t>
         </is>
       </c>
       <c r="C97" s="5">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="F97" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G97" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" s="5" t="n">
         <v>0</v>
@@ -5459,29 +5459,29 @@
       <c r="I97" s="5" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Remove the first 2 Essence of 2 different enemies (you pick both), left to right.</t>
+          <t>Echo: the chant is Released twice this turn.</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Steam bursts two ways at once.</t>
+          <t>The chant strikes again after your spells.</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>FFWF</t>
+          <t>FWFW</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Steam Engine</t>
+          <t>Unshackle</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Fire → Water → Fire → Water</t>
+          <t>Water → Air → Fire → Water</t>
         </is>
       </c>
       <c r="C98" s="5">
@@ -5490,49 +5490,49 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F98" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G98" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H98" s="5" t="n">
-        <v>0</v>
+      <c r="H98" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I98" s="5" t="inlineStr"/>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>Echo: the chant is Released twice this turn.</t>
+          <t>Break one Lock on your spells.</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>The chant strikes again after your spells.</t>
+          <t>Break one lock on your spells.</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>FWFW</t>
+          <t>WAFW</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Unshackle</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Water → Air → Fire → Water</t>
+          <t>Water → Air → Water → Air</t>
         </is>
       </c>
       <c r="C99" s="5">
@@ -5549,41 +5549,41 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F99" s="7" t="n">
-        <v>1</v>
+      <c r="F99" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G99" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" s="5" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Break one Lock on your spells.</t>
+          <t>Heal 7; remove all your debuffs (frozen elements, Blind, Confuse, Bleed, Silence); gain 5 Shield.</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Break one lock on your spells.</t>
+          <t>Light over still water.</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>WAFW</t>
+          <t>WAWA</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Open Grimoire</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Water → Air → Water → Air</t>
+          <t>Water → Fire → Water → Air</t>
         </is>
       </c>
       <c r="C100" s="5">
@@ -5592,49 +5592,49 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>0</v>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H100" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I100" s="5" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>Heal 7; remove all your debuffs (frozen elements, Blind, Confuse, Bleed, Silence); gain 5 Shield.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Add 2 random spells from your spellbook to your active row for this fight.</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Light over still water.</t>
+          <t>Two more pages fall open.</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>WAWA</t>
+          <t>WFWA</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Open Grimoire</t>
+          <t>Stillness</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Water → Fire → Water → Air</t>
+          <t>Water → Water → Water → Water</t>
         </is>
       </c>
       <c r="C101" s="5">
@@ -5643,44 +5643,44 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F101" s="7" t="n">
-        <v>1</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G101" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H101" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I101" s="5" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Add 2 random spells from your spellbook to your active row for this fight.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Every enemy permanently deals 25% less damage.</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Two more pages fall open.</t>
+          <t>Every enemy deals 25% less damage, for good.</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>WFWA</t>
+          <t>WWWW</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Stillness</t>
+          <t>Tidal Wave</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
@@ -5714,12 +5714,12 @@
       <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Every enemy permanently deals 25% less damage.</t>
+          <t>Remove the 2 leftmost Essence of every enemy; Weaken every enemy for 3 turns.</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Every enemy deals 25% less damage, for good.</t>
+          <t>Knock the leftmost off everything.</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -5731,12 +5731,12 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Tidal Wave</t>
+          <t>Firestorm</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Water → Water</t>
+          <t>Air → Fire → Any → Fire → Air</t>
         </is>
       </c>
       <c r="C103" s="5">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -5753,29 +5753,29 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F103" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>0</v>
+      <c r="F103" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="I103" s="5" t="inlineStr"/>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Remove the first 2 Essence of every enemy, left to right; Weaken every enemy for 3 turns.</t>
+          <t>Burn 3: set 3 random Essence of every enemy on fire (removed at the start of your next turn).</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Knock the front off everything.</t>
+          <t>Burning rain on all of them.</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>WWWW</t>
+          <t>AF?FA</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       <c r="I104" s="5" t="inlineStr"/>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>Echo: the chant is Released twice this turn; Amplify 1: when the chant is Released, every enemy it hits also loses its last 1 Essence, right to left.</t>
+          <t>Echo: the chant is Released twice this turn; Amplify 1: when the chant is Released, every enemy it hits also loses its 1 rightmost Essence.</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
@@ -5969,7 +5969,7 @@
       <c r="I107" s="5" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Remove the last 3 Essence of every enemy, right to left; Burn 4 on every enemy.</t>
+          <t>Remove the 3 rightmost Essence of every enemy; Burn 4: set 4 random Essence of every enemy on fire (removed at the start of your next turn).</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">

--- a/docs/spells.xlsx
+++ b/docs/spells.xlsx
@@ -806,7 +806,7 @@
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Weaken the target for 1 turn.</t>
+          <t>Weaken 1 on the target.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -857,7 +857,7 @@
       <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Expose the target for 1 turn.</t>
+          <t>Expose 1 on the target.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -959,7 +959,7 @@
       <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Burn 1: set 1 random Essence of the target on fire (removed at the start of your next turn).</t>
+          <t>Burn 1 on the target.</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1677,7 +1677,7 @@
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Set as many more of the target's Essence on fire as are Burning now.</t>
+          <t>Double the Burn on the target.</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -2187,7 +2187,7 @@
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Burn 1: set 1 random Essence of every enemy on fire (removed at the start of your next turn).</t>
+          <t>Burn 1 on every enemy.</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Burn 2: set 2 random Essence of the target on fire (removed at the start of your next turn).</t>
+          <t>Burn 2 on the target.</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -2701,7 +2701,7 @@
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of the target; Weaken the target for 1 turn.</t>
+          <t>Remove the rightmost Essence of the target; Weaken 1 on the target.</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -2803,7 +2803,7 @@
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Move 1 element of the target to any position you choose; Weaken the target for 1 turn.</t>
+          <t>Move 1 element of the target to any position you choose; Weaken 1 on the target.</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -3109,7 +3109,7 @@
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>Gain 2 Shield; Weaken the target for 1 turn.</t>
+          <t>Gain 2 Shield; Weaken 1 on the target.</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -3160,7 +3160,7 @@
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>Weaken every enemy for 1 turn.</t>
+          <t>Weaken 1 on every enemy.</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -3211,7 +3211,7 @@
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Expose the target for 2 turns.</t>
+          <t>Expose 2 on the target.</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -3827,7 +3827,7 @@
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of every enemy; Weaken every enemy for 1 turn.</t>
+          <t>Remove the rightmost Essence of every enemy; Weaken 1 on every enemy.</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -4235,7 +4235,7 @@
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: Burn 2: set 2 random Essence of a random enemy on fire (removed at the start of your next turn).</t>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: Burn 2 on a random enemy.</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -4592,7 +4592,7 @@
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>Expose every enemy for 1 turn.</t>
+          <t>Expose 1 on every enemy.</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -4694,7 +4694,7 @@
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>Weaken every enemy for 1 turn; gain 4 Shield.</t>
+          <t>Weaken 1 on every enemy; gain 4 Shield.</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -4898,7 +4898,7 @@
       <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>Freeze the target for 1 turn.</t>
+          <t>Freeze 1 on the target.</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
@@ -5204,7 +5204,7 @@
       <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>Freeze every enemy for 2 turns.</t>
+          <t>Freeze 2 on every enemy.</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -5714,7 +5714,7 @@
       <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of every enemy; Weaken every enemy for 3 turns.</t>
+          <t>Remove the 2 leftmost Essence of every enemy; Weaken 3 on every enemy.</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
@@ -5765,7 +5765,7 @@
       <c r="I103" s="5" t="inlineStr"/>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Burn 3: set 3 random Essence of every enemy on fire (removed at the start of your next turn).</t>
+          <t>Burn 3 on every enemy.</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -5969,7 +5969,7 @@
       <c r="I107" s="5" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of every enemy; Burn 4: set 4 random Essence of every enemy on fire (removed at the start of your next turn).</t>
+          <t>Remove the 3 rightmost Essence of every enemy; Burn 4 on every enemy.</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -6122,7 +6122,7 @@
       <c r="I110" s="5" t="inlineStr"/>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>Gain 14 Shield; heal 10; Freeze every enemy for 2 turns.</t>
+          <t>Gain 14 Shield; heal 10; Freeze 2 on every enemy.</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">

--- a/docs/spells.xlsx
+++ b/docs/spells.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Spells" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Spells'!$A$1:$K$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Spells'!$A$1:$K$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -976,7 +976,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Kindle</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1010,12 +1010,12 @@
       <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Your Burn applies +1 stack.</t>
+          <t>Remove the rightmost Essence of the target (only if it has 4+ Essence).</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Every fire you light burns a little longer.</t>
+          <t>Only big things catch.</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>Bandage</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C11" s="5">
@@ -1046,14 +1046,14 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0</v>
@@ -1061,24 +1061,24 @@
       <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of the target (only if it has 4+ Essence).</t>
+          <t>Cure Bleed.</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Only big things catch.</t>
+          <t>Wash it, wrap it, keep going.</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Bandage</t>
+          <t>Chill</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
@@ -1112,12 +1112,12 @@
       <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Cure Bleed.</t>
+          <t>Remove all Armour from the target.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Wash it, wrap it, keep going.</t>
+          <t>Cold makes armour brittle.</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Chill</t>
+          <t>Droplet</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
@@ -1163,12 +1163,12 @@
       <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Remove all Armour from the target.</t>
+          <t>Gain 2 Shield.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Cold makes armour brittle.</t>
+          <t>Every drop helps.</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Droplet</t>
+          <t>Mist</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1214,12 +1214,12 @@
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Gain 2 Shield.</t>
+          <t>Heal 1.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Every drop helps.</t>
+          <t>Cool on the skin.</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1231,7 +1231,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Mist</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
@@ -1265,12 +1265,12 @@
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Heal 1.</t>
+          <t>Turn the rightmost Essence of the target into Water.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Cool on the skin.</t>
+          <t>The end of it turns to water.</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1282,12 +1282,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Air → Air</t>
         </is>
       </c>
       <c r="C16" s="5">
@@ -1301,39 +1301,39 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>0</v>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Turn the rightmost Essence of the target into Water.</t>
+          <t>Remove the rightmost Essence of all enemies (only if it has 4+ Essence).</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>The end of it turns to water.</t>
+          <t>Shaves the big ones down to size.</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>AA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Gale Barrier</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
@@ -1367,12 +1367,12 @@
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of every enemy (only if it has 4+ Essence).</t>
+          <t>Gain 3 Shield; Thorns 1 this turn.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Shaves the big ones down to size.</t>
+          <t>A wall of wind that bites back.</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Gale Barrier</t>
+          <t>Miasma</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
@@ -1418,12 +1418,12 @@
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Gain 3 Shield; Thorns 1 this turn.</t>
+          <t>Poison 2 on the target.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>A wall of wind that bites back.</t>
+          <t>A choking cloud settles on it.</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Miasma</t>
+          <t>Steady Mind</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
@@ -1469,12 +1469,12 @@
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Poison 2 on the target.</t>
+          <t>Cure Confuse; +1 Air next turn.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>A choking cloud settles on it.</t>
+          <t>Breathe in, breathe out.</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Steady Mind</t>
+          <t>Tailwind</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
@@ -1517,15 +1517,19 @@
       <c r="H20" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Cure Confuse; +1 Air next turn.</t>
+          <t>+1 random element next turn.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Breathe in, breathe out.</t>
+          <t>The wind brings more.</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1537,12 +1541,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Tailwind</t>
+          <t>Alchemist's Breath</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Air → Air</t>
+          <t>Air → Fire</t>
         </is>
       </c>
       <c r="C21" s="5">
@@ -1559,40 +1563,36 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F21" s="5" t="n">
-        <v>0</v>
+      <c r="F21" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>+1 random element next turn.</t>
+          <t>Turn 2 of your stored elements into Fire.</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>The wind brings more.</t>
+          <t>Two of your stored elements become Fire.</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AF</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Alchemist's Breath</t>
+          <t>Fan the Flames</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F22" s="7" t="n">
@@ -1626,12 +1626,12 @@
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Turn 2 of your stored elements into Fire.</t>
+          <t>Double the Burn on the target.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Two of your stored elements become Fire.</t>
+          <t>Double the fire already there.</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fan the Flames</t>
+          <t>Gust</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1677,12 +1677,12 @@
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Double the Burn on the target.</t>
+          <t>Targeted: remove 1 Essence of your choice from the target.</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Double the fire already there.</t>
+          <t>A precise gust plucks one piece away.</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Gust</t>
+          <t>Spring Word</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F24" s="7" t="n">
@@ -1728,12 +1728,12 @@
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Targeted: remove 1 Essence of your choice from the target.</t>
+          <t>Put a Water anywhere you like in this turn's chant.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>A precise gust plucks one piece away.</t>
+          <t>A word that wells up.</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Spring Word</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire</t>
+          <t>Air → Water</t>
         </is>
       </c>
       <c r="C25" s="5">
@@ -1764,14 +1764,14 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>1</v>
@@ -1779,24 +1779,24 @@
       <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Put a Water anywhere you like in this turn's chant.</t>
+          <t>Heal 2.</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>A word that wells up.</t>
+          <t>Soft and steady.</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>AF</t>
+          <t>AW</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Refresh</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1830,12 +1830,12 @@
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Heal 2.</t>
+          <t>Remove all your debuffs (frozen elements, Blind, Confuse, Bleed, Silence); +1 Water next turn.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Soft and steady.</t>
+          <t>Wash the frost off.</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Unbind</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1881,12 +1881,12 @@
       <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Remove all your debuffs (frozen elements, Blind, Confuse, Bleed, Silence); +1 Water next turn.</t>
+          <t>Cure Silence on all your spells.</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Wash the frost off.</t>
+          <t>Your voice returns.</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Unbind</t>
+          <t>Blowtorch</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Air → Water</t>
+          <t>Fire → Air</t>
         </is>
       </c>
       <c r="C28" s="5">
@@ -1917,14 +1917,14 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>1</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>1</v>
@@ -1932,24 +1932,24 @@
       <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Cure Silence on all your spells.</t>
+          <t>Remove the rightmost Essence of the target (+1 if it is burning).</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Your voice returns.</t>
+          <t>Hotter where it's already burning.</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
+          <t>FA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Blowtorch</t>
+          <t>Conjure Flame</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F29" s="7" t="n">
@@ -1983,12 +1983,12 @@
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of the target (+1 if it is burning).</t>
+          <t>+2 conjured Fire next turn.</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Hotter where it's already burning.</t>
+          <t>Two flames, borrowed for a turn.</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Conjure Flame</t>
+          <t>Phase Shift</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2034,12 +2034,12 @@
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>+2 conjured Fire next turn.</t>
+          <t>Make the target Ethereal (your spells remove double from it this turn).</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Two flames, borrowed for a turn.</t>
+          <t>Untouchable by chants, fragile to magic.</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Phase Shift</t>
+          <t>Thorn Mantle</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F31" s="7" t="n">
@@ -2085,12 +2085,12 @@
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>Make the target Ethereal (your spells remove double from it this turn).</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Thorns 1 for the rest of the fight.</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Untouchable by chants, fragile to magic.</t>
+          <t>Anything that strikes you gets burned.</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Thorn Mantle</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F32" s="7" t="n">
@@ -2136,12 +2136,12 @@
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Thorns 1 for the rest of the fight.</t>
+          <t>Burn 1 on all enemies.</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Anything that strikes you gets burned.</t>
+          <t>The wind spreads it everywhere.</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Blood Price</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Fire → Air</t>
+          <t>Fire → Fire</t>
         </is>
       </c>
       <c r="C33" s="5">
@@ -2167,44 +2167,44 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="6" t="n">
-        <v>1</v>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Burn 1 on every enemy.</t>
+          <t>Lose 3 HP; +4 random elements now.</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>The wind spreads it everywhere.</t>
+          <t>Pay in blood, gain in power.</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>FF</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Blood Price</t>
+          <t>Fire Ball</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F34" s="7" t="n">
@@ -2235,15 +2235,19 @@
       <c r="H34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>Lose 3 HP; +4 random elements now.</t>
+          <t>Remove the rightmost Essence of the target.</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Pay in blood, gain in power.</t>
+          <t>The classic.</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2255,7 +2259,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Fire Ball</t>
+          <t>Flare</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -2286,19 +2290,15 @@
       <c r="H35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of the target.</t>
+          <t>Remove the leftmost Essence of the target.</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>The classic.</t>
+          <t>Burn away the front line.</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Flare</t>
+          <t>Snuff Out</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2344,12 +2344,12 @@
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Remove the leftmost Essence of the target.</t>
+          <t>If the target has 3 or fewer elements, destroy it.</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>Burn away the front line.</t>
+          <t>Small flames are easy to pinch.</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Snuff Out</t>
+          <t>Twin Flames</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2395,12 +2395,12 @@
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>If the target has 3 or fewer elements, destroy it.</t>
+          <t>Burn 2 on the target.</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>Small flames are easy to pinch.</t>
+          <t>Two fires, one foe.</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Twin Flames</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire</t>
+          <t>Fire → Water</t>
         </is>
       </c>
       <c r="C38" s="5">
@@ -2431,14 +2431,14 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>0</v>
@@ -2446,24 +2446,24 @@
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Burn 2 on the target.</t>
+          <t>Turn the rightmost Essence of the target into Fire.</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Two fires, one foe.</t>
+          <t>Water at the end turns to fire.</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Breath Word</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -2497,12 +2497,12 @@
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>Turn the rightmost Essence of the target into Fire.</t>
+          <t>Put a Air anywhere you like in this turn's chant.</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>Water at the end turns to fire.</t>
+          <t>Exhale, and the wind answers.</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Breath Word</t>
+          <t>Cauterize</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2548,12 +2548,12 @@
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>Put a Air anywhere you like in this turn's chant.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): The target can never heal or regrow elements.</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>Exhale, and the wind answers.</t>
+          <t>Seal the wound so it never grows back.</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Cauterize</t>
+          <t>Mimic</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -2599,12 +2599,12 @@
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): The target can never heal or regrow elements.</t>
+          <t>Repeat the previous spell that fired this cast.</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>Seal the wound so it never grows back.</t>
+          <t>Do that again.</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Mimic</t>
+          <t>Scald</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F42" s="7" t="n">
@@ -2650,12 +2650,12 @@
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>Repeat the previous spell that fired this cast.</t>
+          <t>Remove the rightmost Essence of the target; Weaken 1 on the target.</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>Do that again.</t>
+          <t>Boiling water, badly thrown.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Scald</t>
+          <t>Mist Veil</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Fire → Water</t>
+          <t>Water → Air</t>
         </is>
       </c>
       <c r="C43" s="5">
@@ -2686,39 +2686,39 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>1</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="5" t="n">
-        <v>0</v>
+      <c r="H43" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of the target; Weaken 1 on the target.</t>
+          <t>You become Ethereal this turn.</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Boiling water, badly thrown.</t>
+          <t>Blades pass through you. Curses don't.</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Mist Veil</t>
+          <t>Riptide</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -2752,12 +2752,12 @@
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>You become Ethereal this turn.</t>
+          <t>Move 1 element of the target to any position you choose; Weaken 1 on the target.</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>Blades pass through you. Curses don't.</t>
+          <t>Drags one piece out of place and knocks it off balance.</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Riptide</t>
+          <t>Spark Word</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
@@ -2803,12 +2803,12 @@
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Move 1 element of the target to any position you choose; Weaken 1 on the target.</t>
+          <t>Put a Fire anywhere you like in this turn's chant.</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>Drags one piece out of place and knocks it off balance.</t>
+          <t>Say fire, and there is fire.</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Spark Word</t>
+          <t>Undertow</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -2854,12 +2854,12 @@
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>Put a Fire anywhere you like in this turn's chant.</t>
+          <t>Move 2 elements of the target to any position you choose.</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>Say fire, and there is fire.</t>
+          <t>The current rearranges everything.</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -2871,7 +2871,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Undertow</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
@@ -2905,12 +2905,12 @@
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Move 2 elements of the target to any position you choose.</t>
+          <t>Gain Aegis (1 hit).</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>The current rearranges everything.</t>
+          <t>The next blow simply stops.</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Graft</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Water → Air</t>
+          <t>Water → Fire</t>
         </is>
       </c>
       <c r="C48" s="5">
@@ -2941,39 +2941,39 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>0</v>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G48" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="6" t="n">
-        <v>1</v>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>Gain Aegis (1 hit).</t>
+          <t>Put a Water at the front of the target.</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>The next blow simply stops.</t>
+          <t>Plant water at its leftmost end, then chant it away.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>WF</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Graft</t>
+          <t>Hot Spring</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F49" s="7" t="n">
@@ -3007,12 +3007,12 @@
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>Put a Water at the front of the target.</t>
+          <t>Heal 2; gain 1 Shield.</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Plant water at its leftmost end, then chant it away.</t>
+          <t>Warm water, warm heart.</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Hot Spring</t>
+          <t>Steam</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -3058,12 +3058,12 @@
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Heal 2; gain 1 Shield.</t>
+          <t>Gain 2 Shield; Weaken 1 on the target.</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Warm water, warm heart.</t>
+          <t>Hide in the hiss.</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Steam</t>
+          <t>Frost Nova</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Water → Fire</t>
+          <t>Water → Water</t>
         </is>
       </c>
       <c r="C51" s="5">
@@ -3097,11 +3097,11 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F51" s="7" t="n">
-        <v>1</v>
+      <c r="F51" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" s="5" t="n">
         <v>0</v>
@@ -3109,24 +3109,24 @@
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>Gain 2 Shield; Weaken 1 on the target.</t>
+          <t>Weaken 1 on all enemies.</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Hide in the hiss.</t>
+          <t>Every blade goes numb.</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>WW</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Frost Nova</t>
+          <t>Soak</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
@@ -3160,12 +3160,12 @@
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>Weaken 1 on every enemy.</t>
+          <t>Expose 2 on the target.</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>Every blade goes numb.</t>
+          <t>Drenched and sagging.</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Soak</t>
+          <t>Summon Rain</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
@@ -3211,12 +3211,12 @@
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Expose 2 on the target.</t>
+          <t>+2 conjured Water next turn.</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Drenched and sagging.</t>
+          <t>Two drops, gone by nightfall.</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -3228,7 +3228,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Summon Rain</t>
+          <t>Tide Pool</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
@@ -3262,12 +3262,12 @@
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>+2 conjured Water next turn.</t>
+          <t>Heal 3.</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Two drops, gone by nightfall.</t>
+          <t>Rest in the shallows.</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Tide Pool</t>
+          <t>Water Wall</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -3310,15 +3310,19 @@
       <c r="H55" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Heal 3.</t>
+          <t>Gain 4 Shield.</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Rest in the shallows.</t>
+          <t>Stand behind the water.</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -3330,12 +3334,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Water Wall</t>
+          <t>Tempest</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Water → Water</t>
+          <t>Air → Air → Air</t>
         </is>
       </c>
       <c r="C56" s="5">
@@ -3344,48 +3348,44 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G56" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>Gain 4 Shield.</t>
+          <t>+2 random elements next turn; Rearrange 1.</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Stand behind the water.</t>
+          <t>The storm brings more, and moves what it touches.</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>AAA</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Tempest</t>
+          <t>Trade Winds</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3419,12 +3419,12 @@
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>+2 random elements next turn; Rearrange 1: move one element of your chant to another spot.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: +2 random elements now.</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>The storm brings more, and moves what it touches.</t>
+          <t>The wind brings a little more, every turn.</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Trade Winds</t>
+          <t>Gale Force</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Air</t>
+          <t>Air → Air → Fire</t>
         </is>
       </c>
       <c r="C58" s="5">
@@ -3455,39 +3455,39 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: +2 random elements now.</t>
+          <t>Remove up to 3 Air from the target.</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>The wind brings a little more, every turn.</t>
+          <t>Two breaths torn out of it.</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AAF</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Gale Force</t>
+          <t>Venom Coat</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3521,12 +3521,12 @@
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Air from the target.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): All enemies your Release hits get Poison 1.</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Two breaths torn out of it.</t>
+          <t>Every enemy your chant touches is poisoned.</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Venom Coat</t>
+          <t>Soul Siphon</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Fire</t>
+          <t>Air → Fire → Air</t>
         </is>
       </c>
       <c r="C60" s="5">
@@ -3572,29 +3572,29 @@
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Every enemy your Release hits gets Poison 1.</t>
+          <t>Remove the 3 leftmost Essence of the target; next turn you gain the removed elements (conjured).</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Every enemy your chant touches is poisoned.</t>
+          <t>Pull its two leftmost elements into your hand.</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>AAF</t>
+          <t>AFA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Soul Siphon</t>
+          <t>Backdraft</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Air</t>
+          <t>Air → Fire → Fire</t>
         </is>
       </c>
       <c r="C61" s="5">
@@ -3612,40 +3612,40 @@
         </is>
       </c>
       <c r="F61" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 leftmost Essence of the target; next turn you gain the removed elements (conjured).</t>
+          <t>Remove the 3 rightmost Essence of the target; Overload 1.</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>Pull its two leftmost elements into your hand.</t>
+          <t>Big blast, slow recovery.</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>AFA</t>
+          <t>AFF</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Backdraft</t>
+          <t>Resonance</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Fire</t>
+          <t>Air → Fire → Water</t>
         </is>
       </c>
       <c r="C62" s="5">
@@ -3659,14 +3659,14 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F62" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>1</v>
@@ -3674,29 +3674,29 @@
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of the target; Overload 1: 1 fewer element next turn.</t>
+          <t>Duplicate 1.</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Big blast, slow recovery.</t>
+          <t>One note, sung twice.</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>AFF</t>
+          <t>AFW</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Resonance</t>
+          <t>Echo Chamber</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Water</t>
+          <t>Air → Water → Air</t>
         </is>
       </c>
       <c r="C63" s="5">
@@ -3713,36 +3713,36 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F63" s="7" t="n">
-        <v>1</v>
+      <c r="F63" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G63" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Pick an element in this turn's chant: it becomes 2 in a row.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): The first spell you trigger each turn fires twice.</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>One note, sung twice.</t>
+          <t>The first spell each turn rings twice.</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>AFW</t>
+          <t>AWA</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Echo Chamber</t>
+          <t>Whirlpool</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
@@ -3776,12 +3776,12 @@
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): The first spell you trigger each turn fires twice.</t>
+          <t>Remove the rightmost Essence of all enemies; Weaken 1 on all enemies.</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>The first spell each turn rings twice.</t>
+          <t>Spins them off balance.</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Whirlpool</t>
+          <t>Storm Front</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Air</t>
+          <t>Air → Water → Fire</t>
         </is>
       </c>
       <c r="C65" s="5">
@@ -3812,44 +3812,44 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>0</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G65" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of every enemy; Weaken 1 on every enemy.</t>
+          <t>Gain 5 Shield; Thorns 2 this turn.</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>Spins them off balance.</t>
+          <t>Touch it and get burned.</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>AWA</t>
+          <t>AWF</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Storm Front</t>
+          <t>Frailty</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Fire</t>
+          <t>Air → Water → Water</t>
         </is>
       </c>
       <c r="C66" s="5">
@@ -3863,14 +3863,14 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>1</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>1</v>
@@ -3878,29 +3878,29 @@
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>Gain 5 Shield; Thorns 2 this turn.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): The target is permanently Exposed.</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>Touch it and get burned.</t>
+          <t>It never recovers its guard.</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>AWF</t>
+          <t>AWW</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Frailty</t>
+          <t>Inferno</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Water</t>
+          <t>Fire → Any → Fire</t>
         </is>
       </c>
       <c r="C67" s="5">
@@ -3917,41 +3917,41 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="8" t="n">
+      <c r="F67" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H67" s="6" t="n">
-        <v>1</v>
+      <c r="G67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): The target is permanently Exposed.</t>
+          <t>Remove the rightmost Essence of all enemies.</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>It never recovers its guard.</t>
+          <t>Everything burns a little.</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>AWW</t>
+          <t>F?F</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Inferno</t>
+          <t>Kindling Wind</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Fire → Any → Fire</t>
+          <t>Fire → Air → Fire</t>
         </is>
       </c>
       <c r="C68" s="5">
@@ -3974,35 +3974,35 @@
       <c r="G68" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="5" t="n">
-        <v>0</v>
+      <c r="H68" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of every enemy.</t>
+          <t>Amplify 1.</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>Everything burns a little.</t>
+          <t>Whatever your chant hit burns one element deeper.</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>F?F</t>
+          <t>FAF</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Kindling Wind</t>
+          <t>Absorb</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Fire → Air → Fire</t>
+          <t>Fire → Air → Water</t>
         </is>
       </c>
       <c r="C69" s="5">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="F69" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G69" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H69" s="6" t="n">
         <v>1</v>
@@ -4031,24 +4031,24 @@
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Amplify 1: when the chant is Released, every enemy it hits also loses its 1 rightmost Essence.</t>
+          <t>Remove the 2 rightmost Essence of the target; if this defeats it, heal 5 HP.</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>Whatever your chant hit burns one element deeper.</t>
+          <t>Take the last of it, and feel much better.</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>FAF</t>
+          <t>FAW</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Absorb</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F70" s="7" t="n">
@@ -4082,12 +4082,12 @@
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 rightmost Essence of the target; if this defeats it, heal 5 HP.</t>
+          <t>After the Release, the 2 rightmost elements of your chant go back to your elements.</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>Take the last of it, and feel much better.</t>
+          <t>Two of the chant's elements come back.</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Last Rites</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Fire → Air → Water</t>
+          <t>Fire → Fire → Air</t>
         </is>
       </c>
       <c r="C71" s="5">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F71" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H71" s="6" t="n">
         <v>1</v>
@@ -4133,29 +4133,29 @@
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>After the Release, the 2 rightmost elements of your chant go back to your elements.</t>
+          <t>If the target has 4 or fewer elements, destroy it.</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>Two of the chant's elements come back.</t>
+          <t>If it's already weak, end it.</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>FAW</t>
+          <t>FFA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Last Rites</t>
+          <t>Kindle</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Air</t>
+          <t>Fire → Fire → Fire</t>
         </is>
       </c>
       <c r="C72" s="5">
@@ -4173,28 +4173,28 @@
         </is>
       </c>
       <c r="F72" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="6" t="n">
-        <v>1</v>
+      <c r="H72" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>If the target has 4 or fewer elements, destroy it.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Whenever you apply Burn, apply 1 more; Burn 1 on all enemies.</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>If it's already weak, end it.</t>
+          <t>Every fire you light burns a little longer.</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>FFA</t>
+          <t>FFF</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Poison 2 on every enemy.</t>
+          <t>Poison 2 on all enemies.</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -4592,7 +4592,7 @@
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>Expose 1 on every enemy.</t>
+          <t>Expose 1 on all enemies.</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -4694,7 +4694,7 @@
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>Weaken 1 on every enemy; gain 4 Shield.</t>
+          <t>Weaken 1 on all enemies; gain 4 Shield.</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -5000,7 +5000,7 @@
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of every enemy.</t>
+          <t>Remove the 3 rightmost Essence of all enemies.</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
@@ -5204,7 +5204,7 @@
       <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>Freeze 2 on every enemy.</t>
+          <t>Freeze 2 on all enemies.</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -5459,7 +5459,7 @@
       <c r="I97" s="5" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Echo: the chant is Released twice this turn.</t>
+          <t>Echo.</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
@@ -5663,7 +5663,7 @@
       <c r="I101" s="5" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Every enemy permanently deals 25% less damage.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): All enemies deal 25% less damage for the rest of the fight.</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
@@ -5714,7 +5714,7 @@
       <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of every enemy; Weaken 3 on every enemy.</t>
+          <t>Remove the 2 leftmost Essence of all enemies; Weaken 3 on all enemies.</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
@@ -5765,7 +5765,7 @@
       <c r="I103" s="5" t="inlineStr"/>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Burn 3 on every enemy.</t>
+          <t>Burn 3 on all enemies.</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -5816,7 +5816,7 @@
       <c r="I104" s="5" t="inlineStr"/>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>Echo: the chant is Released twice this turn; Amplify 1: when the chant is Released, every enemy it hits also loses its 1 rightmost Essence.</t>
+          <t>Echo; Amplify 1.</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
@@ -5867,7 +5867,7 @@
       <c r="I105" s="5" t="inlineStr"/>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>Pick an element in this turn's chant: it becomes 3 in a row.</t>
+          <t>Duplicate 2.</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
@@ -5918,7 +5918,7 @@
       <c r="I106" s="5" t="inlineStr"/>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Every enemy your Release hits gets Burn 1.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): All enemies your Release hits get Burn 1.</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
@@ -5969,7 +5969,7 @@
       <c r="I107" s="5" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of every enemy; Burn 4 on every enemy.</t>
+          <t>Remove the 3 rightmost Essence of all enemies; Burn 4 on all enemies.</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -6122,7 +6122,7 @@
       <c r="I110" s="5" t="inlineStr"/>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>Gain 14 Shield; heal 10; Freeze 2 on every enemy.</t>
+          <t>Gain 14 Shield; heal 10; Freeze 2 on all enemies.</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
@@ -6136,8 +6136,59 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>Annihilate</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Fire → Water → Air → Any → Water → Fire</t>
+        </is>
+      </c>
+      <c r="C111" s="5">
+        <f>LEN(L111)</f>
+        <v/>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H111" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="5" t="inlineStr"/>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>Annihilate 1 element on all enemies (you choose Fire, Water or Air: every Essence of it is removed).</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>Pick one. It stops existing.</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>FWA?WF</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K110"/>
+  <autoFilter ref="A1:K111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/spells.xlsx
+++ b/docs/spells.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Spells" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Spells'!$A$1:$K$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Spells'!$A$1:$L$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,8 @@
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="90" customWidth="1" min="10" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -559,7 +560,12 @@
           <t>Flavor</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>code</t>
         </is>
@@ -577,7 +583,7 @@
         </is>
       </c>
       <c r="C2" s="5">
-        <f>LEN(L2)</f>
+        <f>LEN(M2)</f>
         <v/>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -610,7 +616,12 @@
           <t>A breath that isn't yours to keep.</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>borrowed_breath</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -628,7 +639,7 @@
         </is>
       </c>
       <c r="C3" s="5">
-        <f>LEN(L3)</f>
+        <f>LEN(M3)</f>
         <v/>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -653,15 +664,20 @@
       <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of the target; next turn you gain the removed elements (conjured).</t>
+          <t>Remove the 2 leftmost Essence of the target; next turn you gain the removed Essence (conjured).</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Pull its leftmost element into your hand.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+          <t>Pull its leftmost Essence into your hand.</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>siphon</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -679,7 +695,7 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>LEN(L4)</f>
+        <f>LEN(M4)</f>
         <v/>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -712,7 +728,12 @@
           <t>Something foul rides the breeze.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>taint</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -730,7 +751,7 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>LEN(L5)</f>
+        <f>LEN(M5)</f>
         <v/>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -755,15 +776,20 @@
       <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Move 1 element of the target to any position you choose.</t>
+          <t>Move 1 Essence of the target to any position you choose.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Lift one element and set it down where you like.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+          <t>Lift one Essence and set it down where you like.</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>updraft</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -781,7 +807,7 @@
         </is>
       </c>
       <c r="C6" s="5">
-        <f>LEN(L6)</f>
+        <f>LEN(M6)</f>
         <v/>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -814,7 +840,12 @@
           <t>A word in the ear, and its arm goes slack.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>whisper</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -832,7 +863,7 @@
         </is>
       </c>
       <c r="C7" s="5">
-        <f>LEN(L7)</f>
+        <f>LEN(M7)</f>
         <v/>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -865,7 +896,12 @@
           <t>Glowing ash marks the weak spot.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>cinder</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -883,7 +919,7 @@
         </is>
       </c>
       <c r="C8" s="5">
-        <f>LEN(L8)</f>
+        <f>LEN(M8)</f>
         <v/>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -916,7 +952,12 @@
           <t>A flash of light burns the fog away.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>clear_sight</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -934,7 +975,7 @@
         </is>
       </c>
       <c r="C9" s="5">
-        <f>LEN(L9)</f>
+        <f>LEN(M9)</f>
         <v/>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -967,7 +1008,12 @@
           <t>A single spark that won't go out.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>ember</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -985,7 +1031,7 @@
         </is>
       </c>
       <c r="C10" s="5">
-        <f>LEN(L10)</f>
+        <f>LEN(M10)</f>
         <v/>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1018,7 +1064,12 @@
           <t>Only big things catch.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>spark</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -1036,7 +1087,7 @@
         </is>
       </c>
       <c r="C11" s="5">
-        <f>LEN(L11)</f>
+        <f>LEN(M11)</f>
         <v/>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1069,7 +1120,12 @@
           <t>Wash it, wrap it, keep going.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>bandage</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1087,7 +1143,7 @@
         </is>
       </c>
       <c r="C12" s="5">
-        <f>LEN(L12)</f>
+        <f>LEN(M12)</f>
         <v/>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1120,7 +1176,12 @@
           <t>Cold makes armour brittle.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>chill</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1138,7 +1199,7 @@
         </is>
       </c>
       <c r="C13" s="5">
-        <f>LEN(L13)</f>
+        <f>LEN(M13)</f>
         <v/>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1171,7 +1232,12 @@
           <t>Every drop helps.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>droplet</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1189,7 +1255,7 @@
         </is>
       </c>
       <c r="C14" s="5">
-        <f>LEN(L14)</f>
+        <f>LEN(M14)</f>
         <v/>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1222,7 +1288,12 @@
           <t>Cool on the skin.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>mist</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1240,7 +1311,7 @@
         </is>
       </c>
       <c r="C15" s="5">
-        <f>LEN(L15)</f>
+        <f>LEN(M15)</f>
         <v/>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1273,7 +1344,12 @@
           <t>The end of it turns to water.</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>ripple</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1291,7 +1367,7 @@
         </is>
       </c>
       <c r="C16" s="5">
-        <f>LEN(L16)</f>
+        <f>LEN(M16)</f>
         <v/>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1324,7 +1400,12 @@
           <t>Shaves the big ones down to size.</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>cyclone</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
@@ -1342,7 +1423,7 @@
         </is>
       </c>
       <c r="C17" s="5">
-        <f>LEN(L17)</f>
+        <f>LEN(M17)</f>
         <v/>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1375,7 +1456,12 @@
           <t>A wall of wind that bites back.</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>scatter</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
@@ -1393,7 +1479,7 @@
         </is>
       </c>
       <c r="C18" s="5">
-        <f>LEN(L18)</f>
+        <f>LEN(M18)</f>
         <v/>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1426,7 +1512,12 @@
           <t>A choking cloud settles on it.</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>miasma</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
@@ -1444,7 +1535,7 @@
         </is>
       </c>
       <c r="C19" s="5">
-        <f>LEN(L19)</f>
+        <f>LEN(M19)</f>
         <v/>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1477,7 +1568,12 @@
           <t>Breathe in, breathe out.</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>steady_mind</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
@@ -1495,7 +1591,7 @@
         </is>
       </c>
       <c r="C20" s="5">
-        <f>LEN(L20)</f>
+        <f>LEN(M20)</f>
         <v/>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1524,7 +1620,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>+1 random element next turn.</t>
+          <t>+1 random Essence next turn.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1532,7 +1628,12 @@
           <t>The wind brings more.</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>tailwind</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
@@ -1550,7 +1651,7 @@
         </is>
       </c>
       <c r="C21" s="5">
-        <f>LEN(L21)</f>
+        <f>LEN(M21)</f>
         <v/>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1575,15 +1676,20 @@
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Turn 2 of your stored elements into Fire.</t>
+          <t>Turn 2 of your stored Essence into Fire.</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Two of your stored elements become Fire.</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
+          <t>Two of your stored Essence become Fire.</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>alchemists_breath</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>AF</t>
         </is>
@@ -1601,7 +1707,7 @@
         </is>
       </c>
       <c r="C22" s="5">
-        <f>LEN(L22)</f>
+        <f>LEN(M22)</f>
         <v/>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1634,7 +1740,12 @@
           <t>Double the fire already there.</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>fan_the_flames</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>AF</t>
         </is>
@@ -1652,7 +1763,7 @@
         </is>
       </c>
       <c r="C23" s="5">
-        <f>LEN(L23)</f>
+        <f>LEN(M23)</f>
         <v/>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1685,7 +1796,12 @@
           <t>A precise gust plucks one piece away.</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>gust</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>AF</t>
         </is>
@@ -1703,7 +1819,7 @@
         </is>
       </c>
       <c r="C24" s="5">
-        <f>LEN(L24)</f>
+        <f>LEN(M24)</f>
         <v/>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1736,7 +1852,12 @@
           <t>A word that wells up.</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>spring_word</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>AF</t>
         </is>
@@ -1754,7 +1875,7 @@
         </is>
       </c>
       <c r="C25" s="5">
-        <f>LEN(L25)</f>
+        <f>LEN(M25)</f>
         <v/>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1787,7 +1908,12 @@
           <t>Soft and steady.</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>rain</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>AW</t>
         </is>
@@ -1805,7 +1931,7 @@
         </is>
       </c>
       <c r="C26" s="5">
-        <f>LEN(L26)</f>
+        <f>LEN(M26)</f>
         <v/>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1830,7 +1956,7 @@
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Remove all your debuffs (frozen elements, Blind, Confuse, Bleed, Silence); +1 Water next turn.</t>
+          <t>Remove all your debuffs (frozen Essence, Blind, Confuse, Bleed, Silence); +1 Water next turn.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -1838,7 +1964,12 @@
           <t>Wash the frost off.</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>refresh</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>AW</t>
         </is>
@@ -1856,7 +1987,7 @@
         </is>
       </c>
       <c r="C27" s="5">
-        <f>LEN(L27)</f>
+        <f>LEN(M27)</f>
         <v/>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1889,7 +2020,12 @@
           <t>Your voice returns.</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>unbind</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>AW</t>
         </is>
@@ -1907,7 +2043,7 @@
         </is>
       </c>
       <c r="C28" s="5">
-        <f>LEN(L28)</f>
+        <f>LEN(M28)</f>
         <v/>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1940,7 +2076,12 @@
           <t>Hotter where it's already burning.</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>blowtorch</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
@@ -1958,7 +2099,7 @@
         </is>
       </c>
       <c r="C29" s="5">
-        <f>LEN(L29)</f>
+        <f>LEN(M29)</f>
         <v/>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1991,7 +2132,12 @@
           <t>Two flames, borrowed for a turn.</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>conjure_flame</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
@@ -2009,7 +2155,7 @@
         </is>
       </c>
       <c r="C30" s="5">
-        <f>LEN(L30)</f>
+        <f>LEN(M30)</f>
         <v/>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2042,7 +2188,12 @@
           <t>Untouchable by chants, fragile to magic.</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>phase_shift</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
@@ -2060,7 +2211,7 @@
         </is>
       </c>
       <c r="C31" s="5">
-        <f>LEN(L31)</f>
+        <f>LEN(M31)</f>
         <v/>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2093,7 +2244,12 @@
           <t>Anything that strikes you gets burned.</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>thorn_mantle</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
@@ -2111,7 +2267,7 @@
         </is>
       </c>
       <c r="C32" s="5">
-        <f>LEN(L32)</f>
+        <f>LEN(M32)</f>
         <v/>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2144,7 +2300,12 @@
           <t>The wind spreads it everywhere.</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>wildfire</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
@@ -2162,7 +2323,7 @@
         </is>
       </c>
       <c r="C33" s="5">
-        <f>LEN(L33)</f>
+        <f>LEN(M33)</f>
         <v/>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2187,7 +2348,7 @@
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Lose 3 HP; +4 random elements now.</t>
+          <t>Lose 3 HP; +4 random Essence now.</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -2195,7 +2356,12 @@
           <t>Pay in blood, gain in power.</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>blood_price</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>FF</t>
         </is>
@@ -2213,7 +2379,7 @@
         </is>
       </c>
       <c r="C34" s="5">
-        <f>LEN(L34)</f>
+        <f>LEN(M34)</f>
         <v/>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2250,7 +2416,12 @@
           <t>The classic.</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>fire_ball</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>FF</t>
         </is>
@@ -2268,7 +2439,7 @@
         </is>
       </c>
       <c r="C35" s="5">
-        <f>LEN(L35)</f>
+        <f>LEN(M35)</f>
         <v/>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2301,7 +2472,12 @@
           <t>Burn away the front line.</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>flare</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>FF</t>
         </is>
@@ -2319,7 +2495,7 @@
         </is>
       </c>
       <c r="C36" s="5">
-        <f>LEN(L36)</f>
+        <f>LEN(M36)</f>
         <v/>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2344,7 +2520,7 @@
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>If the target has 3 or fewer elements, destroy it.</t>
+          <t>If the target has 3 or fewer Essence, destroy it.</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2352,7 +2528,12 @@
           <t>Small flames are easy to pinch.</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>snuff_out</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>FF</t>
         </is>
@@ -2370,7 +2551,7 @@
         </is>
       </c>
       <c r="C37" s="5">
-        <f>LEN(L37)</f>
+        <f>LEN(M37)</f>
         <v/>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2403,7 +2584,12 @@
           <t>Two fires, one foe.</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>twin_flames</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>FF</t>
         </is>
@@ -2421,7 +2607,7 @@
         </is>
       </c>
       <c r="C38" s="5">
-        <f>LEN(L38)</f>
+        <f>LEN(M38)</f>
         <v/>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2454,7 +2640,12 @@
           <t>Water at the end turns to fire.</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>boil</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>FW</t>
         </is>
@@ -2472,7 +2663,7 @@
         </is>
       </c>
       <c r="C39" s="5">
-        <f>LEN(L39)</f>
+        <f>LEN(M39)</f>
         <v/>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2505,7 +2696,12 @@
           <t>Exhale, and the wind answers.</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>breath_word</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>FW</t>
         </is>
@@ -2523,7 +2719,7 @@
         </is>
       </c>
       <c r="C40" s="5">
-        <f>LEN(L40)</f>
+        <f>LEN(M40)</f>
         <v/>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2548,7 +2744,7 @@
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): The target can never heal or regrow elements.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): The target can never heal or regrow Essence.</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -2556,7 +2752,12 @@
           <t>Seal the wound so it never grows back.</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>cauterize</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>FW</t>
         </is>
@@ -2574,7 +2775,7 @@
         </is>
       </c>
       <c r="C41" s="5">
-        <f>LEN(L41)</f>
+        <f>LEN(M41)</f>
         <v/>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2607,7 +2808,12 @@
           <t>Do that again.</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>mimic</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>FW</t>
         </is>
@@ -2625,7 +2831,7 @@
         </is>
       </c>
       <c r="C42" s="5">
-        <f>LEN(L42)</f>
+        <f>LEN(M42)</f>
         <v/>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2658,7 +2864,12 @@
           <t>Boiling water, badly thrown.</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>scald</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>FW</t>
         </is>
@@ -2676,7 +2887,7 @@
         </is>
       </c>
       <c r="C43" s="5">
-        <f>LEN(L43)</f>
+        <f>LEN(M43)</f>
         <v/>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2709,7 +2920,12 @@
           <t>Blades pass through you. Curses don't.</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>mist_veil</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>WA</t>
         </is>
@@ -2727,7 +2943,7 @@
         </is>
       </c>
       <c r="C44" s="5">
-        <f>LEN(L44)</f>
+        <f>LEN(M44)</f>
         <v/>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2752,7 +2968,7 @@
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>Move 1 element of the target to any position you choose; Weaken 1 on the target.</t>
+          <t>Move 1 Essence of the target to any position you choose; Weaken 1 on the target.</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -2760,7 +2976,12 @@
           <t>Drags one piece out of place and knocks it off balance.</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>riptide</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>WA</t>
         </is>
@@ -2778,7 +2999,7 @@
         </is>
       </c>
       <c r="C45" s="5">
-        <f>LEN(L45)</f>
+        <f>LEN(M45)</f>
         <v/>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2811,7 +3032,12 @@
           <t>Say fire, and there is fire.</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>spark_word</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>WA</t>
         </is>
@@ -2829,7 +3055,7 @@
         </is>
       </c>
       <c r="C46" s="5">
-        <f>LEN(L46)</f>
+        <f>LEN(M46)</f>
         <v/>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2854,7 +3080,7 @@
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>Move 2 elements of the target to any position you choose.</t>
+          <t>Move 2 Essence of the target to any position you choose.</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -2862,7 +3088,12 @@
           <t>The current rearranges everything.</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>undertow</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>WA</t>
         </is>
@@ -2880,7 +3111,7 @@
         </is>
       </c>
       <c r="C47" s="5">
-        <f>LEN(L47)</f>
+        <f>LEN(M47)</f>
         <v/>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2913,7 +3144,12 @@
           <t>The next blow simply stops.</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>ward</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>WA</t>
         </is>
@@ -2931,7 +3167,7 @@
         </is>
       </c>
       <c r="C48" s="5">
-        <f>LEN(L48)</f>
+        <f>LEN(M48)</f>
         <v/>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2964,7 +3200,12 @@
           <t>Plant water at its leftmost end, then chant it away.</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>graft</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>WF</t>
         </is>
@@ -2982,7 +3223,7 @@
         </is>
       </c>
       <c r="C49" s="5">
-        <f>LEN(L49)</f>
+        <f>LEN(M49)</f>
         <v/>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3015,7 +3256,12 @@
           <t>Warm water, warm heart.</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>hot_spring</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>WF</t>
         </is>
@@ -3033,7 +3279,7 @@
         </is>
       </c>
       <c r="C50" s="5">
-        <f>LEN(L50)</f>
+        <f>LEN(M50)</f>
         <v/>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -3066,7 +3312,12 @@
           <t>Hide in the hiss.</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>WF</t>
         </is>
@@ -3084,7 +3335,7 @@
         </is>
       </c>
       <c r="C51" s="5">
-        <f>LEN(L51)</f>
+        <f>LEN(M51)</f>
         <v/>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3117,7 +3368,12 @@
           <t>Every blade goes numb.</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>frost_nova</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>WW</t>
         </is>
@@ -3135,7 +3391,7 @@
         </is>
       </c>
       <c r="C52" s="5">
-        <f>LEN(L52)</f>
+        <f>LEN(M52)</f>
         <v/>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3168,7 +3424,12 @@
           <t>Drenched and sagging.</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>soak</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>WW</t>
         </is>
@@ -3186,7 +3447,7 @@
         </is>
       </c>
       <c r="C53" s="5">
-        <f>LEN(L53)</f>
+        <f>LEN(M53)</f>
         <v/>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3219,7 +3480,12 @@
           <t>Two drops, gone by nightfall.</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>summon_rain</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>WW</t>
         </is>
@@ -3237,7 +3503,7 @@
         </is>
       </c>
       <c r="C54" s="5">
-        <f>LEN(L54)</f>
+        <f>LEN(M54)</f>
         <v/>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3270,7 +3536,12 @@
           <t>Rest in the shallows.</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>tide_pool</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>WW</t>
         </is>
@@ -3288,7 +3559,7 @@
         </is>
       </c>
       <c r="C55" s="5">
-        <f>LEN(L55)</f>
+        <f>LEN(M55)</f>
         <v/>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3325,7 +3596,12 @@
           <t>Stand behind the water.</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>water_wall</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>WW</t>
         </is>
@@ -3343,7 +3619,7 @@
         </is>
       </c>
       <c r="C56" s="5">
-        <f>LEN(L56)</f>
+        <f>LEN(M56)</f>
         <v/>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3368,7 +3644,7 @@
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>+2 random elements next turn; Rearrange 1.</t>
+          <t>+2 random Essence next turn; Rearrange 1.</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -3376,7 +3652,12 @@
           <t>The storm brings more, and moves what it touches.</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>tempest</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
@@ -3394,7 +3675,7 @@
         </is>
       </c>
       <c r="C57" s="5">
-        <f>LEN(L57)</f>
+        <f>LEN(M57)</f>
         <v/>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -3419,7 +3700,7 @@
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: +2 random elements now.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: +2 random Essence now.</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -3427,7 +3708,12 @@
           <t>The wind brings a little more, every turn.</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>trade_winds</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
@@ -3445,7 +3731,7 @@
         </is>
       </c>
       <c r="C58" s="5">
-        <f>LEN(L58)</f>
+        <f>LEN(M58)</f>
         <v/>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -3478,7 +3764,12 @@
           <t>Two breaths torn out of it.</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>gale_force</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>AAF</t>
         </is>
@@ -3496,7 +3787,7 @@
         </is>
       </c>
       <c r="C59" s="5">
-        <f>LEN(L59)</f>
+        <f>LEN(M59)</f>
         <v/>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -3529,7 +3820,12 @@
           <t>Every enemy your chant touches is poisoned.</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>venom_coat</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>AAF</t>
         </is>
@@ -3547,7 +3843,7 @@
         </is>
       </c>
       <c r="C60" s="5">
-        <f>LEN(L60)</f>
+        <f>LEN(M60)</f>
         <v/>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3572,15 +3868,20 @@
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 leftmost Essence of the target; next turn you gain the removed elements (conjured).</t>
+          <t>Remove the 3 leftmost Essence of the target; next turn you gain the removed Essence (conjured).</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Pull its two leftmost elements into your hand.</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
+          <t>Pull its two leftmost Essence into your hand.</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>soul_siphon</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>AFA</t>
         </is>
@@ -3598,7 +3899,7 @@
         </is>
       </c>
       <c r="C61" s="5">
-        <f>LEN(L61)</f>
+        <f>LEN(M61)</f>
         <v/>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3631,7 +3932,12 @@
           <t>Big blast, slow recovery.</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>backdraft</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>AFF</t>
         </is>
@@ -3649,7 +3955,7 @@
         </is>
       </c>
       <c r="C62" s="5">
-        <f>LEN(L62)</f>
+        <f>LEN(M62)</f>
         <v/>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3682,7 +3988,12 @@
           <t>One note, sung twice.</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>resonance</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>AFW</t>
         </is>
@@ -3700,7 +4011,7 @@
         </is>
       </c>
       <c r="C63" s="5">
-        <f>LEN(L63)</f>
+        <f>LEN(M63)</f>
         <v/>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3733,7 +4044,12 @@
           <t>The first spell each turn rings twice.</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>echo_chamber</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>AWA</t>
         </is>
@@ -3751,7 +4067,7 @@
         </is>
       </c>
       <c r="C64" s="5">
-        <f>LEN(L64)</f>
+        <f>LEN(M64)</f>
         <v/>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3784,7 +4100,12 @@
           <t>Spins them off balance.</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>whirlpool</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>AWA</t>
         </is>
@@ -3802,7 +4123,7 @@
         </is>
       </c>
       <c r="C65" s="5">
-        <f>LEN(L65)</f>
+        <f>LEN(M65)</f>
         <v/>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -3835,7 +4156,12 @@
           <t>Touch it and get burned.</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>storm_front</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>AWF</t>
         </is>
@@ -3853,7 +4179,7 @@
         </is>
       </c>
       <c r="C66" s="5">
-        <f>LEN(L66)</f>
+        <f>LEN(M66)</f>
         <v/>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3886,7 +4212,12 @@
           <t>It never recovers its guard.</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>frailty</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>AWW</t>
         </is>
@@ -3904,7 +4235,7 @@
         </is>
       </c>
       <c r="C67" s="5">
-        <f>LEN(L67)</f>
+        <f>LEN(M67)</f>
         <v/>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3937,7 +4268,12 @@
           <t>Everything burns a little.</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>inferno</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>F?F</t>
         </is>
@@ -3955,7 +4291,7 @@
         </is>
       </c>
       <c r="C68" s="5">
-        <f>LEN(L68)</f>
+        <f>LEN(M68)</f>
         <v/>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3985,10 +4321,15 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>Whatever your chant hit burns one element deeper.</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
+          <t>Whatever your chant hit burns one Essence deeper.</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>kindling_wind</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>FAF</t>
         </is>
@@ -4006,7 +4347,7 @@
         </is>
       </c>
       <c r="C69" s="5">
-        <f>LEN(L69)</f>
+        <f>LEN(M69)</f>
         <v/>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -4039,7 +4380,12 @@
           <t>Take the last of it, and feel much better.</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>leech</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>FAW</t>
         </is>
@@ -4057,7 +4403,7 @@
         </is>
       </c>
       <c r="C70" s="5">
-        <f>LEN(L70)</f>
+        <f>LEN(M70)</f>
         <v/>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -4082,15 +4428,20 @@
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>After the Release, the 2 rightmost elements of your chant go back to your elements.</t>
+          <t>After the Release, the 2 rightmost Essence of your chant go back to your bag.</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>Two of the chant's elements come back.</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
+          <t>Two of the chant's Essence come back.</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>FAW</t>
         </is>
@@ -4108,7 +4459,7 @@
         </is>
       </c>
       <c r="C71" s="5">
-        <f>LEN(L71)</f>
+        <f>LEN(M71)</f>
         <v/>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -4133,7 +4484,7 @@
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>If the target has 4 or fewer elements, destroy it.</t>
+          <t>If the target has 4 or fewer Essence, destroy it.</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -4141,7 +4492,12 @@
           <t>If it's already weak, end it.</t>
         </is>
       </c>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>last_rites</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
         <is>
           <t>FFA</t>
         </is>
@@ -4159,7 +4515,7 @@
         </is>
       </c>
       <c r="C72" s="5">
-        <f>LEN(L72)</f>
+        <f>LEN(M72)</f>
         <v/>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -4192,7 +4548,12 @@
           <t>Every fire you light burns a little longer.</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>kindle</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>FFF</t>
         </is>
@@ -4210,7 +4571,7 @@
         </is>
       </c>
       <c r="C73" s="5">
-        <f>LEN(L73)</f>
+        <f>LEN(M73)</f>
         <v/>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -4243,7 +4604,12 @@
           <t>A crown that sets something alight each turn.</t>
         </is>
       </c>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>ember_crown</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>FFW</t>
         </is>
@@ -4261,7 +4627,7 @@
         </is>
       </c>
       <c r="C74" s="5">
-        <f>LEN(L74)</f>
+        <f>LEN(M74)</f>
         <v/>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -4294,7 +4660,12 @@
           <t>Two of its fires go out.</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>searing_mist</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>FFW</t>
         </is>
@@ -4312,7 +4683,7 @@
         </is>
       </c>
       <c r="C75" s="5">
-        <f>LEN(L75)</f>
+        <f>LEN(M75)</f>
         <v/>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -4345,7 +4716,12 @@
           <t>All its water becomes fire.</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>alchemy</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>FWA</t>
         </is>
@@ -4363,7 +4739,7 @@
         </is>
       </c>
       <c r="C76" s="5">
-        <f>LEN(L76)</f>
+        <f>LEN(M76)</f>
         <v/>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -4388,15 +4764,20 @@
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Choose an element: one of your draws each turn is always that element.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Choose an Essence: one of your draws each turn is always that Essence.</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>Choose an element; one draw each turn is always it.</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
+          <t>Choose an Essence; one draw each turn is always it.</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>attunement</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>FWA</t>
         </is>
@@ -4414,7 +4795,7 @@
         </is>
       </c>
       <c r="C77" s="5">
-        <f>LEN(L77)</f>
+        <f>LEN(M77)</f>
         <v/>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -4447,7 +4828,12 @@
           <t>Sickness on the wind, for everyone.</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr">
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>blight_wind</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>WAA</t>
         </is>
@@ -4465,7 +4851,7 @@
         </is>
       </c>
       <c r="C78" s="5">
-        <f>LEN(L78)</f>
+        <f>LEN(M78)</f>
         <v/>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -4498,7 +4884,12 @@
           <t>Step between the drops.</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>mistwalk</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>WAW</t>
         </is>
@@ -4516,7 +4907,7 @@
         </is>
       </c>
       <c r="C79" s="5">
-        <f>LEN(L79)</f>
+        <f>LEN(M79)</f>
         <v/>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -4541,7 +4932,7 @@
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Steal 1 element of your choice from the target (they go to your elements).</t>
+          <t>Steal 1 Essence of your choice from the target (they go to your bag).</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
@@ -4549,7 +4940,12 @@
           <t>The current takes what it likes and brings it to you.</t>
         </is>
       </c>
-      <c r="L79" s="2" t="inlineStr">
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>tide_thief</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>WAW</t>
         </is>
@@ -4558,7 +4954,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Geyser</t>
+          <t>Arcane Barrage</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -4567,12 +4963,12 @@
         </is>
       </c>
       <c r="C80" s="5">
-        <f>LEN(L80)</f>
+        <f>LEN(M80)</f>
         <v/>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -4592,15 +4988,20 @@
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>Expose 1 on all enemies.</t>
+          <t>Remove 3 random Essence from random enemies (the same enemy can be hit more than once).</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>Blown wide open.</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
+          <t>Three bolts, three guesses. Something will get hit.</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>arcane_barrage</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>WFA</t>
         </is>
@@ -4609,16 +5010,16 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Reforge</t>
+          <t>Geyser</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Water → Fire → Fire</t>
+          <t>Water → Fire → Air</t>
         </is>
       </c>
       <c r="C81" s="5">
-        <f>LEN(L81)</f>
+        <f>LEN(M81)</f>
         <v/>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -4628,48 +5029,53 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F81" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H81" s="5" t="n">
-        <v>0</v>
+      <c r="H81" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Turn the 2 leftmost Essence of the target into Fire.</t>
+          <t>Expose 1 on all enemies.</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>Its two leftmost elements become Fire.</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>WFF</t>
+          <t>Blown wide open.</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>geyser</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>WFA</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Steam Cloud</t>
+          <t>Reforge</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Water → Fire → Water</t>
+          <t>Water → Fire → Fire</t>
         </is>
       </c>
       <c r="C82" s="5">
-        <f>LEN(L82)</f>
+        <f>LEN(M82)</f>
         <v/>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -4679,14 +5085,14 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F82" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82" s="5" t="n">
         <v>0</v>
@@ -4694,33 +5100,38 @@
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>Weaken 1 on all enemies; gain 4 Shield.</t>
+          <t>Turn the 2 leftmost Essence of the target into Fire.</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>Nobody can see to aim.</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>WFW</t>
+          <t>Its two leftmost Essence become Fire.</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>reforge</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>WFF</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Purify</t>
+          <t>Steam Cloud</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Air</t>
+          <t>Water → Fire → Water</t>
         </is>
       </c>
       <c r="C83" s="5">
-        <f>LEN(L83)</f>
+        <f>LEN(M83)</f>
         <v/>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4733,45 +5144,50 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F83" s="5" t="n">
-        <v>0</v>
+      <c r="F83" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G83" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H83" s="6" t="n">
-        <v>1</v>
+      <c r="H83" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Remove all your debuffs (frozen elements, Blind, Confuse, Bleed, Silence).</t>
+          <t>Weaken 1 on all enemies; gain 4 Shield.</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Every curse washed away.</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>WWA</t>
+          <t>Nobody can see to aim.</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>steam_cloud</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>WFW</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Boiling Tide</t>
+          <t>Purify</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Fire</t>
+          <t>Water → Water → Air</t>
         </is>
       </c>
       <c r="C84" s="5">
-        <f>LEN(L84)</f>
+        <f>LEN(M84)</f>
         <v/>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -4781,39 +5197,44 @@
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="n">
-        <v>1</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G84" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H84" s="5" t="n">
-        <v>0</v>
+      <c r="H84" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Water from the target.</t>
+          <t>Remove all your debuffs (frozen Essence, Blind, Confuse, Bleed, Silence).</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Two of its waters boil away.</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>WWF</t>
+          <t>Every curse washed away.</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>purify</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>WWA</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Siren's Call</t>
+          <t>Boiling Tide</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -4822,7 +5243,7 @@
         </is>
       </c>
       <c r="C85" s="5">
-        <f>LEN(L85)</f>
+        <f>LEN(M85)</f>
         <v/>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -4847,15 +5268,20 @@
       <c r="I85" s="5" t="inlineStr"/>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Steal up to 2 Fire from the target (they go to your elements).</t>
+          <t>Remove up to 3 Water from the target.</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>A song so sweet the fire walks into the water.</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
+          <t>Two of its waters boil away.</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>boiling_tide</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>WWF</t>
         </is>
@@ -4864,16 +5290,16 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Glacier</t>
+          <t>Siren's Call</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Water</t>
+          <t>Water → Water → Fire</t>
         </is>
       </c>
       <c r="C86" s="5">
-        <f>LEN(L86)</f>
+        <f>LEN(M86)</f>
         <v/>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -4883,14 +5309,14 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>0</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H86" s="5" t="n">
         <v>0</v>
@@ -4898,24 +5324,29 @@
       <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>Freeze 1 on the target.</t>
+          <t>Steal up to 2 Fire from the target (they go to your bag).</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Frozen mid-swing.</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>WWW</t>
+          <t>A song so sweet the fire walks into the water.</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>sirens_call</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>WWF</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Rising Tide</t>
+          <t>Glacier</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -4924,7 +5355,7 @@
         </is>
       </c>
       <c r="C87" s="5">
-        <f>LEN(L87)</f>
+        <f>LEN(M87)</f>
         <v/>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -4949,15 +5380,20 @@
       <c r="I87" s="5" t="inlineStr"/>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: gain 4 Shield.</t>
+          <t>Freeze 1 on the target.</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>The water rises around you every turn.</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
+          <t>Frozen mid-swing.</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>glacier</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>WWW</t>
         </is>
@@ -4966,123 +5402,133 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Hurricane</t>
+          <t>Rising Tide</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Air → Air</t>
+          <t>Water → Water → Water</t>
         </is>
       </c>
       <c r="C88" s="5">
-        <f>LEN(L88)</f>
+        <f>LEN(M88)</f>
         <v/>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="6" t="n">
-        <v>4</v>
+      <c r="G88" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of all enemies.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: gain 4 Shield.</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>The whole row is torn apart.</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>AAAA</t>
+          <t>The water rises around you every turn.</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>rising_tide</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>WWW</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Storm Crown</t>
+          <t>Hurricane</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Air → Fire</t>
+          <t>Air → Air → Air → Air</t>
         </is>
       </c>
       <c r="C89" s="5">
-        <f>LEN(L89)</f>
+        <f>LEN(M89)</f>
         <v/>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="n">
-        <v>1</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G89" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: +2 conjured Air now.</t>
+          <t>Remove the 3 rightmost Essence of all enemies.</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>A conjured Wind every turn.</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>AAAF</t>
+          <t>The whole row is torn apart.</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>hurricane</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>AAAA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Long Chant</t>
+          <t>Storm Crown</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Water → Air</t>
+          <t>Air → Air → Air → Fire</t>
         </is>
       </c>
       <c r="C90" s="5">
-        <f>LEN(L90)</f>
+        <f>LEN(M90)</f>
         <v/>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -5090,11 +5536,11 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="8" t="n">
-        <v>1</v>
+      <c r="F90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>3</v>
@@ -5102,33 +5548,38 @@
       <c r="I90" s="5" t="inlineStr"/>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Your chant line gets +2 slots.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: +2 conjured Air now.</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Two more slots in your chant line.</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>AAWA</t>
+          <t>A conjured Wind every turn.</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>storm_crown</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>AAAF</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Misdirection</t>
+          <t>Long Chant</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Air → Water</t>
+          <t>Air → Air → Water → Air</t>
         </is>
       </c>
       <c r="C91" s="5">
-        <f>LEN(L91)</f>
+        <f>LEN(M91)</f>
         <v/>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -5138,48 +5589,53 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I91" s="5" t="inlineStr"/>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Redirect the intent of the target: its attacks hit the enemy you choose (it can be itself), and anything aimed at you fizzles; gain Aegis (1 hit).</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Your chant line gets +2 slots.</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Point its anger somewhere else. Anywhere else.</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>AWAW</t>
+          <t>Two more slots in your chant line.</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>long_chant</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>AAWA</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Eye of the Storm</t>
+          <t>Misdirection</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Fire → Air</t>
+          <t>Air → Water → Air → Water</t>
         </is>
       </c>
       <c r="C92" s="5">
-        <f>LEN(L92)</f>
+        <f>LEN(M92)</f>
         <v/>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -5192,11 +5648,11 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F92" s="7" t="n">
-        <v>1</v>
+      <c r="F92" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>2</v>
@@ -5204,38 +5660,43 @@
       <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>Freeze 2 on all enemies.</t>
+          <t>Redirect the intent of the target: its attacks hit the enemy you choose (it can be itself), and anything aimed at you fizzles; gain Aegis (1 hit).</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>For one moment, everything stops.</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>AWFA</t>
+          <t>Point its anger somewhere else. Anywhere else.</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>decoy</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>AWAW</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Phoenix Rite</t>
+          <t>Eye of the Storm</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Fire → Air → Fire → Air</t>
+          <t>Air → Water → Fire → Air</t>
         </is>
       </c>
       <c r="C93" s="5">
-        <f>LEN(L93)</f>
+        <f>LEN(M93)</f>
         <v/>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -5244,10 +5705,10 @@
         </is>
       </c>
       <c r="F93" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G93" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H93" s="6" t="n">
         <v>2</v>
@@ -5255,33 +5716,38 @@
       <c r="I93" s="5" t="inlineStr"/>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Gain Aegis (1 hit); heal 5.</t>
+          <t>Freeze 2 on all enemies.</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Rise from the next blow untouched.</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>FAFA</t>
+          <t>For one moment, everything stops.</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>eye_of_the_storm</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>AWFA</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Pyromancy</t>
+          <t>Phoenix Rite</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Air</t>
+          <t>Fire → Air → Fire → Air</t>
         </is>
       </c>
       <c r="C94" s="5">
-        <f>LEN(L94)</f>
+        <f>LEN(M94)</f>
         <v/>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -5291,53 +5757,58 @@
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F94" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Your spells that remove elements remove +1.</t>
+          <t>Gain Aegis (1 hit); heal 5.</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Your spells tear out one element more.</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>FFFA</t>
+          <t>Rise from the next blow untouched.</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>phoenix_rite</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>FAFA</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Meteor</t>
+          <t>Pyromancy</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Fire</t>
+          <t>Fire → Fire → Fire → Air</t>
         </is>
       </c>
       <c r="C95" s="5">
-        <f>LEN(L95)</f>
+        <f>LEN(M95)</f>
         <v/>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -5346,49 +5817,54 @@
         </is>
       </c>
       <c r="F95" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H95" s="5" t="n">
-        <v>0</v>
+      <c r="H95" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I95" s="5" t="inlineStr"/>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Remove the 5 rightmost Essence of the target.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Your spells that remove Essence remove +1.</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Very big, very hot.</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>FFFF</t>
+          <t>Your spells tear out one Essence more.</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>pyromancy</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>FFFA</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Thermal Burst</t>
+          <t>Meteor</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Water → Fire</t>
+          <t>Fire → Fire → Fire → Fire</t>
         </is>
       </c>
       <c r="C96" s="5">
-        <f>LEN(L96)</f>
+        <f>LEN(M96)</f>
         <v/>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -5397,10 +5873,10 @@
         </is>
       </c>
       <c r="F96" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G96" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>0</v>
@@ -5408,38 +5884,43 @@
       <c r="I96" s="5" t="inlineStr"/>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of 2 different enemies (you pick both).</t>
+          <t>Remove the 5 rightmost Essence of the target.</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Steam bursts two ways at once.</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>FFWF</t>
+          <t>Very big, very hot.</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>meteor</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>FFFF</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Steam Engine</t>
+          <t>Thermal Burst</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Fire → Water → Fire → Water</t>
+          <t>Fire → Fire → Water → Fire</t>
         </is>
       </c>
       <c r="C97" s="5">
-        <f>LEN(L97)</f>
+        <f>LEN(M97)</f>
         <v/>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -5448,10 +5929,10 @@
         </is>
       </c>
       <c r="F97" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G97" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" s="5" t="n">
         <v>0</v>
@@ -5459,84 +5940,94 @@
       <c r="I97" s="5" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Echo.</t>
+          <t>Remove the 2 leftmost Essence of 2 different enemies (you pick both).</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>The chant strikes again after your spells.</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>FWFW</t>
+          <t>Steam bursts two ways at once.</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>thermal_burst</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>FFWF</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Unshackle</t>
+          <t>Steam Engine</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Water → Air → Fire → Water</t>
+          <t>Fire → Water → Fire → Water</t>
         </is>
       </c>
       <c r="C98" s="5">
-        <f>LEN(L98)</f>
+        <f>LEN(M98)</f>
         <v/>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F98" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H98" s="6" t="n">
-        <v>1</v>
+      <c r="H98" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I98" s="5" t="inlineStr"/>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>Break one Lock on your spells.</t>
+          <t>Echo.</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Break one lock on your spells.</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
-        <is>
-          <t>WAFW</t>
+          <t>The chant strikes again after your spells.</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>steam_engine</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>FWFW</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Unshackle</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Water → Air → Water → Air</t>
+          <t>Water → Air → Fire → Water</t>
         </is>
       </c>
       <c r="C99" s="5">
-        <f>LEN(L99)</f>
+        <f>LEN(M99)</f>
         <v/>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -5549,138 +6040,153 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F99" s="5" t="n">
-        <v>0</v>
+      <c r="F99" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G99" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" s="5" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Heal 7; remove all your debuffs (frozen elements, Blind, Confuse, Bleed, Silence); gain 5 Shield.</t>
+          <t>Break one Lock on your spells.</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Light over still water.</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>WAWA</t>
+          <t>Break one lock on your spells.</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>unshackle</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>WAFW</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Open Grimoire</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Water → Fire → Water → Air</t>
+          <t>Water → Air → Water → Air</t>
         </is>
       </c>
       <c r="C100" s="5">
-        <f>LEN(L100)</f>
+        <f>LEN(M100)</f>
         <v/>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="n">
-        <v>1</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H100" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100" s="5" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): Add 2 random spells from your spellbook to your active row for this fight.</t>
+          <t>Heal 7; remove all your debuffs (frozen Essence, Blind, Confuse, Bleed, Silence); gain 5 Shield.</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Two more pages fall open.</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>WFWA</t>
+          <t>Light over still water.</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>aurora</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>WAWA</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Stillness</t>
+          <t>Open Grimoire</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Water → Water</t>
+          <t>Water → Fire → Water → Air</t>
         </is>
       </c>
       <c r="C101" s="5">
-        <f>LEN(L101)</f>
+        <f>LEN(M101)</f>
         <v/>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>0</v>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G101" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I101" s="5" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): All enemies deal 25% less damage for the rest of the fight.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): Add 2 random spells from your spellbook to your active row for this fight.</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Every enemy deals 25% less damage, for good.</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>WWWW</t>
+          <t>Two more pages fall open.</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>grimoire</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>WFWA</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Tidal Wave</t>
+          <t>Stillness</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -5689,17 +6195,17 @@
         </is>
       </c>
       <c r="C102" s="5">
-        <f>LEN(L102)</f>
+        <f>LEN(M102)</f>
         <v/>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
@@ -5714,15 +6220,20 @@
       <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of all enemies; Weaken 3 on all enemies.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): All enemies deal 25% less damage for the rest of the fight.</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Knock the leftmost off everything.</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
+          <t>Every enemy deals 25% less damage, for good.</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>stillness</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
         <is>
           <t>WWWW</t>
         </is>
@@ -5731,21 +6242,21 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Firestorm</t>
+          <t>Tidal Wave</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Any → Fire → Air</t>
+          <t>Water → Water → Water → Water</t>
         </is>
       </c>
       <c r="C103" s="5">
-        <f>LEN(L103)</f>
+        <f>LEN(M103)</f>
         <v/>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -5753,50 +6264,55 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F103" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="6" t="n">
-        <v>2</v>
+      <c r="F103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I103" s="5" t="inlineStr"/>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Burn 3 on all enemies.</t>
+          <t>Remove the 2 leftmost Essence of all enemies; Weaken 3 on all enemies.</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Burning rain on all of them.</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>AF?FA</t>
+          <t>Knock the leftmost off everything.</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>tidal_wave</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>WWWW</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>Convergence</t>
+          <t>Firestorm</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Water → Fire → Air</t>
+          <t>Air → Fire → Any → Fire → Air</t>
         </is>
       </c>
       <c r="C104" s="5">
-        <f>LEN(L104)</f>
+        <f>LEN(M104)</f>
         <v/>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -5807,8 +6323,8 @@
       <c r="F104" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G104" s="8" t="n">
-        <v>1</v>
+      <c r="G104" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H104" s="6" t="n">
         <v>2</v>
@@ -5816,33 +6332,38 @@
       <c r="I104" s="5" t="inlineStr"/>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>Echo; Amplify 1.</t>
+          <t>Burn 3 on all enemies.</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>All three elements sing as one.</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>AFWFA</t>
+          <t>Burning rain on all of them.</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>firestorm</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>AF?FA</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Triune Chant</t>
+          <t>Convergence</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Fire → Air → Water → Air → Fire</t>
+          <t>Air → Fire → Water → Fire → Air</t>
         </is>
       </c>
       <c r="C105" s="5">
-        <f>LEN(L105)</f>
+        <f>LEN(M105)</f>
         <v/>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -5852,7 +6373,7 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F105" s="7" t="n">
@@ -5867,33 +6388,38 @@
       <c r="I105" s="5" t="inlineStr"/>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>Duplicate 2.</t>
+          <t>Echo; Amplify 1.</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Three voices, one word.</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>FAWAF</t>
+          <t>All three Essence sing as one.</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>convergence</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>AFWFA</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Avatar of Flame</t>
+          <t>Triune Chant</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Fire → Air</t>
+          <t>Fire → Air → Water → Air → Fire</t>
         </is>
       </c>
       <c r="C106" s="5">
-        <f>LEN(L106)</f>
+        <f>LEN(M106)</f>
         <v/>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -5903,48 +6429,53 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F106" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G106" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H106" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I106" s="5" t="inlineStr"/>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): All enemies your Release hits get Burn 1.</t>
+          <t>Duplicate 2.</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Every enemy your chant touches catches fire.</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>FFFFA</t>
+          <t>Three voices, one word.</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>triune_chant</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>FAWAF</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Supernova</t>
+          <t>Avatar of Flame</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Fire → Fire</t>
+          <t>Fire → Fire → Fire → Fire → Air</t>
         </is>
       </c>
       <c r="C107" s="5">
-        <f>LEN(L107)</f>
+        <f>LEN(M107)</f>
         <v/>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -5958,44 +6489,49 @@
         </is>
       </c>
       <c r="F107" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H107" s="5" t="n">
-        <v>0</v>
+      <c r="H107" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I107" s="5" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of all enemies; Burn 4 on all enemies.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): All enemies your Release hits get Burn 1.</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>A star dies on the battlefield.</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr">
-        <is>
-          <t>FFFFF</t>
+          <t>Every enemy your chant touches catches fire.</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>avatar_of_flame</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>FFFFA</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>World Tree's Blessing</t>
+          <t>Supernova</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Water → Air → Water → Air → Water</t>
+          <t>Fire → Fire → Fire → Fire → Fire</t>
         </is>
       </c>
       <c r="C108" s="5">
-        <f>LEN(L108)</f>
+        <f>LEN(M108)</f>
         <v/>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -6005,48 +6541,53 @@
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H108" s="6" t="n">
-        <v>2</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I108" s="5" t="inlineStr"/>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: heal 7; +3 random elements now.</t>
+          <t>Remove the 3 rightmost Essence of all enemies; Burn 4 on all enemies.</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>The Last Tree gives back, every turn.</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr">
-        <is>
-          <t>WAWAW</t>
+          <t>A star dies on the battlefield.</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>supernova</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>FFFFF</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Maelstrom Grasp</t>
+          <t>World Tree's Blessing</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Air → Water → Water</t>
+          <t>Water → Air → Water → Air → Water</t>
         </is>
       </c>
       <c r="C109" s="5">
-        <f>LEN(L109)</f>
+        <f>LEN(M109)</f>
         <v/>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -6056,48 +6597,53 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I109" s="5" t="inlineStr"/>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>Steal 2 elements of your choice from the target (they go to your elements); gain 4 Shield.</t>
+          <t>**Power** (leaves your active row for the rest of the fight): At the start of each of your turns: heal 7; +3 random Essence now.</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>The whirlpool swallows their strength and spits it out at your feet.</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>WWAWW</t>
+          <t>The Last Tree gives back, every turn.</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>world_tree_blessing</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>WAWAW</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Deluge</t>
+          <t>Maelstrom Grasp</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Water → Water → Water</t>
+          <t>Water → Water → Air → Water → Water</t>
         </is>
       </c>
       <c r="C110" s="5">
-        <f>LEN(L110)</f>
+        <f>LEN(M110)</f>
         <v/>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -6107,48 +6653,53 @@
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H110" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I110" s="5" t="inlineStr"/>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>Gain 14 Shield; heal 10; Freeze 2 on all enemies.</t>
+          <t>Steal 2 Essence of your choice from the target (they go to your bag); gain 4 Shield.</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>The flood answers.</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr">
-        <is>
-          <t>WWWWW</t>
+          <t>The whirlpool swallows their strength and spits it out at your feet.</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>maelstrom_grasp</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>WWAWW</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Annihilate</t>
+          <t>Deluge</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Fire → Water → Air → Any → Water → Fire</t>
+          <t>Water → Water → Water → Water → Water</t>
         </is>
       </c>
       <c r="C111" s="5">
-        <f>LEN(L111)</f>
+        <f>LEN(M111)</f>
         <v/>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -6158,37 +6709,98 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="n">
-        <v>2</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G111" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H111" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I111" s="5" t="inlineStr"/>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>Annihilate 1 element on all enemies (you choose Fire, Water or Air: every Essence of it is removed).</t>
+          <t>Gain 14 Shield; heal 10; Freeze 2 on all enemies.</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
+          <t>The flood answers.</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>deluge</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>WWWWW</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Annihilate</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Fire → Water → Air → Any → Water → Fire</t>
+        </is>
+      </c>
+      <c r="C112" s="5">
+        <f>LEN(M112)</f>
+        <v/>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G112" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="5" t="inlineStr"/>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>Annihilate 1 kind of Essence on all enemies (you choose Fire, Water or Air: every Essence of it is removed).</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
           <t>Pick one. It stops existing.</t>
         </is>
       </c>
-      <c r="L111" s="2" t="inlineStr">
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>annihilate</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
         <is>
           <t>FWA?WF</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K111"/>
+  <autoFilter ref="A1:L112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/spells.xlsx
+++ b/docs/spells.xlsx
@@ -50,7 +50,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -60,11 +60,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004A5A3A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -114,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -130,7 +125,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -138,14 +133,11 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -650,7 +642,7 @@
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Infuse an Air into the chant.</t>
+          <t>Infuse 1 Air.</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -663,11 +655,7 @@
           <t>borrowed_breath</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t>pattern (was A), rarity (was common), effect</t>
-        </is>
-      </c>
+      <c r="N2" s="4" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -701,7 +689,7 @@
       <c r="G3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -712,7 +700,7 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Gain 2 Thorns this turn.</t>
+          <t>Thorns 2 this turn.</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -763,7 +751,7 @@
       <c r="G4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -787,11 +775,7 @@
           <t>zephyr</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>renamed (was Zephyr), effect</t>
-        </is>
-      </c>
+      <c r="N4" s="4" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>A</t>
@@ -829,7 +813,7 @@
       <c r="G5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -840,7 +824,7 @@
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of an enemy. Next turn you gain the removed Essence (Conjured).</t>
+          <t>Remove an enemy's 2 leftmost Essence; get them next turn (Conjured).</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -891,7 +875,7 @@
       <c r="G6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -953,7 +937,7 @@
       <c r="G7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1015,7 +999,7 @@
       <c r="G8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1041,11 +1025,7 @@
           <t>taint</t>
         </is>
       </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>cooldown</t>
-        </is>
-      </c>
+      <c r="N8" s="4" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>A</t>
@@ -1083,7 +1063,7 @@
       <c r="G9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1094,7 +1074,7 @@
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Pick 1 of an enemy's Essence and move it to any spot in that row.</t>
+          <t>Move 1 of an enemy's Essence anywhere in its row.</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1145,7 +1125,7 @@
       <c r="G10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1207,7 +1187,7 @@
       <c r="G11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1218,7 +1198,7 @@
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Infuse a random Essence into the chant.</t>
+          <t>Infuse 1 Random.</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1231,11 +1211,7 @@
           <t>wisp</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N11" s="4" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>A</t>
@@ -1267,7 +1243,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="5" t="n">
@@ -1329,7 +1305,7 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
@@ -1391,7 +1367,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="5" t="n">
@@ -1421,11 +1397,7 @@
           <t>cinder</t>
         </is>
       </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>renamed (was Cinder), effect</t>
-        </is>
-      </c>
+      <c r="N14" s="4" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>F</t>
@@ -1457,7 +1429,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
@@ -1519,7 +1491,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="5" t="n">
@@ -1581,7 +1553,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
@@ -1598,7 +1570,7 @@
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of all enemies. Burn 4 on all enemies.</t>
+          <t>Remove all enemies' 3 rightmost Essence. Burn 4 on all enemies.</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1643,7 +1615,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="5" t="n">
@@ -1660,7 +1632,7 @@
       <c r="J18" s="5" t="n"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of an enemy (only if it has 4 or more Essence).</t>
+          <t>Remove an enemy's rightmost Essence (if it has 4+).</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1705,7 +1677,7 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
@@ -1767,7 +1739,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="5" t="n">
@@ -1832,7 +1804,7 @@
       <c r="F21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
@@ -1894,7 +1866,7 @@
       <c r="F22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="5" t="n">
@@ -1956,7 +1928,7 @@
       <c r="F23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="5" t="n">
@@ -1970,7 +1942,7 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Break all Armour on an enemy.</t>
+          <t>Break an enemy's Armour.</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2018,7 +1990,7 @@
       <c r="F24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="5" t="n">
@@ -2080,7 +2052,7 @@
       <c r="F25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="5" t="n">
@@ -2142,7 +2114,7 @@
       <c r="F26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="5" t="n">
@@ -2204,7 +2176,7 @@
       <c r="F27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="5" t="n">
@@ -2266,7 +2238,7 @@
       <c r="F28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="5" t="n">
@@ -2280,7 +2252,7 @@
       <c r="J28" s="5" t="n"/>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Change the rightmost Essence of an enemy into Water.</t>
+          <t>Turn an enemy's rightmost Essence into Water.</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2328,7 +2300,7 @@
       <c r="F29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="5" t="n">
@@ -2342,7 +2314,7 @@
       <c r="J29" s="5" t="n"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of a random enemy.</t>
+          <t>Remove a random enemy's rightmost Essence.</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2390,7 +2362,7 @@
       <c r="F30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="5" t="n">
@@ -2455,7 +2427,7 @@
       <c r="G31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="H31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -2517,7 +2489,7 @@
       <c r="G32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H32" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2579,7 +2551,7 @@
       <c r="G33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="7" t="n">
+      <c r="H33" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -2590,7 +2562,7 @@
       <c r="J33" s="5" t="n"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of all enemies (only if it has 4 or more Essence).</t>
+          <t>Remove all enemies' rightmost Essence (if it has 4+).</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2641,7 +2613,7 @@
       <c r="G34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="H34" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -2652,7 +2624,7 @@
       <c r="J34" s="5" t="n"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Gain 3 Shield. Gain 1 Thorns this turn.</t>
+          <t>Gain 3 Shield. Thorns 1 this turn.</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2703,7 +2675,7 @@
       <c r="G35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="7" t="n">
+      <c r="H35" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -2729,11 +2701,7 @@
           <t>miasma</t>
         </is>
       </c>
-      <c r="N35" s="6" t="inlineStr">
-        <is>
-          <t>effect, cooldown</t>
-        </is>
-      </c>
+      <c r="N35" s="4" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t>AA</t>
@@ -2771,7 +2739,7 @@
       <c r="G36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="H36" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -2833,7 +2801,7 @@
       <c r="G37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="7" t="n">
+      <c r="H37" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -2844,7 +2812,7 @@
       <c r="J37" s="5" t="n"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>Gain 1 random Essence next turn.</t>
+          <t>Gain 1 Random next turn.</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2895,7 +2863,7 @@
       <c r="G38" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H38" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -2906,7 +2874,7 @@
       <c r="J38" s="5" t="n"/>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Steal 1 Essence of your choice from an enemy.</t>
+          <t>Steal 1 Essence from an enemy.</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2957,7 +2925,7 @@
       <c r="G39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="7" t="n">
+      <c r="H39" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -2968,7 +2936,7 @@
       <c r="J39" s="5" t="n"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>Move the leftmost Essence of an enemy to the right end of its row.</t>
+          <t>Move an enemy's leftmost Essence to its right end.</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3013,13 +2981,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -3030,7 +2998,7 @@
       <c r="J40" s="5" t="n"/>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>Change 2 of your unused Essence into Fire.</t>
+          <t>Turn 2 unused Essence into Fire.</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -3075,13 +3043,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="7" t="n">
+      <c r="H41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -3137,13 +3105,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="7" t="n">
+      <c r="H42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -3154,7 +3122,7 @@
       <c r="J42" s="5" t="n"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>Double the Burn on an enemy.</t>
+          <t>Double an enemy's Burn.</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -3199,13 +3167,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="F43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="7" t="n">
+      <c r="H43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -3261,13 +3229,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -3323,13 +3291,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="F45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="7" t="n">
+      <c r="H45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -3353,11 +3321,7 @@
           <t>ember_gust</t>
         </is>
       </c>
-      <c r="N45" s="6" t="inlineStr">
-        <is>
-          <t>renamed (was Ember Gust), effect</t>
-        </is>
-      </c>
+      <c r="N45" s="4" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
           <t>AF</t>
@@ -3389,13 +3353,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="H46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -3406,7 +3370,7 @@
       <c r="J46" s="5" t="n"/>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>Infuse a Water into the chant.</t>
+          <t>Infuse 1 Water.</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -3451,13 +3415,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F47" s="8" t="n">
+      <c r="F47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="7" t="n">
+      <c r="H47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -3468,7 +3432,7 @@
       <c r="J47" s="5" t="n"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of a random enemy.</t>
+          <t>Remove a random enemy's rightmost Essence.</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -3516,10 +3480,10 @@
       <c r="F48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="7" t="n">
+      <c r="G48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -3578,10 +3542,10 @@
       <c r="F49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="7" t="n">
+      <c r="G49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -3640,10 +3604,10 @@
       <c r="F50" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="7" t="n">
+      <c r="G50" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -3702,10 +3666,10 @@
       <c r="F51" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G51" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="7" t="n">
+      <c r="G51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -3729,11 +3693,7 @@
           <t>thorn_dart</t>
         </is>
       </c>
-      <c r="N51" s="6" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
+      <c r="N51" s="4" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
           <t>AW</t>
@@ -3768,10 +3728,10 @@
       <c r="F52" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G52" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="7" t="n">
+      <c r="G52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -3782,7 +3742,7 @@
       <c r="J52" s="5" t="n"/>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>Cure Silence on all your spells.</t>
+          <t>Cure Silence.</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3827,7 +3787,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n">
+      <c r="F53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="5" t="n">
@@ -3889,7 +3849,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F54" s="8" t="n">
+      <c r="F54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="5" t="n">
@@ -3951,13 +3911,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F55" s="8" t="n">
+      <c r="F55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="7" t="n">
+      <c r="H55" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I55" s="5" t="inlineStr">
@@ -3968,7 +3928,7 @@
       <c r="J55" s="5" t="n"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Burn 1 on all enemies. Double the Burn on all enemies.</t>
+          <t>Burn 1 on all enemies. Double all enemies' Burn.</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -4013,13 +3973,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F56" s="8" t="n">
+      <c r="F56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="7" t="n">
+      <c r="H56" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -4030,7 +3990,7 @@
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of an enemy. If it has Burn, remove 1 more.</t>
+          <t>Remove an enemy's rightmost Essence. +1 if it has Burn.</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -4075,13 +4035,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F57" s="8" t="n">
+      <c r="F57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="7" t="n">
+      <c r="H57" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -4092,7 +4052,7 @@
       <c r="J57" s="5" t="n"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>Infuse 2 Fire into the chant.</t>
+          <t>Infuse 2 Fire.</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -4105,11 +4065,7 @@
           <t>conjure_flame</t>
         </is>
       </c>
-      <c r="N57" s="6" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N57" s="4" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>FA</t>
@@ -4141,13 +4097,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F58" s="8" t="n">
+      <c r="F58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="7" t="n">
+      <c r="H58" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -4203,13 +4159,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n">
+      <c r="F59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="7" t="n">
+      <c r="H59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I59" s="5" t="inlineStr">
@@ -4265,13 +4221,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F60" s="8" t="n">
+      <c r="F60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="7" t="n">
+      <c r="H60" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -4327,13 +4283,13 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F61" s="8" t="n">
+      <c r="F61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="7" t="n">
+      <c r="H61" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I61" s="5" t="inlineStr">
@@ -4344,7 +4300,7 @@
       <c r="J61" s="5" t="n"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>Gain 1 Thorns for the rest of the fight.</t>
+          <t>Thorns 1 all fight.</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -4389,13 +4345,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n">
+      <c r="F62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="7" t="n">
+      <c r="H62" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I62" s="5" t="inlineStr">
@@ -4451,13 +4407,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F63" s="8" t="n">
+      <c r="F63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="7" t="n">
+      <c r="H63" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I63" s="5" t="inlineStr">
@@ -4513,7 +4469,7 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F64" s="8" t="n">
+      <c r="F64" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G64" s="5" t="n">
@@ -4530,7 +4486,7 @@
       <c r="J64" s="5" t="n"/>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>Lose 3 of your HP. Gain 4 random Essence.</t>
+          <t>Lose 3 HP. Gain 4 Random.</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -4575,7 +4531,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F65" s="8" t="n">
+      <c r="F65" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G65" s="5" t="n">
@@ -4592,7 +4548,7 @@
       <c r="J65" s="5" t="n"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 rightmost Essence of a random enemy.</t>
+          <t>Remove a random enemy's 2 rightmost Essence.</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -4637,7 +4593,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F66" s="8" t="n">
+      <c r="F66" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G66" s="5" t="n">
@@ -4667,11 +4623,7 @@
           <t>searing_brand</t>
         </is>
       </c>
-      <c r="N66" s="6" t="inlineStr">
-        <is>
-          <t>renamed (was Searing Brand), effect</t>
-        </is>
-      </c>
+      <c r="N66" s="4" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
           <t>FF</t>
@@ -4703,7 +4655,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F67" s="8" t="n">
+      <c r="F67" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G67" s="5" t="n">
@@ -4720,7 +4672,7 @@
       <c r="J67" s="5" t="n"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of an enemy.</t>
+          <t>Remove an enemy's rightmost Essence.</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4765,7 +4717,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F68" s="8" t="n">
+      <c r="F68" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G68" s="5" t="n">
@@ -4827,7 +4779,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F69" s="8" t="n">
+      <c r="F69" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G69" s="5" t="n">
@@ -4844,7 +4796,7 @@
       <c r="J69" s="5" t="n"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>Remove the leftmost Essence of an enemy.</t>
+          <t>Remove an enemy's leftmost Essence.</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4889,7 +4841,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F70" s="8" t="n">
+      <c r="F70" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G70" s="5" t="n">
@@ -4906,7 +4858,7 @@
       <c r="J70" s="5" t="n"/>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>Execute an enemy with 3 Essence or less (not bosses).</t>
+          <t>Execute an enemy with 3 or less Essence.</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4951,7 +4903,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F71" s="8" t="n">
+      <c r="F71" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G71" s="5" t="n">
@@ -5013,7 +4965,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F72" s="8" t="n">
+      <c r="F72" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G72" s="5" t="n">
@@ -5075,10 +5027,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F73" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="9" t="n">
+      <c r="F73" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="5" t="n">
@@ -5092,7 +5044,7 @@
       <c r="J73" s="5" t="n"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>Change the rightmost Essence of an enemy into Fire.</t>
+          <t>Turn an enemy's rightmost Essence into Fire.</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -5137,10 +5089,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F74" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="9" t="n">
+      <c r="F74" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="5" t="n">
@@ -5154,7 +5106,7 @@
       <c r="J74" s="5" t="n"/>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>Infuse an Air into the chant.</t>
+          <t>Infuse 1 Air.</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -5199,10 +5151,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F75" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="9" t="n">
+      <c r="F75" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="5" t="n">
@@ -5216,7 +5168,7 @@
       <c r="J75" s="5" t="n"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>An enemy can never Mend.</t>
+          <t>An enemy can't Mend.</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -5261,10 +5213,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F76" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="9" t="n">
+      <c r="F76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="5" t="n">
@@ -5323,10 +5275,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F77" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="9" t="n">
+      <c r="F77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="5" t="n">
@@ -5385,10 +5337,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F78" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="9" t="n">
+      <c r="F78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="5" t="n">
@@ -5402,7 +5354,7 @@
       <c r="J78" s="5" t="n"/>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>Repeat the last spell you cast this turn.</t>
+          <t>Repeat your last spell this turn.</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -5447,10 +5399,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F79" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="9" t="n">
+      <c r="F79" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="5" t="n">
@@ -5464,7 +5416,7 @@
       <c r="J79" s="5" t="n"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of an enemy. Weaken 1 on an enemy.</t>
+          <t>Remove an enemy's rightmost Essence. Weaken 1 on an enemy.</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -5509,10 +5461,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F80" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="9" t="n">
+      <c r="F80" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="5" t="n">
@@ -5541,11 +5493,7 @@
           <t>scalding_rain</t>
         </is>
       </c>
-      <c r="N80" s="6" t="inlineStr">
-        <is>
-          <t>cooldown</t>
-        </is>
-      </c>
+      <c r="N80" s="4" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>FW</t>
@@ -5577,10 +5525,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="9" t="n">
+      <c r="F81" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H81" s="5" t="n">
@@ -5642,10 +5590,10 @@
       <c r="F82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="7" t="n">
+      <c r="G82" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I82" s="5" t="inlineStr">
@@ -5704,10 +5652,10 @@
       <c r="F83" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G83" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="7" t="n">
+      <c r="G83" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I83" s="5" t="inlineStr">
@@ -5718,7 +5666,7 @@
       <c r="J83" s="5" t="n"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Infuse a random Essence into the chant.</t>
+          <t>Infuse 1 Random.</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -5731,11 +5679,7 @@
           <t>mist_step</t>
         </is>
       </c>
-      <c r="N83" s="6" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N83" s="4" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
           <t>WA</t>
@@ -5770,10 +5714,10 @@
       <c r="F84" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G84" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" s="7" t="n">
+      <c r="G84" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I84" s="5" t="inlineStr">
@@ -5784,7 +5728,7 @@
       <c r="J84" s="5" t="n"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>You become Ethereal this turn.</t>
+          <t>Become Ethereal this turn.</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -5832,10 +5776,10 @@
       <c r="F85" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G85" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="7" t="n">
+      <c r="G85" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I85" s="5" t="inlineStr">
@@ -5846,7 +5790,7 @@
       <c r="J85" s="5" t="n"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Change the rightmost Essence of an enemy into Water.</t>
+          <t>Turn an enemy's rightmost Essence into Water.</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -5894,10 +5838,10 @@
       <c r="F86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="7" t="n">
+      <c r="G86" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I86" s="5" t="inlineStr">
@@ -5908,7 +5852,7 @@
       <c r="J86" s="5" t="n"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Pick 1 of an enemy's Essence and move it to any spot in that row. Weaken 1 on an enemy.</t>
+          <t>Move 1 of an enemy's Essence anywhere in its row. Weaken 1 on an enemy.</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -5956,10 +5900,10 @@
       <c r="F87" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G87" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" s="7" t="n">
+      <c r="G87" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I87" s="5" t="inlineStr">
@@ -6018,10 +5962,10 @@
       <c r="F88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="7" t="n">
+      <c r="G88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I88" s="5" t="inlineStr">
@@ -6032,7 +5976,7 @@
       <c r="J88" s="5" t="n"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>Infuse a Fire into the chant.</t>
+          <t>Infuse 1 Fire.</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -6080,10 +6024,10 @@
       <c r="F89" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G89" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" s="7" t="n">
+      <c r="G89" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I89" s="5" t="inlineStr">
@@ -6107,11 +6051,7 @@
           <t>spray</t>
         </is>
       </c>
-      <c r="N89" s="6" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N89" s="4" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
           <t>WA</t>
@@ -6146,10 +6086,10 @@
       <c r="F90" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G90" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" s="7" t="n">
+      <c r="G90" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I90" s="5" t="inlineStr">
@@ -6160,7 +6100,7 @@
       <c r="J90" s="5" t="n"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Pick 2 of an enemy's Essence, one at a time, and move each to any spot in that row.</t>
+          <t>Move 2 of an enemy's Essence anywhere in its row.</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -6208,10 +6148,10 @@
       <c r="F91" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G91" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" s="7" t="n">
+      <c r="G91" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I91" s="5" t="inlineStr">
@@ -6267,10 +6207,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F92" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="9" t="n">
+      <c r="F92" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H92" s="5" t="n">
@@ -6284,7 +6224,7 @@
       <c r="J92" s="5" t="n"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Add a Water at the leftmost end of an enemy's Essence.</t>
+          <t>Add a Water to the left end of an enemy's row.</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -6329,10 +6269,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F93" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="9" t="n">
+      <c r="F93" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H93" s="5" t="n">
@@ -6391,10 +6331,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F94" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="9" t="n">
+      <c r="F94" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H94" s="5" t="n">
@@ -6453,10 +6393,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F95" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="9" t="n">
+      <c r="F95" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H95" s="5" t="n">
@@ -6515,10 +6455,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F96" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="9" t="n">
+      <c r="F96" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H96" s="5" t="n">
@@ -6547,11 +6487,7 @@
           <t>steam_vent</t>
         </is>
       </c>
-      <c r="N96" s="6" t="inlineStr">
-        <is>
-          <t>effect, cooldown</t>
-        </is>
-      </c>
+      <c r="N96" s="4" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>WF</t>
@@ -6583,10 +6519,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F97" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="9" t="n">
+      <c r="F97" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="5" t="n">
@@ -6648,7 +6584,7 @@
       <c r="F98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G98" s="9" t="n">
+      <c r="G98" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H98" s="5" t="n">
@@ -6677,11 +6613,7 @@
           <t>brine</t>
         </is>
       </c>
-      <c r="N98" s="6" t="inlineStr">
-        <is>
-          <t>effect, cooldown</t>
-        </is>
-      </c>
+      <c r="N98" s="4" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
           <t>WW</t>
@@ -6716,7 +6648,7 @@
       <c r="F99" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G99" s="9" t="n">
+      <c r="G99" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H99" s="5" t="n">
@@ -6778,7 +6710,7 @@
       <c r="F100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G100" s="9" t="n">
+      <c r="G100" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H100" s="5" t="n">
@@ -6840,7 +6772,7 @@
       <c r="F101" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G101" s="9" t="n">
+      <c r="G101" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H101" s="5" t="n">
@@ -6867,11 +6799,7 @@
           <t>soak</t>
         </is>
       </c>
-      <c r="N101" s="6" t="inlineStr">
-        <is>
-          <t>renamed (was Soak), effect</t>
-        </is>
-      </c>
+      <c r="N101" s="4" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
           <t>WW</t>
@@ -6906,7 +6834,7 @@
       <c r="F102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G102" s="9" t="n">
+      <c r="G102" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H102" s="5" t="n">
@@ -6920,7 +6848,7 @@
       <c r="J102" s="5" t="n"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Infuse 2 Water into the chant.</t>
+          <t>Infuse 2 Water.</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -6933,11 +6861,7 @@
           <t>summon_rain</t>
         </is>
       </c>
-      <c r="N102" s="6" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N102" s="4" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
           <t>WW</t>
@@ -6972,7 +6896,7 @@
       <c r="F103" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="9" t="n">
+      <c r="G103" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H103" s="5" t="n">
@@ -7034,7 +6958,7 @@
       <c r="F104" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G104" s="9" t="n">
+      <c r="G104" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H104" s="5" t="n">
@@ -7048,7 +6972,7 @@
       <c r="J104" s="5" t="n"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Gain 3 Thorns this turn.</t>
+          <t>Thorns 3 this turn.</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -7096,7 +7020,7 @@
       <c r="F105" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G105" s="9" t="n">
+      <c r="G105" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H105" s="5" t="n">
@@ -7110,7 +7034,7 @@
       <c r="J105" s="5" t="n"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of an enemy. Next turn you gain the removed Essence (Conjured).</t>
+          <t>Remove an enemy's 2 leftmost Essence; get them next turn (Conjured).</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -7158,7 +7082,7 @@
       <c r="F106" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G106" s="9" t="n">
+      <c r="G106" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H106" s="5" t="n">
@@ -7223,7 +7147,7 @@
       <c r="G107" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H107" s="7" t="n">
+      <c r="H107" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I107" s="5" t="inlineStr">
@@ -7285,7 +7209,7 @@
       <c r="G108" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H108" s="7" t="n">
+      <c r="H108" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I108" s="5" t="inlineStr">
@@ -7296,7 +7220,7 @@
       <c r="J108" s="5" t="n"/>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Infuse 2 Water into the chant.</t>
+          <t>Infuse 2 Water.</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -7309,11 +7233,7 @@
           <t>tidecaller</t>
         </is>
       </c>
-      <c r="N108" s="6" t="inlineStr">
-        <is>
-          <t>pattern (was W?), effect</t>
-        </is>
-      </c>
+      <c r="N108" s="4" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
           <t>A?A</t>
@@ -7351,7 +7271,7 @@
       <c r="G109" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H109" s="7" t="n">
+      <c r="H109" s="6" t="n">
         <v>3</v>
       </c>
       <c r="I109" s="5" t="inlineStr">
@@ -7375,11 +7295,7 @@
           <t>sky_lance</t>
         </is>
       </c>
-      <c r="N109" s="6" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N109" s="4" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7417,7 +7333,7 @@
       <c r="G110" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H110" s="7" t="n">
+      <c r="H110" s="6" t="n">
         <v>3</v>
       </c>
       <c r="I110" s="5" t="inlineStr">
@@ -7428,7 +7344,7 @@
       <c r="J110" s="5" t="n"/>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>Gain 2 random Essence next turn. Rearrange 1.</t>
+          <t>Gain 2 Random next turn. Rearrange 1.</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
@@ -7479,7 +7395,7 @@
       <c r="G111" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="7" t="n">
+      <c r="H111" s="6" t="n">
         <v>3</v>
       </c>
       <c r="I111" s="5" t="inlineStr">
@@ -7490,7 +7406,7 @@
       <c r="J111" s="5" t="n"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>At the start of each of your turns: gain 2 random Essence.</t>
+          <t>Each turn: gain 2 Random.</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -7535,13 +7451,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F112" s="8" t="n">
+      <c r="F112" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H112" s="7" t="n">
+      <c r="H112" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I112" s="5" t="inlineStr">
@@ -7552,7 +7468,7 @@
       <c r="J112" s="5" t="n"/>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>Pick 2 of an enemy's Essence, one at a time, and move each to any spot in that row.</t>
+          <t>Move 2 of an enemy's Essence anywhere in its row.</t>
         </is>
       </c>
       <c r="L112" s="4" t="inlineStr">
@@ -7597,13 +7513,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F113" s="8" t="n">
+      <c r="F113" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="7" t="n">
+      <c r="H113" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I113" s="5" t="inlineStr">
@@ -7614,7 +7530,7 @@
       <c r="J113" s="5" t="n"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Air from an enemy's Essence.</t>
+          <t>Remove up to 3 Air from an enemy.</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -7659,13 +7575,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F114" s="8" t="n">
+      <c r="F114" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="7" t="n">
+      <c r="H114" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I114" s="5" t="inlineStr">
@@ -7689,11 +7605,7 @@
           <t>thunderhead</t>
         </is>
       </c>
-      <c r="N114" s="6" t="inlineStr">
-        <is>
-          <t>renamed (was Thunderhead), rarity (was rare), effect</t>
-        </is>
-      </c>
+      <c r="N114" s="4" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr">
         <is>
           <t>AAF</t>
@@ -7725,13 +7637,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F115" s="8" t="n">
+      <c r="F115" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="7" t="n">
+      <c r="H115" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I115" s="5" t="inlineStr">
@@ -7742,7 +7654,7 @@
       <c r="J115" s="5" t="n"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>All enemies your Release hits get Poison 1.</t>
+          <t>Your Release puts Poison 1 on what it hits.</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -7790,10 +7702,10 @@
       <c r="F116" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G116" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H116" s="7" t="n">
+      <c r="G116" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I116" s="5" t="inlineStr">
@@ -7817,11 +7729,7 @@
           <t>mistral</t>
         </is>
       </c>
-      <c r="N116" s="6" t="inlineStr">
-        <is>
-          <t>renamed (was Mistral), effect</t>
-        </is>
-      </c>
+      <c r="N116" s="4" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr">
         <is>
           <t>AAW</t>
@@ -7853,13 +7761,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F117" s="8" t="n">
+      <c r="F117" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H117" s="7" t="n">
+      <c r="H117" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I117" s="5" t="inlineStr">
@@ -7883,11 +7791,7 @@
           <t>hawks_eye</t>
         </is>
       </c>
-      <c r="N117" s="6" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
+      <c r="N117" s="4" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr">
         <is>
           <t>AFA</t>
@@ -7919,13 +7823,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F118" s="8" t="n">
+      <c r="F118" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H118" s="7" t="n">
+      <c r="H118" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I118" s="5" t="inlineStr">
@@ -7936,7 +7840,7 @@
       <c r="J118" s="5" t="n"/>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 leftmost Essence of an enemy. Next turn you gain the removed Essence (Conjured).</t>
+          <t>Remove an enemy's 3 leftmost Essence; get them next turn (Conjured).</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
@@ -7981,13 +7885,13 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F119" s="8" t="n">
+      <c r="F119" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G119" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H119" s="7" t="n">
+      <c r="H119" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I119" s="5" t="inlineStr">
@@ -8043,13 +7947,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F120" s="8" t="n">
+      <c r="F120" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G120" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H120" s="7" t="n">
+      <c r="H120" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I120" s="5" t="inlineStr">
@@ -8060,7 +7964,7 @@
       <c r="J120" s="5" t="n"/>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of an enemy. Overload 1.</t>
+          <t>Remove an enemy's 3 rightmost Essence. Overload 1.</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
@@ -8105,13 +8009,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F121" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H121" s="7" t="n">
+      <c r="F121" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I121" s="5" t="inlineStr">
@@ -8170,10 +8074,10 @@
       <c r="F122" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G122" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H122" s="7" t="n">
+      <c r="G122" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I122" s="5" t="inlineStr">
@@ -8184,7 +8088,7 @@
       <c r="J122" s="5" t="n"/>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>The first spell you cast each turn is cast twice.</t>
+          <t>Your first spell each turn is cast twice.</t>
         </is>
       </c>
       <c r="L122" s="4" t="inlineStr">
@@ -8197,11 +8101,7 @@
           <t>echo_chamber</t>
         </is>
       </c>
-      <c r="N122" s="6" t="inlineStr">
-        <is>
-          <t>renamed (was Echo Chamber), rarity (was rare)</t>
-        </is>
-      </c>
+      <c r="N122" s="4" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr">
         <is>
           <t>AWA</t>
@@ -8236,10 +8136,10 @@
       <c r="F123" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H123" s="7" t="n">
+      <c r="G123" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I123" s="5" t="inlineStr">
@@ -8298,10 +8198,10 @@
       <c r="F124" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G124" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H124" s="7" t="n">
+      <c r="G124" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I124" s="5" t="inlineStr">
@@ -8360,10 +8260,10 @@
       <c r="F125" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H125" s="7" t="n">
+      <c r="G125" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I125" s="5" t="inlineStr">
@@ -8374,7 +8274,7 @@
       <c r="J125" s="5" t="n"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of all enemies. Weaken 1 on all enemies.</t>
+          <t>Remove all enemies' rightmost Essence. Weaken 1 on all enemies.</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -8419,13 +8319,13 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F126" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H126" s="7" t="n">
+      <c r="F126" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I126" s="5" t="inlineStr">
@@ -8436,7 +8336,7 @@
       <c r="J126" s="5" t="n"/>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>Gain 5 Shield. Gain 2 Thorns this turn.</t>
+          <t>Gain 5 Shield. Thorns 2 this turn.</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
@@ -8481,13 +8381,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F127" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G127" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H127" s="7" t="n">
+      <c r="F127" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I127" s="5" t="inlineStr">
@@ -8498,7 +8398,7 @@
       <c r="J127" s="5" t="n"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 rightmost Essence of an enemy.</t>
+          <t>Remove an enemy's 2 rightmost Essence.</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -8546,10 +8446,10 @@
       <c r="F128" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G128" s="9" t="n">
+      <c r="G128" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H128" s="7" t="n">
+      <c r="H128" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I128" s="5" t="inlineStr">
@@ -8560,7 +8460,7 @@
       <c r="J128" s="5" t="n"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>Execute an enemy with 3 Essence or less (not bosses).</t>
+          <t>Execute an enemy with 3 or less Essence.</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
@@ -8608,10 +8508,10 @@
       <c r="F129" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G129" s="9" t="n">
+      <c r="G129" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H129" s="7" t="n">
+      <c r="H129" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I129" s="5" t="inlineStr">
@@ -8670,10 +8570,10 @@
       <c r="F130" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G130" s="9" t="n">
+      <c r="G130" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H130" s="7" t="n">
+      <c r="H130" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I130" s="5" t="inlineStr">
@@ -8684,7 +8584,7 @@
       <c r="J130" s="5" t="n"/>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>At the start of each of your turns: Expose 1.</t>
+          <t>Each turn: Expose 1.</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
@@ -8697,11 +8597,7 @@
           <t>frailty</t>
         </is>
       </c>
-      <c r="N130" s="6" t="inlineStr">
-        <is>
-          <t>renamed (was Frailty), effect</t>
-        </is>
-      </c>
+      <c r="N130" s="4" t="inlineStr"/>
       <c r="O130" s="2" t="inlineStr">
         <is>
           <t>AWW</t>
@@ -8733,7 +8629,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F131" s="8" t="n">
+      <c r="F131" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G131" s="5" t="n">
@@ -8750,7 +8646,7 @@
       <c r="J131" s="5" t="n"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of all enemies.</t>
+          <t>Remove all enemies' rightmost Essence.</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -8795,7 +8691,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F132" s="8" t="n">
+      <c r="F132" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G132" s="5" t="n">
@@ -8825,11 +8721,7 @@
           <t>witch_fire</t>
         </is>
       </c>
-      <c r="N132" s="6" t="inlineStr">
-        <is>
-          <t>rarity (was rare)</t>
-        </is>
-      </c>
+      <c r="N132" s="4" t="inlineStr"/>
       <c r="O132" s="2" t="inlineStr">
         <is>
           <t>F?F</t>
@@ -8861,13 +8753,13 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F133" s="8" t="n">
+      <c r="F133" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H133" s="7" t="n">
+      <c r="H133" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I133" s="5" t="inlineStr">
@@ -8878,7 +8770,7 @@
       <c r="J133" s="5" t="n"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>You become Ethereal this turn.</t>
+          <t>Become Ethereal this turn. Vulnerable 2 on you.</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -8923,13 +8815,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F134" s="8" t="n">
+      <c r="F134" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G134" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H134" s="7" t="n">
+      <c r="H134" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I134" s="5" t="inlineStr">
@@ -8985,13 +8877,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F135" s="8" t="n">
+      <c r="F135" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G135" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H135" s="7" t="n">
+      <c r="H135" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I135" s="5" t="inlineStr">
@@ -9047,13 +8939,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F136" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H136" s="7" t="n">
+      <c r="F136" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I136" s="5" t="inlineStr">
@@ -9064,7 +8956,7 @@
       <c r="J136" s="5" t="n"/>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 rightmost Essence of an enemy. If this defeats it, heal 5 HP.</t>
+          <t>Remove an enemy's 2 rightmost Essence. If it dies, heal 5 HP.</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
@@ -9109,13 +9001,13 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F137" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H137" s="7" t="n">
+      <c r="F137" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I137" s="5" t="inlineStr">
@@ -9171,13 +9063,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F138" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H138" s="7" t="n">
+      <c r="F138" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I138" s="5" t="inlineStr">
@@ -9188,7 +9080,7 @@
       <c r="J138" s="5" t="n"/>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>After the Release, the 2 rightmost Essence of your chant go back to your bag, to use again.</t>
+          <t>Refund your chant's 2 rightmost Essence.</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
@@ -9233,13 +9125,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F139" s="8" t="n">
+      <c r="F139" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G139" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H139" s="7" t="n">
+      <c r="H139" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I139" s="5" t="inlineStr">
@@ -9295,13 +9187,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F140" s="8" t="n">
+      <c r="F140" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G140" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H140" s="7" t="n">
+      <c r="H140" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I140" s="5" t="inlineStr">
@@ -9312,7 +9204,7 @@
       <c r="J140" s="5" t="n"/>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>Execute an enemy with 4 Essence or less (not bosses).</t>
+          <t>Execute an enemy with 4 or less Essence.</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
@@ -9357,7 +9249,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F141" s="8" t="n">
+      <c r="F141" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G141" s="5" t="n">
@@ -9419,7 +9311,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F142" s="8" t="n">
+      <c r="F142" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G142" s="5" t="n">
@@ -9436,7 +9328,7 @@
       <c r="J142" s="5" t="n"/>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>Whenever you apply Burn, apply 1 more. Burn 1 on all enemies.</t>
+          <t>Your Burn +1. Burn 1 on all enemies.</t>
         </is>
       </c>
       <c r="L142" s="4" t="inlineStr">
@@ -9481,10 +9373,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F143" s="8" t="n">
+      <c r="F143" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G143" s="9" t="n">
+      <c r="G143" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H143" s="5" t="n">
@@ -9498,7 +9390,7 @@
       <c r="J143" s="5" t="n"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>At the start of each of your turns: Burn 2 on a random enemy.</t>
+          <t>Each turn: Burn 2 on a random enemy.</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -9543,10 +9435,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F144" s="8" t="n">
+      <c r="F144" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G144" s="9" t="n">
+      <c r="G144" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H144" s="5" t="n">
@@ -9560,7 +9452,7 @@
       <c r="J144" s="5" t="n"/>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of an enemy. Burn 2 on an enemy.</t>
+          <t>Remove an enemy's 2 leftmost Essence. Burn 2 on an enemy.</t>
         </is>
       </c>
       <c r="L144" s="4" t="inlineStr">
@@ -9605,10 +9497,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F145" s="8" t="n">
+      <c r="F145" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G145" s="9" t="n">
+      <c r="G145" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H145" s="5" t="n">
@@ -9622,7 +9514,7 @@
       <c r="J145" s="5" t="n"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Fire from an enemy's Essence.</t>
+          <t>Remove up to 3 Fire from an enemy.</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -9667,13 +9559,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F146" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H146" s="7" t="n">
+      <c r="F146" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I146" s="5" t="inlineStr">
@@ -9684,7 +9576,7 @@
       <c r="J146" s="5" t="n"/>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>Change every Water in an enemy's Essence into Fire.</t>
+          <t>Turn every Water of an enemy into Fire.</t>
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr">
@@ -9729,13 +9621,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F147" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H147" s="7" t="n">
+      <c r="F147" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I147" s="5" t="inlineStr">
@@ -9791,13 +9683,13 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F148" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H148" s="7" t="n">
+      <c r="F148" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I148" s="5" t="inlineStr">
@@ -9808,7 +9700,7 @@
       <c r="J148" s="5" t="n"/>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>Conjure 2 spells. Gain 3 random Essence next turn. Heal 3 HP.</t>
+          <t>Conjure 2 spells. Gain 3 Random next turn. Heal 3 HP.</t>
         </is>
       </c>
       <c r="L148" s="4" t="inlineStr">
@@ -9853,10 +9745,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F149" s="8" t="n">
+      <c r="F149" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G149" s="9" t="n">
+      <c r="G149" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H149" s="5" t="n">
@@ -9915,10 +9807,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F150" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" s="9" t="n">
+      <c r="F150" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H150" s="5" t="n">
@@ -9980,7 +9872,7 @@
       <c r="F151" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G151" s="9" t="n">
+      <c r="G151" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H151" s="5" t="n">
@@ -10042,10 +9934,10 @@
       <c r="F152" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G152" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H152" s="7" t="n">
+      <c r="G152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I152" s="5" t="inlineStr">
@@ -10104,10 +9996,10 @@
       <c r="F153" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G153" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H153" s="7" t="n">
+      <c r="G153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I153" s="5" t="inlineStr">
@@ -10133,11 +10025,7 @@
           <t>blight_wind</t>
         </is>
       </c>
-      <c r="N153" s="6" t="inlineStr">
-        <is>
-          <t>rarity (was rare), effect, cooldown</t>
-        </is>
-      </c>
+      <c r="N153" s="4" t="inlineStr"/>
       <c r="O153" s="2" t="inlineStr">
         <is>
           <t>WAA</t>
@@ -10169,13 +10057,13 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F154" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H154" s="7" t="n">
+      <c r="F154" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I154" s="5" t="inlineStr">
@@ -10234,10 +10122,10 @@
       <c r="F155" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G155" s="9" t="n">
+      <c r="G155" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H155" s="7" t="n">
+      <c r="H155" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I155" s="5" t="inlineStr">
@@ -10263,11 +10151,7 @@
           <t>frostbite</t>
         </is>
       </c>
-      <c r="N155" s="6" t="inlineStr">
-        <is>
-          <t>effect, cooldown</t>
-        </is>
-      </c>
+      <c r="N155" s="4" t="inlineStr"/>
       <c r="O155" s="2" t="inlineStr">
         <is>
           <t>WAW</t>
@@ -10302,10 +10186,10 @@
       <c r="F156" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G156" s="9" t="n">
+      <c r="G156" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H156" s="7" t="n">
+      <c r="H156" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I156" s="5" t="inlineStr">
@@ -10316,7 +10200,7 @@
       <c r="J156" s="5" t="n"/>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>You become Ethereal this turn. Heal 4 HP.</t>
+          <t>Become Ethereal this turn. Heal 4 HP.</t>
         </is>
       </c>
       <c r="L156" s="4" t="inlineStr">
@@ -10364,10 +10248,10 @@
       <c r="F157" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G157" s="9" t="n">
+      <c r="G157" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H157" s="7" t="n">
+      <c r="H157" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I157" s="5" t="inlineStr">
@@ -10378,7 +10262,7 @@
       <c r="J157" s="5" t="n"/>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>Steal 1 Essence of your choice from an enemy.</t>
+          <t>Steal 1 Essence from an enemy.</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -10423,13 +10307,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F158" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H158" s="7" t="n">
+      <c r="F158" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I158" s="5" t="inlineStr">
@@ -10485,13 +10369,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F159" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H159" s="7" t="n">
+      <c r="F159" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I159" s="5" t="inlineStr">
@@ -10502,7 +10386,7 @@
       <c r="J159" s="5" t="n"/>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>Remove the leftmost Essence of 2 different enemies.</t>
+          <t>Remove the leftmost Essence of 2 enemies.</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -10547,13 +10431,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F160" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H160" s="7" t="n">
+      <c r="F160" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I160" s="5" t="inlineStr">
@@ -10577,11 +10461,7 @@
           <t>geyser</t>
         </is>
       </c>
-      <c r="N160" s="6" t="inlineStr">
-        <is>
-          <t>renamed (was Geyser), effect</t>
-        </is>
-      </c>
+      <c r="N160" s="4" t="inlineStr"/>
       <c r="O160" s="2" t="inlineStr">
         <is>
           <t>WFA</t>
@@ -10613,10 +10493,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F161" s="8" t="n">
+      <c r="F161" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G161" s="9" t="n">
+      <c r="G161" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H161" s="5" t="n">
@@ -10630,7 +10510,7 @@
       <c r="J161" s="5" t="n"/>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Fire from an enemy's Essence.</t>
+          <t>Remove up to 3 Fire from an enemy.</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -10675,10 +10555,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F162" s="8" t="n">
+      <c r="F162" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G162" s="9" t="n">
+      <c r="G162" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H162" s="5" t="n">
@@ -10692,7 +10572,7 @@
       <c r="J162" s="5" t="n"/>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>Change the 2 leftmost Essence of an enemy into Fire.</t>
+          <t>Turn an enemy's 2 leftmost Essence into Fire.</t>
         </is>
       </c>
       <c r="L162" s="4" t="inlineStr">
@@ -10737,10 +10617,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F163" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G163" s="9" t="n">
+      <c r="F163" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H163" s="5" t="n">
@@ -10799,10 +10679,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F164" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G164" s="9" t="n">
+      <c r="F164" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H164" s="5" t="n">
@@ -10864,10 +10744,10 @@
       <c r="F165" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G165" s="9" t="n">
+      <c r="G165" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H165" s="7" t="n">
+      <c r="H165" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I165" s="5" t="inlineStr">
@@ -10926,10 +10806,10 @@
       <c r="F166" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G166" s="9" t="n">
+      <c r="G166" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H166" s="7" t="n">
+      <c r="H166" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I166" s="5" t="inlineStr">
@@ -10940,7 +10820,7 @@
       <c r="J166" s="5" t="n"/>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of an enemy.</t>
+          <t>Remove an enemy's 2 leftmost Essence.</t>
         </is>
       </c>
       <c r="L166" s="4" t="inlineStr">
@@ -10988,10 +10868,10 @@
       <c r="F167" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G167" s="9" t="n">
+      <c r="G167" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H167" s="7" t="n">
+      <c r="H167" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I167" s="5" t="inlineStr">
@@ -11047,10 +10927,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F168" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G168" s="9" t="n">
+      <c r="F168" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H168" s="5" t="n">
@@ -11064,7 +10944,7 @@
       <c r="J168" s="5" t="n"/>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Water from an enemy's Essence.</t>
+          <t>Remove up to 3 Water from an enemy.</t>
         </is>
       </c>
       <c r="L168" s="4" t="inlineStr">
@@ -11087,7 +10967,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>Siren's Call</t>
+          <t>Undertow Grip</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -11101,18 +10981,18 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F169" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G169" s="9" t="n">
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H169" s="5" t="n">
@@ -11126,17 +11006,17 @@
       <c r="J169" s="5" t="n"/>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>Steal up to 2 Fire from an enemy.</t>
+          <t>Weaken 2 on an enemy.</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>A song so sweet the fire walks into the water.</t>
+          <t>Pulled under and worn down.</t>
         </is>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>sirens_call</t>
+          <t>undertow_grip</t>
         </is>
       </c>
       <c r="N169" s="4" t="inlineStr"/>
@@ -11149,12 +11029,12 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>Undertow Grip</t>
+          <t>Glacier</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Fire</t>
+          <t>Water → Water → Water</t>
         </is>
       </c>
       <c r="C170" s="5">
@@ -11163,7 +11043,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -11171,11 +11051,11 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F170" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G170" s="9" t="n">
-        <v>2</v>
+      <c r="F170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="H170" s="5" t="n">
         <v>0</v>
@@ -11185,33 +11065,35 @@
           <t>Spell</t>
         </is>
       </c>
-      <c r="J170" s="5" t="n"/>
+      <c r="J170" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>Weaken 2 on an enemy.</t>
+          <t>Freeze 1 on an enemy. Cooldown 1.</t>
         </is>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>Pulled under and worn down.</t>
+          <t>Frozen mid-swing.</t>
         </is>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>undertow_grip</t>
+          <t>glacier</t>
         </is>
       </c>
       <c r="N170" s="4" t="inlineStr"/>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>WWF</t>
+          <t>WWW</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>Glacier</t>
+          <t>Rising Tide</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -11236,7 +11118,7 @@
       <c r="F171" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G171" s="9" t="n">
+      <c r="G171" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H171" s="5" t="n">
@@ -11244,23 +11126,23 @@
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="J171" s="5" t="n"/>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>Freeze 1 on an enemy.</t>
+          <t>Each turn: gain 4 Shield.</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t>Frozen mid-swing.</t>
+          <t>The water rises around you every turn.</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>glacier</t>
+          <t>rising_tide</t>
         </is>
       </c>
       <c r="N171" s="4" t="inlineStr"/>
@@ -11273,7 +11155,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>Rising Tide</t>
+          <t>Tsunami Ward</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -11298,7 +11180,7 @@
       <c r="F172" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G172" s="9" t="n">
+      <c r="G172" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H172" s="5" t="n">
@@ -11306,23 +11188,23 @@
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J172" s="5" t="n"/>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>At the start of each of your turns: gain 4 Shield.</t>
+          <t>Gain 6 Shield.</t>
         </is>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>The water rises around you every turn.</t>
+          <t>A wall of sea with teeth.</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>rising_tide</t>
+          <t>tsunami_ward</t>
         </is>
       </c>
       <c r="N172" s="4" t="inlineStr"/>
@@ -11335,12 +11217,12 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>Tsunami Ward</t>
+          <t>Cyclone Edge</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Water → Water → Water</t>
+          <t>Air → Any → Air → Fire</t>
         </is>
       </c>
       <c r="C173" s="5">
@@ -11354,17 +11236,17 @@
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H173" s="5" t="n">
-        <v>0</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
@@ -11374,35 +11256,35 @@
       <c r="J173" s="5" t="n"/>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>Gain 6 Shield.</t>
+          <t>Remove 2 leftmost Essence of 2 enemies.</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>A wall of sea with teeth.</t>
+          <t>Two spinning cuts, two open wounds.</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>tsunami_ward</t>
+          <t>cyclone_edge</t>
         </is>
       </c>
       <c r="N173" s="4" t="inlineStr"/>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>WWW</t>
+          <t>A?AF</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>Cyclone Edge</t>
+          <t>Hurricane</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Air → Any → Air → Fire</t>
+          <t>Air → Air → Air → Air</t>
         </is>
       </c>
       <c r="C174" s="5">
@@ -11411,7 +11293,7 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -11419,14 +11301,14 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F174" s="8" t="n">
-        <v>1</v>
+      <c r="F174" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G174" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H174" s="7" t="n">
-        <v>2</v>
+      <c r="H174" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
@@ -11436,35 +11318,35 @@
       <c r="J174" s="5" t="n"/>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of 2 different enemies.</t>
+          <t>Remove all enemies' 3 rightmost Essence.</t>
         </is>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>Two spinning cuts, two open wounds.</t>
+          <t>The whole row is torn apart.</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>cyclone_edge</t>
+          <t>hurricane</t>
         </is>
       </c>
       <c r="N174" s="4" t="inlineStr"/>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>A?AF</t>
+          <t>AAAA</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>Hurricane</t>
+          <t>Storm Crown</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Air → Air</t>
+          <t>Air → Air → Air → Fire</t>
         </is>
       </c>
       <c r="C175" s="5">
@@ -11473,55 +11355,55 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F175" s="5" t="n">
-        <v>0</v>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G175" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H175" s="7" t="n">
-        <v>4</v>
+      <c r="H175" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="J175" s="5" t="n"/>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of all enemies.</t>
+          <t>Refund 1 Air each chant.</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>The whole row is torn apart.</t>
+          <t>A conjured Wind every turn.</t>
         </is>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>hurricane</t>
+          <t>storm_crown</t>
         </is>
       </c>
       <c r="N175" s="4" t="inlineStr"/>
       <c r="O175" s="2" t="inlineStr">
         <is>
-          <t>AAAA</t>
+          <t>AAAF</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>Storm Crown</t>
+          <t>Storm Legion</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -11540,44 +11422,40 @@
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F176" s="8" t="n">
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G176" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H176" s="7" t="n">
+      <c r="H176" s="6" t="n">
         <v>3</v>
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J176" s="5" t="n"/>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>Refund 1 Air each chant.</t>
+          <t>Remove 4 random Essence from random enemies.</t>
         </is>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>A conjured Wind every turn.</t>
+          <t>A hundred tiny lightnings, all late for something.</t>
         </is>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>storm_crown</t>
-        </is>
-      </c>
-      <c r="N176" s="6" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+          <t>storm_legion</t>
+        </is>
+      </c>
+      <c r="N176" s="4" t="inlineStr"/>
       <c r="O176" s="2" t="inlineStr">
         <is>
           <t>AAAF</t>
@@ -11587,12 +11465,12 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>Storm Legion</t>
+          <t>Gust Front</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Air → Fire</t>
+          <t>Air → Air → Fire → Fire</t>
         </is>
       </c>
       <c r="C177" s="5">
@@ -11601,7 +11479,7 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -11609,14 +11487,14 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F177" s="8" t="n">
-        <v>1</v>
+      <c r="F177" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="G177" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H177" s="7" t="n">
-        <v>3</v>
+      <c r="H177" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
@@ -11626,35 +11504,35 @@
       <c r="J177" s="5" t="n"/>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>Remove 4 random Essence from random enemies.</t>
+          <t>Remove all enemies' rightmost Essence.</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>A hundred tiny lightnings, all late for something.</t>
+          <t>The wall of wind before the storm.</t>
         </is>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>storm_legion</t>
+          <t>gust_front</t>
         </is>
       </c>
       <c r="N177" s="4" t="inlineStr"/>
       <c r="O177" s="2" t="inlineStr">
         <is>
-          <t>AAAF</t>
+          <t>AAFF</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>Gust Front</t>
+          <t>Quiet Wind</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Fire → Fire</t>
+          <t>Air → Air → Water → Air</t>
         </is>
       </c>
       <c r="C178" s="5">
@@ -11668,50 +11546,50 @@
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F178" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G178" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H178" s="7" t="n">
-        <v>2</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Anti-spell</t>
         </is>
       </c>
       <c r="J178" s="5" t="n"/>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>Remove the rightmost Essence of all enemies.</t>
+          <t>Gain 2 Shield.</t>
         </is>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>The wall of wind before the storm.</t>
+          <t>Say nothing, and the wind keeps you.</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>gust_front</t>
+          <t>quiet_wind</t>
         </is>
       </c>
       <c r="N178" s="4" t="inlineStr"/>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>AAFF</t>
+          <t>AAWA</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>Quiet Wind</t>
+          <t>Sky Sovereign</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -11725,42 +11603,42 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F179" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G179" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H179" s="7" t="n">
+      <c r="G179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" s="6" t="n">
         <v>3</v>
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>Anti-spell</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J179" s="5" t="n"/>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>Gain 2 Shield.</t>
+          <t>Conjure 2 spells. Infuse 2 Random. Amplify 1.</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
-          <t>Say nothing, and the wind keeps you.</t>
+          <t>The sky bows to no one, but sends gifts.</t>
         </is>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>quiet_wind</t>
+          <t>sky_sovereign</t>
         </is>
       </c>
       <c r="N179" s="4" t="inlineStr"/>
@@ -11773,12 +11651,12 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>Sky Sovereign</t>
+          <t>Gale Slash</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Water → Air</t>
+          <t>Air → Fire → Fire → Air</t>
         </is>
       </c>
       <c r="C180" s="5">
@@ -11787,7 +11665,7 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -11795,14 +11673,14 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H180" s="7" t="n">
-        <v>3</v>
+      <c r="F180" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
@@ -11812,39 +11690,35 @@
       <c r="J180" s="5" t="n"/>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>Conjure 2 spells. Infuse 2 random Essence into the chant. Amplify 1.</t>
+          <t>Remove all enemies' leftmost Essence.</t>
         </is>
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>The sky bows to no one, but sends gifts.</t>
+          <t>One sweep, everyone.</t>
         </is>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>sky_sovereign</t>
-        </is>
-      </c>
-      <c r="N180" s="6" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+          <t>gale_slash</t>
+        </is>
+      </c>
+      <c r="N180" s="4" t="inlineStr"/>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>AAWA</t>
+          <t>AFFA</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>Gale Slash</t>
+          <t>Misdirection</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Fire → Air</t>
+          <t>Air → Water → Air → Water</t>
         </is>
       </c>
       <c r="C181" s="5">
@@ -11853,21 +11727,21 @@
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F181" s="8" t="n">
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" s="7" t="n">
+      <c r="H181" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I181" s="5" t="inlineStr">
@@ -11878,35 +11752,35 @@
       <c r="J181" s="5" t="n"/>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>Remove the leftmost Essence of all enemies.</t>
+          <t>Redirect an enemy's intent. Gain 1 Aegis.</t>
         </is>
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>One sweep, everyone.</t>
+          <t>Point its anger somewhere else. Anywhere else.</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>gale_slash</t>
+          <t>decoy</t>
         </is>
       </c>
       <c r="N181" s="4" t="inlineStr"/>
       <c r="O181" s="2" t="inlineStr">
         <is>
-          <t>AFFA</t>
+          <t>AWAW</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>Misdirection</t>
+          <t>Eye of the Storm</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Air → Water</t>
+          <t>Air → Water → Fire → Air</t>
         </is>
       </c>
       <c r="C182" s="5">
@@ -11923,13 +11797,13 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F182" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H182" s="7" t="n">
+      <c r="F182" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I182" s="5" t="inlineStr">
@@ -11940,35 +11814,35 @@
       <c r="J182" s="5" t="n"/>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>Redirect the intent of an enemy. Gain 1 Aegis.</t>
+          <t>Freeze 2 on all enemies.</t>
         </is>
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>Point its anger somewhere else. Anywhere else.</t>
+          <t>For one moment, everything stops.</t>
         </is>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>decoy</t>
+          <t>eye_of_the_storm</t>
         </is>
       </c>
       <c r="N182" s="4" t="inlineStr"/>
       <c r="O182" s="2" t="inlineStr">
         <is>
-          <t>AWAW</t>
+          <t>AWFA</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>Eye of the Storm</t>
+          <t>Wildfire Pact</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Fire → Air</t>
+          <t>Fire → Any → Fire → Air</t>
         </is>
       </c>
       <c r="C183" s="5">
@@ -11977,22 +11851,22 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F183" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H183" s="7" t="n">
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F183" s="7" t="n">
         <v>2</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
@@ -12002,35 +11876,35 @@
       <c r="J183" s="5" t="n"/>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>Freeze 2 on all enemies.</t>
+          <t>Burn 2 on all enemies.</t>
         </is>
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>For one moment, everything stops.</t>
+          <t>Burn it all, and pay tomorrow.</t>
         </is>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>eye_of_the_storm</t>
+          <t>wildfire_pact</t>
         </is>
       </c>
       <c r="N183" s="4" t="inlineStr"/>
       <c r="O183" s="2" t="inlineStr">
         <is>
-          <t>AWFA</t>
+          <t>F?FA</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>Wildfire Pact</t>
+          <t>Phoenix Rite</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Fire → Any → Fire → Air</t>
+          <t>Fire → Air → Fire → Air</t>
         </is>
       </c>
       <c r="C184" s="5">
@@ -12044,17 +11918,17 @@
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F184" s="8" t="n">
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G184" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H184" s="7" t="n">
-        <v>1</v>
+      <c r="H184" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
@@ -12064,35 +11938,35 @@
       <c r="J184" s="5" t="n"/>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>Burn 2 on all enemies.</t>
+          <t>Gain 1 Aegis. Heal 5 HP.</t>
         </is>
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>Burn it all, and pay tomorrow.</t>
+          <t>Rise from the next blow untouched.</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>wildfire_pact</t>
+          <t>phoenix_rite</t>
         </is>
       </c>
       <c r="N184" s="4" t="inlineStr"/>
       <c r="O184" s="2" t="inlineStr">
         <is>
-          <t>F?FA</t>
+          <t>FAFA</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>Phoenix Rite</t>
+          <t>Phoenix Dive</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Fire → Air → Fire → Air</t>
+          <t>Fire → Air → Fire → Fire</t>
         </is>
       </c>
       <c r="C185" s="5">
@@ -12106,17 +11980,17 @@
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F185" s="8" t="n">
-        <v>2</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="G185" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H185" s="7" t="n">
-        <v>2</v>
+      <c r="H185" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
@@ -12126,35 +12000,35 @@
       <c r="J185" s="5" t="n"/>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>Gain 1 Aegis. Heal 5 HP.</t>
+          <t>Remove all enemies' 2 rightmost Essence.</t>
         </is>
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
-          <t>Rise from the next blow untouched.</t>
+          <t>Fall like fire, rise like it too.</t>
         </is>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>phoenix_rite</t>
+          <t>phoenix_dive</t>
         </is>
       </c>
       <c r="N185" s="4" t="inlineStr"/>
       <c r="O185" s="2" t="inlineStr">
         <is>
-          <t>FAFA</t>
+          <t>FAFF</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>Phoenix Dive</t>
+          <t>Inferno Lance</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Fire → Air → Fire → Fire</t>
+          <t>Fire → Fire → Fire → Air</t>
         </is>
       </c>
       <c r="C186" s="5">
@@ -12171,13 +12045,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F186" s="8" t="n">
+      <c r="F186" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G186" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H186" s="7" t="n">
+      <c r="H186" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I186" s="5" t="inlineStr">
@@ -12188,30 +12062,30 @@
       <c r="J186" s="5" t="n"/>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 rightmost Essence of all enemies.</t>
+          <t>Snipe 3.</t>
         </is>
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>Fall like fire, rise like it too.</t>
+          <t>Through them, then all over them.</t>
         </is>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>phoenix_dive</t>
+          <t>inferno_lance</t>
         </is>
       </c>
       <c r="N186" s="4" t="inlineStr"/>
       <c r="O186" s="2" t="inlineStr">
         <is>
-          <t>FAFF</t>
+          <t>FFFA</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>Inferno Lance</t>
+          <t>Pyromancy</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -12233,41 +12107,37 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F187" s="8" t="n">
+      <c r="F187" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G187" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H187" s="7" t="n">
+      <c r="H187" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="J187" s="5" t="n"/>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>Snipe 3.</t>
+          <t>Your spells remove 1 more Essence.</t>
         </is>
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>Through them, then all over them.</t>
+          <t>Your spells tear out one Essence more.</t>
         </is>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>inferno_lance</t>
-        </is>
-      </c>
-      <c r="N187" s="6" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+          <t>pyromancy</t>
+        </is>
+      </c>
+      <c r="N187" s="4" t="inlineStr"/>
       <c r="O187" s="2" t="inlineStr">
         <is>
           <t>FFFA</t>
@@ -12277,12 +12147,12 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>Pyromancy</t>
+          <t>Meteor</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Air</t>
+          <t>Fire → Fire → Fire → Fire</t>
         </is>
       </c>
       <c r="C188" s="5">
@@ -12291,7 +12161,7 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
@@ -12299,52 +12169,52 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F188" s="8" t="n">
-        <v>3</v>
+      <c r="F188" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="G188" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H188" s="7" t="n">
-        <v>1</v>
+      <c r="H188" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J188" s="5" t="n"/>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>Your spells remove 1 more Essence.</t>
+          <t>Remove an enemy's 5 rightmost Essence.</t>
         </is>
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>Your spells tear out one Essence more.</t>
+          <t>Very big, very hot.</t>
         </is>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>pyromancy</t>
+          <t>meteor</t>
         </is>
       </c>
       <c r="N188" s="4" t="inlineStr"/>
       <c r="O188" s="2" t="inlineStr">
         <is>
-          <t>FFFA</t>
+          <t>FFFF</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>Meteor</t>
+          <t>Thermal Burst</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Fire → Fire</t>
+          <t>Fire → Fire → Water → Fire</t>
         </is>
       </c>
       <c r="C189" s="5">
@@ -12353,7 +12223,7 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
@@ -12361,11 +12231,11 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F189" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G189" s="5" t="n">
-        <v>0</v>
+      <c r="F189" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G189" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H189" s="5" t="n">
         <v>0</v>
@@ -12378,35 +12248,35 @@
       <c r="J189" s="5" t="n"/>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>Remove the 5 rightmost Essence of an enemy.</t>
+          <t>Remove 2 leftmost Essence of 2 enemies.</t>
         </is>
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>Very big, very hot.</t>
+          <t>Steam bursts two ways at once.</t>
         </is>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>meteor</t>
+          <t>thermal_burst</t>
         </is>
       </c>
       <c r="N189" s="4" t="inlineStr"/>
       <c r="O189" s="2" t="inlineStr">
         <is>
-          <t>FFFF</t>
+          <t>FFWF</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>Thermal Burst</t>
+          <t>Forge Fire</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Water → Fire</t>
+          <t>Fire → Fire → Water → Water</t>
         </is>
       </c>
       <c r="C190" s="5">
@@ -12415,19 +12285,19 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F190" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G190" s="9" t="n">
-        <v>1</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G190" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="H190" s="5" t="n">
         <v>0</v>
@@ -12440,35 +12310,35 @@
       <c r="J190" s="5" t="n"/>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of 2 different enemies.</t>
+          <t>Gain 6 Shield.</t>
         </is>
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>Steam bursts two ways at once.</t>
+          <t>Hammer, quench, repeat.</t>
         </is>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>thermal_burst</t>
+          <t>forge_fire</t>
         </is>
       </c>
       <c r="N190" s="4" t="inlineStr"/>
       <c r="O190" s="2" t="inlineStr">
         <is>
-          <t>FFWF</t>
+          <t>FFWW</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>Forge Fire</t>
+          <t>Ember Chorus</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire → Water → Water</t>
+          <t>Fire → Water → Air → Fire</t>
         </is>
       </c>
       <c r="C191" s="5">
@@ -12477,22 +12347,22 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F191" s="8" t="n">
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G191" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H191" s="5" t="n">
-        <v>0</v>
+      <c r="G191" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
@@ -12502,35 +12372,35 @@
       <c r="J191" s="5" t="n"/>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>Gain 6 Shield.</t>
+          <t>Conjure 3 spells.</t>
         </is>
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>Hammer, quench, repeat.</t>
+          <t>Fire sings in harmony.</t>
         </is>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
-          <t>forge_fire</t>
+          <t>ember_chorus</t>
         </is>
       </c>
       <c r="N191" s="4" t="inlineStr"/>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>FFWW</t>
+          <t>FWAF</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>Ember Chorus</t>
+          <t>Steam Engine</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Fire → Water → Air → Fire</t>
+          <t>Fire → Water → Fire → Water</t>
         </is>
       </c>
       <c r="C192" s="5">
@@ -12539,22 +12409,22 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F192" s="8" t="n">
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G192" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H192" s="7" t="n">
-        <v>1</v>
+      <c r="G192" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I192" s="5" t="inlineStr">
         <is>
@@ -12564,30 +12434,30 @@
       <c r="J192" s="5" t="n"/>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>Conjure 3 spells.</t>
+          <t>Echo.</t>
         </is>
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>Fire sings in harmony.</t>
+          <t>The chant strikes again after your spells.</t>
         </is>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>ember_chorus</t>
+          <t>steam_engine</t>
         </is>
       </c>
       <c r="N192" s="4" t="inlineStr"/>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>FWAF</t>
+          <t>FWFW</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>Steam Engine</t>
+          <t>Steam Titan</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -12609,10 +12479,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F193" s="8" t="n">
+      <c r="F193" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G193" s="9" t="n">
+      <c r="G193" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H193" s="5" t="n">
@@ -12626,17 +12496,17 @@
       <c r="J193" s="5" t="n"/>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>Echo.</t>
+          <t>Remove an enemy's 3 rightmost Essence. Gain 5 Shield. Burn 2 on an enemy.</t>
         </is>
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
-          <t>The chant strikes again after your spells.</t>
+          <t>Iron lungs, boiling fists.</t>
         </is>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>steam_engine</t>
+          <t>steam_titan</t>
         </is>
       </c>
       <c r="N193" s="4" t="inlineStr"/>
@@ -12649,12 +12519,12 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>Steam Titan</t>
+          <t>Blood Moon</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Fire → Water → Fire → Water</t>
+          <t>Fire → Water → Water → Fire</t>
         </is>
       </c>
       <c r="C194" s="5">
@@ -12663,7 +12533,7 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
@@ -12671,10 +12541,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F194" s="8" t="n">
+      <c r="F194" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G194" s="9" t="n">
+      <c r="G194" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H194" s="5" t="n">
@@ -12688,35 +12558,35 @@
       <c r="J194" s="5" t="n"/>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of an enemy. Gain 5 Shield. Burn 2 on an enemy.</t>
+          <t>Remove all enemies' 2 rightmost Essence.</t>
         </is>
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>Iron lungs, boiling fists.</t>
+          <t>A red night asks for a red price.</t>
         </is>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>steam_titan</t>
+          <t>blood_moon</t>
         </is>
       </c>
       <c r="N194" s="4" t="inlineStr"/>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>FWFW</t>
+          <t>FWWF</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>Blood Moon</t>
+          <t>Moon Tide</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Fire → Water → Water → Fire</t>
+          <t>Water → Any → Water → Air</t>
         </is>
       </c>
       <c r="C195" s="5">
@@ -12730,17 +12600,17 @@
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F195" s="8" t="n">
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G195" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H195" s="5" t="n">
-        <v>0</v>
+      <c r="H195" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
@@ -12750,35 +12620,35 @@
       <c r="J195" s="5" t="n"/>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 rightmost Essence of all enemies.</t>
+          <t>Heal 7 HP.</t>
         </is>
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
-          <t>A red night asks for a red price.</t>
+          <t>Silver water, washing clean.</t>
         </is>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>blood_moon</t>
+          <t>moon_tide</t>
         </is>
       </c>
       <c r="N195" s="4" t="inlineStr"/>
       <c r="O195" s="2" t="inlineStr">
         <is>
-          <t>FWWF</t>
+          <t>W?WA</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>Moon Tide</t>
+          <t>Siren's Call</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Water → Any → Water → Air</t>
+          <t>Water → Air → Any → Water</t>
         </is>
       </c>
       <c r="C196" s="5">
@@ -12792,16 +12662,16 @@
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F196" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G196" s="9" t="n">
+      <c r="G196" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H196" s="7" t="n">
+      <c r="H196" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I196" s="5" t="inlineStr">
@@ -12812,23 +12682,23 @@
       <c r="J196" s="5" t="n"/>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>Heal 7 HP.</t>
+          <t>Steal up to 2 Fire from an enemy.</t>
         </is>
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>Silver water, washing clean.</t>
+          <t>A song so sweet the fire walks into the water.</t>
         </is>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>moon_tide</t>
+          <t>sirens_call</t>
         </is>
       </c>
       <c r="N196" s="4" t="inlineStr"/>
       <c r="O196" s="2" t="inlineStr">
         <is>
-          <t>W?WA</t>
+          <t>WA?W</t>
         </is>
       </c>
     </row>
@@ -12857,13 +12727,13 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F197" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G197" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H197" s="7" t="n">
+      <c r="F197" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I197" s="5" t="inlineStr">
@@ -12922,10 +12792,10 @@
       <c r="F198" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G198" s="9" t="n">
+      <c r="G198" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H198" s="7" t="n">
+      <c r="H198" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I198" s="5" t="inlineStr">
@@ -12981,13 +12851,13 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F199" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G199" s="9" t="n">
+      <c r="F199" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H199" s="7" t="n">
+      <c r="H199" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I199" s="5" t="inlineStr">
@@ -12998,7 +12868,7 @@
       <c r="J199" s="5" t="n"/>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>Break one Lock on your spells.</t>
+          <t>Break 1 Lock.</t>
         </is>
       </c>
       <c r="L199" s="4" t="inlineStr">
@@ -13046,10 +12916,10 @@
       <c r="F200" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G200" s="9" t="n">
+      <c r="G200" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H200" s="7" t="n">
+      <c r="H200" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I200" s="5" t="inlineStr">
@@ -13108,10 +12978,10 @@
       <c r="F201" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G201" s="9" t="n">
+      <c r="G201" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H201" s="7" t="n">
+      <c r="H201" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I201" s="5" t="inlineStr">
@@ -13122,7 +12992,7 @@
       <c r="J201" s="5" t="n"/>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of all enemies. Next turn you gain the removed Essence (Conjured).</t>
+          <t>Remove all enemies' 2 leftmost Essence; get them next turn (Conjured).</t>
         </is>
       </c>
       <c r="L201" s="4" t="inlineStr">
@@ -13167,13 +13037,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F202" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G202" s="9" t="n">
+      <c r="F202" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H202" s="7" t="n">
+      <c r="H202" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I202" s="5" t="inlineStr">
@@ -13184,7 +13054,7 @@
       <c r="J202" s="5" t="n"/>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>Add 2 random spells from your spellbook to your active row for this fight.</t>
+          <t>Add 2 random spells from your spellbook to this fight.</t>
         </is>
       </c>
       <c r="L202" s="4" t="inlineStr">
@@ -13232,10 +13102,10 @@
       <c r="F203" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G203" s="9" t="n">
+      <c r="G203" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H203" s="7" t="n">
+      <c r="H203" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I203" s="5" t="inlineStr">
@@ -13261,11 +13131,7 @@
           <t>frozen_tomb</t>
         </is>
       </c>
-      <c r="N203" s="6" t="inlineStr">
-        <is>
-          <t>effect, cooldown</t>
-        </is>
-      </c>
+      <c r="N203" s="4" t="inlineStr"/>
       <c r="O203" s="2" t="inlineStr">
         <is>
           <t>WWAW</t>
@@ -13300,10 +13166,10 @@
       <c r="F204" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G204" s="9" t="n">
+      <c r="G204" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H204" s="7" t="n">
+      <c r="H204" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I204" s="5" t="inlineStr">
@@ -13362,7 +13228,7 @@
       <c r="F205" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G205" s="9" t="n">
+      <c r="G205" s="8" t="n">
         <v>4</v>
       </c>
       <c r="H205" s="5" t="n">
@@ -13376,7 +13242,7 @@
       <c r="J205" s="5" t="n"/>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>All enemies deal 25% less damage for the rest of the fight.</t>
+          <t>All enemies deal 25% less all fight.</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
@@ -13424,7 +13290,7 @@
       <c r="F206" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G206" s="9" t="n">
+      <c r="G206" s="8" t="n">
         <v>4</v>
       </c>
       <c r="H206" s="5" t="n">
@@ -13438,7 +13304,7 @@
       <c r="J206" s="5" t="n"/>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>Remove the 2 leftmost Essence of all enemies. Weaken 3 on all enemies.</t>
+          <t>Remove all enemies' 2 leftmost Essence. Weaken 3 on all enemies.</t>
         </is>
       </c>
       <c r="L206" s="4" t="inlineStr">
@@ -13500,7 +13366,7 @@
       <c r="J207" s="5" t="n"/>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>Gain 1 random Essence next turn. Remove the rightmost Essence of a random enemy.</t>
+          <t>Gain 1 Random next turn. Remove a random enemy's rightmost Essence.</t>
         </is>
       </c>
       <c r="L207" s="4" t="inlineStr">
@@ -13513,11 +13379,7 @@
           <t>broken_clock</t>
         </is>
       </c>
-      <c r="N207" s="6" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
+      <c r="N207" s="4" t="inlineStr"/>
       <c r="O207" s="2" t="inlineStr">
         <is>
           <t>?????</t>
@@ -13552,10 +13414,10 @@
       <c r="F208" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G208" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H208" s="7" t="n">
+      <c r="G208" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I208" s="5" t="inlineStr">
@@ -13614,10 +13476,10 @@
       <c r="F209" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G209" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H209" s="7" t="n">
+      <c r="G209" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H209" s="6" t="n">
         <v>4</v>
       </c>
       <c r="I209" s="5" t="inlineStr">
@@ -13673,13 +13535,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F210" s="8" t="n">
+      <c r="F210" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G210" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H210" s="7" t="n">
+      <c r="H210" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I210" s="5" t="inlineStr">
@@ -13735,13 +13597,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F211" s="8" t="n">
+      <c r="F211" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G211" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H211" s="7" t="n">
+      <c r="G211" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I211" s="5" t="inlineStr">
@@ -13797,13 +13659,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F212" s="8" t="n">
+      <c r="F212" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G212" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H212" s="7" t="n">
+      <c r="H212" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I212" s="5" t="inlineStr">
@@ -13859,13 +13721,13 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F213" s="8" t="n">
+      <c r="F213" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G213" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H213" s="7" t="n">
+      <c r="G213" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I213" s="5" t="inlineStr">
@@ -13921,13 +13783,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F214" s="8" t="n">
+      <c r="F214" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G214" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H214" s="7" t="n">
+      <c r="H214" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I214" s="5" t="inlineStr">
@@ -13938,7 +13800,7 @@
       <c r="J214" s="5" t="n"/>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of all enemies. Burn 3 on all enemies.</t>
+          <t>Remove all enemies' 3 rightmost Essence. Burn 3 on all enemies.</t>
         </is>
       </c>
       <c r="L214" s="4" t="inlineStr">
@@ -13983,13 +13845,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F215" s="8" t="n">
+      <c r="F215" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G215" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H215" s="7" t="n">
+      <c r="H215" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I215" s="5" t="inlineStr">
@@ -14000,7 +13862,7 @@
       <c r="J215" s="5" t="n"/>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>All enemies your Release hits get Burn 1.</t>
+          <t>Your Release puts Burn 1 on what it hits.</t>
         </is>
       </c>
       <c r="L215" s="4" t="inlineStr">
@@ -14045,7 +13907,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F216" s="8" t="n">
+      <c r="F216" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G216" s="5" t="n">
@@ -14062,7 +13924,7 @@
       <c r="J216" s="5" t="n"/>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 rightmost Essence of all enemies. Burn 4 on all enemies.</t>
+          <t>Remove all enemies' 3 rightmost Essence. Burn 4 on all enemies.</t>
         </is>
       </c>
       <c r="L216" s="4" t="inlineStr">
@@ -14107,10 +13969,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F217" s="8" t="n">
+      <c r="F217" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G217" s="9" t="n">
+      <c r="G217" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H217" s="5" t="n">
@@ -14124,7 +13986,7 @@
       <c r="J217" s="5" t="n"/>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>Remove the 5 rightmost Essence of an enemy.</t>
+          <t>Remove an enemy's 5 rightmost Essence.</t>
         </is>
       </c>
       <c r="L217" s="4" t="inlineStr">
@@ -14169,13 +14031,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F218" s="8" t="n">
+      <c r="F218" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G218" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H218" s="7" t="n">
+      <c r="G218" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H218" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I218" s="5" t="inlineStr">
@@ -14234,10 +14096,10 @@
       <c r="F219" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G219" s="9" t="n">
+      <c r="G219" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H219" s="7" t="n">
+      <c r="H219" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I219" s="5" t="inlineStr">
@@ -14296,10 +14158,10 @@
       <c r="F220" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G220" s="9" t="n">
+      <c r="G220" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H220" s="7" t="n">
+      <c r="H220" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I220" s="5" t="inlineStr">
@@ -14310,7 +14172,7 @@
       <c r="J220" s="5" t="n"/>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>At the start of each of your turns: heal 7 HP; gain 3 random Essence.</t>
+          <t>Each turn: heal 7 HP; gain 3 Random.</t>
         </is>
       </c>
       <c r="L220" s="4" t="inlineStr">
@@ -14358,10 +14220,10 @@
       <c r="F221" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G221" s="9" t="n">
+      <c r="G221" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H221" s="7" t="n">
+      <c r="H221" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I221" s="5" t="inlineStr">
@@ -14372,7 +14234,7 @@
       <c r="J221" s="5" t="n"/>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>Steal 2 Essence of your choice from an enemy. Gain 4 Shield.</t>
+          <t>Steal 2 Essence from an enemy. Gain 4 Shield.</t>
         </is>
       </c>
       <c r="L221" s="4" t="inlineStr">
@@ -14417,10 +14279,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F222" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G222" s="9" t="n">
+      <c r="F222" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="8" t="n">
         <v>4</v>
       </c>
       <c r="H222" s="5" t="n">
@@ -14434,7 +14296,7 @@
       <c r="J222" s="5" t="n"/>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>Remove the 3 leftmost Essence of all enemies. Next turn you gain the removed Essence (Conjured). Freeze 1 on all enemies.</t>
+          <t>Remove all enemies' 3 leftmost Essence; get them next turn (Conjured). Freeze 1 on all enemies.</t>
         </is>
       </c>
       <c r="L222" s="4" t="inlineStr">
@@ -14482,7 +14344,7 @@
       <c r="F223" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G223" s="9" t="n">
+      <c r="G223" s="8" t="n">
         <v>5</v>
       </c>
       <c r="H223" s="5" t="n">
@@ -14541,13 +14403,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F224" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G224" s="9" t="n">
+      <c r="F224" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H224" s="7" t="n">
+      <c r="H224" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I224" s="5" t="inlineStr">
@@ -14560,7 +14422,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>Remove the 5 rightmost Essence of all enemies. Burn 3 on all enemies. Poison 2 on all enemies. Cooldown 2.</t>
+          <t>Remove all enemies' 5 rightmost Essence. Burn 3 on all enemies. Poison 2 on all enemies. Cooldown 2.</t>
         </is>
       </c>
       <c r="L224" s="4" t="inlineStr">
@@ -14573,11 +14435,7 @@
           <t>worlds_end</t>
         </is>
       </c>
-      <c r="N224" s="6" t="inlineStr">
-        <is>
-          <t>effect, cooldown</t>
-        </is>
-      </c>
+      <c r="N224" s="4" t="inlineStr"/>
       <c r="O224" s="2" t="inlineStr">
         <is>
           <t>FWA?AW</t>
@@ -14609,13 +14467,13 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F225" s="8" t="n">
+      <c r="F225" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G225" s="9" t="n">
+      <c r="G225" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H225" s="7" t="n">
+      <c r="H225" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I225" s="5" t="inlineStr">
@@ -14647,9 +14505,9 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="10" t="inlineStr">
-        <is>
-          <t>Effect text is taken from the game itself (SpellText.card_text). "Changed" compares with data/spells.json at commit 0e53250 (the previous sheet). Spells removed since then: see the Removed sheet.</t>
+      <c r="A227" s="9" t="inlineStr">
+        <is>
+          <t>Effect text is taken from the game itself (SpellText.card_text). "Changed" compares with data/spells.json at commit aac985d (the previous sheet). Spells removed since then: see the Removed sheet.</t>
         </is>
       </c>
     </row>
@@ -14675,46 +14533,31 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Rarity</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Long Chant</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>AAWA</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>long_chant</t>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>(none)</t>
         </is>
       </c>
     </row>

--- a/docs/spells.xlsx
+++ b/docs/spells.xlsx
@@ -50,7 +50,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +75,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00AED6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -133,11 +138,14 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3457,12 +3465,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Wild Flame</t>
+          <t>Ash and Ember</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Fire → Any</t>
+          <t>Fire → Air</t>
         </is>
       </c>
       <c r="C48" s="5">
@@ -3485,41 +3493,41 @@
       <c r="G48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>0</v>
+      <c r="H48" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Durability 1</t>
         </is>
       </c>
       <c r="J48" s="5" t="n"/>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Apply 3 Burn to an enemy.</t>
+          <t>Apply 1 Burn to all enemies. Double all enemies' Burn. Durability 1.</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>Any fuel will do.</t>
+          <t>Feed every fire at once.</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>wild_flame</t>
+          <t>ash_and_ember</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>F?</t>
+          <t>FA</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Ash and Ember</t>
+          <t>Blowtorch</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -3533,7 +3541,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3552,23 +3560,23 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Durability 1</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J49" s="5" t="n"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Apply 1 Burn to all enemies. Double all enemies' Burn. Durability 1.</t>
+          <t>Remove an enemy's rightmost Essence. +1 if it has Burn.</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>Feed every fire at once.</t>
+          <t>Hotter where it's already burning.</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>ash_and_ember</t>
+          <t>blowtorch</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr"/>
@@ -3581,7 +3589,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Blowtorch</t>
+          <t>Conjure Flame</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -3600,7 +3608,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F50" s="7" t="n">
@@ -3620,17 +3628,17 @@
       <c r="J50" s="5" t="n"/>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's rightmost Essence. +1 if it has Burn.</t>
+          <t>Conjure 1 offensive spell.</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>Hotter where it's already burning.</t>
+          <t>Two flames, borrowed for a turn.</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>blowtorch</t>
+          <t>conjure_flame</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr"/>
@@ -3643,7 +3651,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Conjure Flame</t>
+          <t>Heat Haze</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -3657,12 +3665,12 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F51" s="7" t="n">
@@ -3676,23 +3684,23 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Anti-spell</t>
         </is>
       </c>
       <c r="J51" s="5" t="n"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Conjure 1 offensive spell.</t>
+          <t>Apply 1 Burn to all enemies.</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>Two flames, borrowed for a turn.</t>
+          <t>Shimmering air shows every weak spot, and singes it.</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>conjure_flame</t>
+          <t>heat_haze</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr"/>
@@ -3705,7 +3713,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Heat Haze</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -3719,7 +3727,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -3738,7 +3746,7 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Anti-spell</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J52" s="5" t="n"/>
@@ -3749,12 +3757,12 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>Shimmering air shows every weak spot, and singes it.</t>
+          <t>The wind spreads it everywhere.</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>heat_haze</t>
+          <t>wildfire</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr"/>
@@ -3767,12 +3775,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Blood Price</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Fire → Air</t>
+          <t>Fire → Fire</t>
         </is>
       </c>
       <c r="C53" s="5">
@@ -3781,22 +3789,22 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F53" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="6" t="n">
-        <v>1</v>
+      <c r="H53" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
@@ -3806,30 +3814,30 @@
       <c r="J53" s="5" t="n"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Apply 1 Burn to all enemies.</t>
+          <t>Lose 3 HP. Gain 3 Random.</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>The wind spreads it everywhere.</t>
+          <t>Pay in blood, gain in power.</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>wildfire</t>
+          <t>blood_price</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>FF</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Blood Price</t>
+          <t>Coal Toss</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -3843,12 +3851,12 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F54" s="7" t="n">
@@ -3868,17 +3876,17 @@
       <c r="J54" s="5" t="n"/>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Lose 3 HP. Gain 3 Random.</t>
+          <t>Remove a random enemy's 2 rightmost Essence.</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>Pay in blood, gain in power.</t>
+          <t>Underhand, still hot.</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>blood_price</t>
+          <t>coal_toss</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr"/>
@@ -3891,7 +3899,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Coal Toss</t>
+          <t>Daub</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -3905,7 +3913,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3930,17 +3938,17 @@
       <c r="J55" s="5" t="n"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Remove a random enemy's 2 rightmost Essence.</t>
+          <t>Repaint 2 Random.</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>Underhand, still hot.</t>
+          <t>Slapped on thick, still smoking.</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>coal_toss</t>
+          <t>searing_brand</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr"/>
@@ -3953,7 +3961,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Daub</t>
+          <t>Fire Ball</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -3967,7 +3975,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3986,23 +3994,23 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Repaint 2 Random.</t>
+          <t>Remove an enemy's rightmost Essence.</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>Slapped on thick, still smoking.</t>
+          <t>The classic.</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>searing_brand</t>
+          <t>fire_ball</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr"/>
@@ -4015,7 +4023,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Fire Ball</t>
+          <t>Flame Lash</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -4048,23 +4056,23 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J57" s="5" t="n"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's rightmost Essence.</t>
+          <t>Apply 1 Burn to 2 different enemies.</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>The classic.</t>
+          <t>A whip of fire, with a lingering sting.</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>fire_ball</t>
+          <t>flame_lash</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr"/>
@@ -4077,7 +4085,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Flame Lash</t>
+          <t>Flare</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -4116,17 +4124,17 @@
       <c r="J58" s="5" t="n"/>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Apply 1 Burn to 2 different enemies.</t>
+          <t>Apply 1 Burn to an enemy for every 2 Fire in your chant.</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>A whip of fire, with a lingering sting.</t>
+          <t>Burn away the front line.</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>flame_lash</t>
+          <t>flare</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr"/>
@@ -4139,7 +4147,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Flare</t>
+          <t>Snuff Out</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -4153,7 +4161,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -4178,17 +4186,17 @@
       <c r="J59" s="5" t="n"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Apply 1 Burn to an enemy for every 2 Fire in your chant.</t>
+          <t>Snipe 1. Then if it has 3 or fewer Essence, Execute it.</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>Burn away the front line.</t>
+          <t>Small flames are easy to pinch.</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>flare</t>
+          <t>snuff_out</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr"/>
@@ -4201,7 +4209,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Snuff Out</t>
+          <t>Twin Comets</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -4240,17 +4248,17 @@
       <c r="J60" s="5" t="n"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Snipe 1. Then if it has 3 or fewer Essence, Execute it.</t>
+          <t>Apply 2 Burn to 2 different enemies.</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>Small flames are easy to pinch.</t>
+          <t>One for you, one for your friend.</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>snuff_out</t>
+          <t>twin_comets</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr"/>
@@ -4263,12 +4271,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Twin Comets</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Fire → Fire</t>
+          <t>Fire → Water</t>
         </is>
       </c>
       <c r="C61" s="5">
@@ -4277,19 +4285,19 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F61" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H61" s="5" t="n">
         <v>0</v>
@@ -4302,30 +4310,30 @@
       <c r="J61" s="5" t="n"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>Apply 2 Burn to 2 different enemies.</t>
+          <t>Wild Repaint 3 Fire.</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>One for you, one for your friend.</t>
+          <t>Water at the end turns to fire.</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>twin_comets</t>
+          <t>boil</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Breath Word</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -4364,17 +4372,17 @@
       <c r="J62" s="5" t="n"/>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Wild Repaint 3 Fire.</t>
+          <t>Infuse 1 Air.</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>Water at the end turns to fire.</t>
+          <t>Exhale, and the wind answers.</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>boil</t>
+          <t>breath_word</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr"/>
@@ -4387,7 +4395,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Breath Word</t>
+          <t>Cauterize</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -4401,7 +4409,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -4420,23 +4428,23 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="J63" s="5" t="n"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>Infuse 1 Air.</t>
+          <t>Prevent an enemy from Mending.</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>Exhale, and the wind answers.</t>
+          <t>Seal the wound so it never grows back.</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>breath_word</t>
+          <t>cauterize</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr"/>
@@ -4449,7 +4457,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Cauterize</t>
+          <t>Fog of War</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -4482,23 +4490,23 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Anti-spell</t>
         </is>
       </c>
       <c r="J64" s="5" t="n"/>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>Prevent an enemy from Mending.</t>
+          <t>Apply 1 Dazed to all enemies.</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>Seal the wound so it never grows back.</t>
+          <t>While it hangs, nobody swings straight.</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>cauterize</t>
+          <t>fog_of_war</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr"/>
@@ -4511,7 +4519,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Fog of War</t>
+          <t>Handyman</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -4544,23 +4552,23 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Anti-spell</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="J65" s="5" t="n"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>Apply 1 Dazed to all enemies.</t>
+          <t>Your spells with Durability get +1 Durability.</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>While it hangs, nobody swings straight.</t>
+          <t>A little glue, a few nails: everything lasts a bit longer.</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>fog_of_war</t>
+          <t>handyman_power</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr"/>
@@ -4573,7 +4581,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Handyman</t>
+          <t>Kindled Heart</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -4592,7 +4600,7 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F66" s="7" t="n">
@@ -4606,23 +4614,25 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="J66" s="5" t="n"/>
+          <t>Spell</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>Your spells with Durability get +1 Durability.</t>
+          <t>Gain 1 Evasion. Cooldown 2.</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>A little glue, a few nails: everything lasts a bit longer.</t>
+          <t>A warm heart burns two ways.</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>handyman_power</t>
+          <t>kindled_heart</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr"/>
@@ -4635,7 +4645,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Kindled Heart</t>
+          <t>Mimic</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -4654,7 +4664,7 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F67" s="7" t="n">
@@ -4676,17 +4686,17 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>Gain 1 Evasion. Cooldown 2.</t>
+          <t>Your next spell this fight is cast twice. Cooldown 2.</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>A warm heart burns two ways.</t>
+          <t>Do that again.</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>kindled_heart</t>
+          <t>mimic</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr"/>
@@ -4699,7 +4709,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Mimic</t>
+          <t>Scald</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -4713,12 +4723,12 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F68" s="7" t="n">
@@ -4735,22 +4745,20 @@
           <t>Spell</t>
         </is>
       </c>
-      <c r="J68" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="J68" s="5" t="n"/>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>Your next spell this fight is cast twice. Cooldown 2.</t>
+          <t>Remove an enemy's rightmost Essence. Apply 1 Weaken to it.</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>Do that again.</t>
+          <t>Boiling water, badly thrown.</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>mimic</t>
+          <t>scald</t>
         </is>
       </c>
       <c r="N68" s="4" t="inlineStr"/>
@@ -4763,7 +4771,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Scald</t>
+          <t>Scalding Rain</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -4777,7 +4785,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -4799,20 +4807,22 @@
           <t>Spell</t>
         </is>
       </c>
-      <c r="J69" s="5" t="n"/>
+      <c r="J69" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's rightmost Essence. Apply 1 Weaken to it.</t>
+          <t>Apply 1 Poison to all enemies. Cooldown 2.</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>Boiling water, badly thrown.</t>
+          <t>Hot, wet and vile.</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>scald</t>
+          <t>scalding_rain</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr"/>
@@ -4825,7 +4835,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Scalding Rain</t>
+          <t>Steam Burst</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -4839,12 +4849,12 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F70" s="7" t="n">
@@ -4861,22 +4871,20 @@
           <t>Spell</t>
         </is>
       </c>
-      <c r="J70" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="J70" s="5" t="n"/>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>Apply 1 Poison to all enemies. Cooldown 2.</t>
+          <t>Gain 3 Shield.</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>Hot, wet and vile.</t>
+          <t>Hiss, pop, and a cloud to hide in.</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>scalding_rain</t>
+          <t>steam_burst</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr"/>
@@ -4889,12 +4897,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Steam Burst</t>
+          <t>Arctic Wind</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Fire → Water</t>
+          <t>Water → Air</t>
         </is>
       </c>
       <c r="C71" s="5">
@@ -4903,7 +4911,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -4911,47 +4919,47 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F71" s="7" t="n">
-        <v>1</v>
+      <c r="F71" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G71" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H71" s="5" t="n">
-        <v>0</v>
+      <c r="H71" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Durability 1</t>
         </is>
       </c>
       <c r="J71" s="5" t="n"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>Gain 3 Shield.</t>
+          <t>Apply 1 Freeze to an enemy. Durability 1.</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>Hiss, pop, and a cloud to hide in.</t>
+          <t>Frozen mid-swing.</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>steam_burst</t>
+          <t>cold_snap</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Arctic Wind</t>
+          <t>Mist Step</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -4965,12 +4973,12 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
@@ -4984,23 +4992,23 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Durability 1</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J72" s="5" t="n"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>Apply 1 Freeze to an enemy. Durability 1.</t>
+          <t>Infuse 1 Random.</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>Frozen mid-swing.</t>
+          <t>Step aside, into the fog.</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>cold_snap</t>
+          <t>mist_step</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr"/>
@@ -5013,7 +5021,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Mist Step</t>
+          <t>Mist Veil</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -5032,7 +5040,7 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
@@ -5046,23 +5054,23 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Durability 1</t>
         </is>
       </c>
       <c r="J73" s="5" t="n"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>Infuse 1 Random.</t>
+          <t>Become Ethereal this turn. Apply 3 Vulnerable to yourself. Durability 1.</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>Step aside, into the fog.</t>
+          <t>Blades pass through you. Curses don't.</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>mist_step</t>
+          <t>mist_veil</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr"/>
@@ -5075,7 +5083,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Mist Veil</t>
+          <t>Ripplewind</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -5094,7 +5102,7 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
@@ -5108,23 +5116,23 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Durability 1</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J74" s="5" t="n"/>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>Become Ethereal this turn. Apply 3 Vulnerable to yourself. Durability 1.</t>
+          <t>Self-Repaint 3 Water.</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>Blades pass through you. Curses don't.</t>
+          <t>A ripple that rewrites the shore.</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>mist_veil</t>
+          <t>ripplewind</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr"/>
@@ -5137,7 +5145,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Ripplewind</t>
+          <t>Riptide</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -5156,7 +5164,7 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
@@ -5176,17 +5184,17 @@
       <c r="J75" s="5" t="n"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Self-Repaint 3 Water.</t>
+          <t>Rearrange 1. Apply 2 Weaken to an enemy.</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>A ripple that rewrites the shore.</t>
+          <t>Drags one piece out of place and knocks it off balance.</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>ripplewind</t>
+          <t>riptide</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr"/>
@@ -5199,7 +5207,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Riptide</t>
+          <t>Spark Word</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -5218,7 +5226,7 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
@@ -5238,17 +5246,17 @@
       <c r="J76" s="5" t="n"/>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>Rearrange 1. Apply 2 Weaken to an enemy.</t>
+          <t>Infuse 1 Fire.</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>Drags one piece out of place and knocks it off balance.</t>
+          <t>Say fire, and there is fire.</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>riptide</t>
+          <t>spark_word</t>
         </is>
       </c>
       <c r="N76" s="4" t="inlineStr"/>
@@ -5261,7 +5269,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Spark Word</t>
+          <t>Spray</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -5280,7 +5288,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
@@ -5300,17 +5308,17 @@
       <c r="J77" s="5" t="n"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>Infuse 1 Fire.</t>
+          <t>Repaint 1 Random.</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>Say fire, and there is fire.</t>
+          <t>Splash them, and see where they flinch.</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>spark_word</t>
+          <t>spray</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr"/>
@@ -5323,7 +5331,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Spray</t>
+          <t>Undertow</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -5342,7 +5350,7 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
@@ -5362,17 +5370,17 @@
       <c r="J78" s="5" t="n"/>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>Repaint 1 Random.</t>
+          <t>Rearrange 2.</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>Splash them, and see where they flinch.</t>
+          <t>The current rearranges everything.</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>spray</t>
+          <t>undertow</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr"/>
@@ -5385,7 +5393,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Undertow</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -5404,7 +5412,7 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
@@ -5421,20 +5429,22 @@
           <t>Spell</t>
         </is>
       </c>
-      <c r="J79" s="5" t="n"/>
+      <c r="J79" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Rearrange 2.</t>
+          <t>Gain 1 Evasion. Cooldown 2.</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>The current rearranges everything.</t>
+          <t>The next blow simply stops.</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>undertow</t>
+          <t>ward</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr"/>
@@ -5447,12 +5457,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Graft</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Water → Air</t>
+          <t>Water → Fire</t>
         </is>
       </c>
       <c r="C80" s="5">
@@ -5466,52 +5476,50 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>0</v>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G80" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H80" s="6" t="n">
-        <v>1</v>
+      <c r="H80" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
           <t>Spell</t>
         </is>
       </c>
-      <c r="J80" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="J80" s="5" t="n"/>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>Gain 1 Evasion. Cooldown 2.</t>
+          <t>Wild Repaint 2 Water.</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>The next blow simply stops.</t>
+          <t>Plant water at its leftmost end, then chant it away.</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>ward</t>
+          <t>graft</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>WF</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Graft</t>
+          <t>Hot Spring</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -5530,7 +5538,7 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F81" s="7" t="n">
@@ -5550,17 +5558,17 @@
       <c r="J81" s="5" t="n"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>Wild Repaint 2 Water.</t>
+          <t>Heal 2 HP. Gain 1 Shield.</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>Plant water at its leftmost end, then chant it away.</t>
+          <t>Warm water, warm heart.</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>graft</t>
+          <t>hot_spring</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr"/>
@@ -5573,7 +5581,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Hot Spring</t>
+          <t>Quench</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5612,17 +5620,17 @@
       <c r="J82" s="5" t="n"/>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>Heal 2 HP. Gain 1 Shield.</t>
+          <t>Heal 3 HP.</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>Warm water, warm heart.</t>
+          <t>Douse every burning trouble.</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>hot_spring</t>
+          <t>quench</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr"/>
@@ -5635,7 +5643,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Quench</t>
+          <t>Steam</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -5674,17 +5682,17 @@
       <c r="J83" s="5" t="n"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Heal 3 HP.</t>
+          <t>Gain 2 Shield. Apply 1 Weaken to an enemy.</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>Douse every burning trouble.</t>
+          <t>Hide in the hiss.</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>quench</t>
+          <t>steam</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr"/>
@@ -5697,7 +5705,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Steam</t>
+          <t>Steam Vent</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5711,12 +5719,12 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F84" s="7" t="n">
@@ -5730,23 +5738,25 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
-        </is>
-      </c>
-      <c r="J84" s="5" t="n"/>
+          <t>Anti-spell</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Gain 2 Shield. Apply 1 Weaken to an enemy.</t>
+          <t>Apply 1 Poison to all enemies. Cooldown 2.</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>Hide in the hiss.</t>
+          <t>Keep the lid on and it seeps out.</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>steam</t>
+          <t>steam_vent</t>
         </is>
       </c>
       <c r="N84" s="4" t="inlineStr"/>
@@ -5759,7 +5769,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Steam Vent</t>
+          <t>Water Whip</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5773,7 +5783,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -5792,25 +5802,23 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Anti-spell</t>
-        </is>
-      </c>
-      <c r="J85" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>Spell</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="n"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Apply 1 Poison to all enemies. Cooldown 2.</t>
+          <t>Snipe 1.</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>Keep the lid on and it seeps out.</t>
+          <t>Snap off whatever you like.</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>steam_vent</t>
+          <t>water_whip</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr"/>
@@ -5823,12 +5831,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Water Whip</t>
+          <t>Brine</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Water → Fire</t>
+          <t>Water → Water</t>
         </is>
       </c>
       <c r="C86" s="5">
@@ -5845,11 +5853,11 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F86" s="7" t="n">
-        <v>1</v>
+      <c r="F86" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86" s="5" t="n">
         <v>0</v>
@@ -5859,33 +5867,35 @@
           <t>Spell</t>
         </is>
       </c>
-      <c r="J86" s="5" t="n"/>
+      <c r="J86" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Snipe 1.</t>
+          <t>Apply 1 Poison to an enemy. Cooldown 2.</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>Snap off whatever you like.</t>
+          <t>Salt in every wound.</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>water_whip</t>
+          <t>brine</t>
         </is>
       </c>
       <c r="N86" s="4" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>WW</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Brine</t>
+          <t>Chill</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5904,7 +5914,7 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
@@ -5921,22 +5931,20 @@
           <t>Spell</t>
         </is>
       </c>
-      <c r="J87" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="J87" s="5" t="n"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Apply 1 Poison to an enemy. Cooldown 2.</t>
+          <t>Break an enemy's Armour. Gain 3 Shield for each Armour broken.</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>Salt in every wound.</t>
+          <t>Cold makes armour brittle.</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>brine</t>
+          <t>chill</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr"/>
@@ -5949,7 +5957,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Chill</t>
+          <t>Frost Nova</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5968,7 +5976,7 @@
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
@@ -5988,17 +5996,17 @@
       <c r="J88" s="5" t="n"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>Break an enemy's Armour. Gain 3 Shield for each Armour broken.</t>
+          <t>Apply 1 Weaken to all enemies.</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>Cold makes armour brittle.</t>
+          <t>Every blade goes numb.</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>chill</t>
+          <t>frost_nova</t>
         </is>
       </c>
       <c r="N88" s="4" t="inlineStr"/>
@@ -6011,7 +6019,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Frost Nova</t>
+          <t>Moonlight on a Still Lake</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -6025,12 +6033,12 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
@@ -6050,17 +6058,17 @@
       <c r="J89" s="5" t="n"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>Apply 1 Weaken to all enemies.</t>
+          <t>Duplicate 2.</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>Every blade goes numb.</t>
+          <t>Look closely: there are two of you.</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>frost_nova</t>
+          <t>mirror_pool</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr"/>
@@ -6073,7 +6081,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Moonlight on a Still Lake</t>
+          <t>Spritz</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -6087,7 +6095,7 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -6112,17 +6120,17 @@
       <c r="J90" s="5" t="n"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Duplicate 2.</t>
+          <t>Self-Repaint 2 Random.</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>Look closely: there are two of you.</t>
+          <t>A quick mist of colour, and they're anyone's.</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>mirror_pool</t>
+          <t>soak</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr"/>
@@ -6135,7 +6143,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Spritz</t>
+          <t>Summon Rain</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -6149,7 +6157,7 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -6174,17 +6182,17 @@
       <c r="J91" s="5" t="n"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Self-Repaint 2 Random.</t>
+          <t>Infuse 2 Water.</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>A quick mist of colour, and they're anyone's.</t>
+          <t>Two drops, gone by nightfall.</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>soak</t>
+          <t>summon_rain</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr"/>
@@ -6197,7 +6205,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Summon Rain</t>
+          <t>Tide Pool</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -6216,7 +6224,7 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F92" s="5" t="n">
@@ -6236,17 +6244,17 @@
       <c r="J92" s="5" t="n"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Infuse 2 Water.</t>
+          <t>Heal 3 HP.</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>Two drops, gone by nightfall.</t>
+          <t>Rest in the shallows.</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>summon_rain</t>
+          <t>tide_pool</t>
         </is>
       </c>
       <c r="N92" s="4" t="inlineStr"/>
@@ -6259,7 +6267,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Tide Pool</t>
+          <t>Tide Ward</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -6298,17 +6306,17 @@
       <c r="J93" s="5" t="n"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Heal 3 HP.</t>
+          <t>Gain 3 Thorns this turn.</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>Rest in the shallows.</t>
+          <t>The sea guards its own, with barnacles.</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>tide_pool</t>
+          <t>tide_ward</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr"/>
@@ -6321,7 +6329,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Tide Ward</t>
+          <t>Undercurrent</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -6335,12 +6343,12 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F94" s="5" t="n">
@@ -6354,23 +6362,23 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Durability 1</t>
         </is>
       </c>
       <c r="J94" s="5" t="n"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Gain 3 Thorns this turn.</t>
+          <t>Steal up to 2 Water from an enemy. Durability 1.</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>The sea guards its own, with barnacles.</t>
+          <t>What it pulls under, it gives to you.</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>tide_ward</t>
+          <t>undercurrent</t>
         </is>
       </c>
       <c r="N94" s="4" t="inlineStr"/>
@@ -6383,7 +6391,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Undercurrent</t>
+          <t>Water Wall</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -6397,12 +6405,12 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F95" s="5" t="n">
@@ -6416,23 +6424,23 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Durability 1</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="J95" s="5" t="n"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Steal up to 2 Water from an enemy. Durability 1.</t>
+          <t>Gain 4 Shield.</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>What it pulls under, it gives to you.</t>
+          <t>Stand behind the water.</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>undercurrent</t>
+          <t>water_wall</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr"/>
@@ -6445,12 +6453,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Water Wall</t>
+          <t>Stormcaller</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Water → Water</t>
+          <t>Air → Any → Air</t>
         </is>
       </c>
       <c r="C96" s="5">
@@ -6459,55 +6467,55 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G96" s="8" t="n">
+      <c r="G96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H96" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J96" s="5" t="n"/>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Gain 4 Shield.</t>
+          <t>Conjure 2 spells.</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>Stand behind the water.</t>
+          <t>Two voices answer the storm.</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>water_wall</t>
+          <t>stormcaller</t>
         </is>
       </c>
       <c r="N96" s="4" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>A?A</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Stormcaller</t>
+          <t>Tidecaller</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -6546,17 +6554,17 @@
       <c r="J97" s="5" t="n"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Conjure 2 spells.</t>
+          <t>Infuse 1 Water. Infuse 1 Any Essence.</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>Two voices answer the storm.</t>
+          <t>The water comes when called, for a turn.</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>stormcaller</t>
+          <t>tidecaller</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr"/>
@@ -6569,12 +6577,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Tidecaller</t>
+          <t>Thieving Wind</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Air → Any → Air</t>
+          <t>Air → Air → Any</t>
         </is>
       </c>
       <c r="C98" s="5">
@@ -6588,7 +6596,7 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F98" s="5" t="n">
@@ -6608,35 +6616,35 @@
       <c r="J98" s="5" t="n"/>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Infuse 1 Water. Infuse 1 Any Essence.</t>
+          <t>Steal 1 Essence from an enemy.</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>The water comes when called, for a turn.</t>
+          <t>The breeze has sticky fingers.</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>tidecaller</t>
+          <t>thieving_wind</t>
         </is>
       </c>
       <c r="N98" s="4" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>A?A</t>
+          <t>AA?</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Thieving Wind</t>
+          <t>Aole's Blessing</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Any</t>
+          <t>Air → Air → Air</t>
         </is>
       </c>
       <c r="C99" s="5">
@@ -6650,7 +6658,7 @@
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
@@ -6660,40 +6668,40 @@
         <v>0</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="J99" s="5" t="n"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Steal 1 Essence from an enemy.</t>
+          <t>Each turn: gain 1 Random.</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>The breeze has sticky fingers.</t>
+          <t>The wind brings a little more, every turn.</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>thieving_wind</t>
+          <t>trade_winds</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>AA?</t>
+          <t>AAA</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Aole's Blessing</t>
+          <t>Braum's Resolve</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -6732,17 +6740,17 @@
       <c r="J100" s="5" t="n"/>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Each turn: gain 1 Random.</t>
+          <t>All your Shield is Lasting.</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>The wind brings a little more, every turn.</t>
+          <t>Stand your ground, and the ground stands with you.</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>trade_winds</t>
+          <t>braums_resolve</t>
         </is>
       </c>
       <c r="N100" s="4" t="inlineStr"/>
@@ -6755,7 +6763,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Braum's Resolve</t>
+          <t>Sky Lance</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -6769,12 +6777,12 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F101" s="5" t="n">
@@ -6788,23 +6796,23 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J101" s="5" t="n"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>All your Shield is Lasting.</t>
+          <t>Snipe 2.</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>Stand your ground, and the ground stands with you.</t>
+          <t>Down from the clouds, straight through.</t>
         </is>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>braums_resolve</t>
+          <t>sky_lance</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr"/>
@@ -6817,7 +6825,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Sky Lance</t>
+          <t>Tempest</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -6831,12 +6839,12 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
@@ -6856,17 +6864,17 @@
       <c r="J102" s="5" t="n"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Snipe 2.</t>
+          <t>Gain 2 Random next turn. Self-Rearrange 1.</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>Down from the clouds, straight through.</t>
+          <t>The storm brings more, and moves what it touches.</t>
         </is>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>sky_lance</t>
+          <t>tempest</t>
         </is>
       </c>
       <c r="N102" s="4" t="inlineStr"/>
@@ -6879,12 +6887,12 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Tempest</t>
+          <t>Dustdevil</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Air</t>
+          <t>Air → Air → Fire</t>
         </is>
       </c>
       <c r="C103" s="5">
@@ -6893,22 +6901,22 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>0</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G103" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
@@ -6918,30 +6926,30 @@
       <c r="J103" s="5" t="n"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Gain 2 Random next turn. Self-Rearrange 1.</t>
+          <t>Rearrange 2. Repaint 2 Random.</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>The storm brings more, and moves what it touches.</t>
+          <t>Spins things around, throws things about.</t>
         </is>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>tempest</t>
+          <t>dustdevil</t>
         </is>
       </c>
       <c r="N103" s="4" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AAF</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>Dustdevil</t>
+          <t>Vacuum</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -6955,7 +6963,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -6980,17 +6988,17 @@
       <c r="J104" s="5" t="n"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Rearrange 2. Repaint 2 Random.</t>
+          <t>Remove up to 3 Air from an enemy.</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>Spins things around, throws things about.</t>
+          <t>Two breaths torn out of it.</t>
         </is>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>dustdevil</t>
+          <t>gale_force</t>
         </is>
       </c>
       <c r="N104" s="4" t="inlineStr"/>
@@ -7003,7 +7011,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Vacuum</t>
+          <t>Venom Coat</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -7022,7 +7030,7 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F105" s="7" t="n">
@@ -7036,23 +7044,23 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Durability 1</t>
         </is>
       </c>
       <c r="J105" s="5" t="n"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Air from an enemy.</t>
+          <t>Each time you're hit until your next turn, apply 1 Poison to all enemies. Durability 1.</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>Two breaths torn out of it.</t>
+          <t>Every enemy your chant touches is poisoned.</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>gale_force</t>
+          <t>venom_coat</t>
         </is>
       </c>
       <c r="N105" s="4" t="inlineStr"/>
@@ -7065,12 +7073,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Venom Coat</t>
+          <t>Splotch</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Fire</t>
+          <t>Air → Air → Water</t>
         </is>
       </c>
       <c r="C106" s="5">
@@ -7084,55 +7092,55 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>0</v>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H106" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Durability 1</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J106" s="5" t="n"/>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Each time you're hit until your next turn, apply 1 Poison to all enemies. Durability 1.</t>
+          <t>Repaint 3 Random.</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>Every enemy your chant touches is poisoned.</t>
+          <t>A cold wind throws the whole pot.</t>
         </is>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>venom_coat</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="N106" s="4" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>AAF</t>
+          <t>AAW</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Splotch</t>
+          <t>Daedalus's Scope</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Air → Air → Water</t>
+          <t>Air → Fire → Air</t>
         </is>
       </c>
       <c r="C107" s="5">
@@ -7149,11 +7157,11 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F107" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="8" t="n">
-        <v>1</v>
+      <c r="F107" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H107" s="6" t="n">
         <v>2</v>
@@ -7166,30 +7174,30 @@
       <c r="J107" s="5" t="n"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Repaint 3 Random.</t>
+          <t>Snipe 2.</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>A cold wind throws the whole pot.</t>
+          <t>Nothing hides from the hawk.</t>
         </is>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>hawks_eye</t>
         </is>
       </c>
       <c r="N107" s="4" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>AAW</t>
+          <t>AFA</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Daedalus's Scope</t>
+          <t>Desperate Measure</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -7203,7 +7211,7 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -7228,17 +7236,17 @@
       <c r="J108" s="5" t="n"/>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Snipe 2.</t>
+          <t>Apply 6 Burn to an enemy. Heal 6 HP. Gain 6 max HP. All your spells have Durability 1 this fight.</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>Nothing hides from the hawk.</t>
+          <t>Everything you have, right now. Nothing left for later.</t>
         </is>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>hawks_eye</t>
+          <t>desperate_measure</t>
         </is>
       </c>
       <c r="N108" s="4" t="inlineStr"/>
@@ -7251,7 +7259,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Desperate Measure</t>
+          <t>Windless Night</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -7265,12 +7273,12 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F109" s="7" t="n">
@@ -7284,23 +7292,23 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Anti-spell</t>
         </is>
       </c>
       <c r="J109" s="5" t="n"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>Apply 6 Burn to an enemy. Heal 6 HP. Gain 6 max HP. All your spells have Durability 1 this fight.</t>
+          <t>Gain 3 Shield.</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>Everything you have, right now. Nothing left for later.</t>
+          <t>Not a breath, not a blow.</t>
         </is>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>desperate_measure</t>
+          <t>windless_night</t>
         </is>
       </c>
       <c r="N109" s="4" t="inlineStr"/>
@@ -7313,12 +7321,12 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Windless Night</t>
+          <t>Backdraft</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Air</t>
+          <t>Air → Fire → Fire</t>
         </is>
       </c>
       <c r="C110" s="5">
@@ -7327,60 +7335,60 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F110" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H110" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Anti-spell</t>
+          <t>Durability 2</t>
         </is>
       </c>
       <c r="J110" s="5" t="n"/>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>Gain 3 Shield.</t>
+          <t>Remove an enemy's 3 rightmost Essence. Durability 2.</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>Not a breath, not a blow.</t>
+          <t>Big blast, slow recovery.</t>
         </is>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>windless_night</t>
+          <t>backdraft</t>
         </is>
       </c>
       <c r="N110" s="4" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>AFA</t>
+          <t>AFF</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Backdraft</t>
+          <t>Resonance</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Fire</t>
+          <t>Air → Fire → Water</t>
         </is>
       </c>
       <c r="C111" s="5">
@@ -7394,55 +7402,55 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="F111" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G111" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H111" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Durability 2</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J111" s="5" t="n"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's 3 rightmost Essence. Durability 2.</t>
+          <t>Duplicate 1. Heal 3 HP for each Extension it causes.</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>Big blast, slow recovery.</t>
+          <t>One note, sung twice.</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>backdraft</t>
+          <t>resonance</t>
         </is>
       </c>
       <c r="N111" s="4" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>AFF</t>
+          <t>AFW</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Resonance</t>
+          <t>Rain Song</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Air → Fire → Water</t>
+          <t>Air → Water → Air</t>
         </is>
       </c>
       <c r="C112" s="5">
@@ -7451,22 +7459,22 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>1</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G112" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H112" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
@@ -7476,30 +7484,30 @@
       <c r="J112" s="5" t="n"/>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>Duplicate 1. Heal 3 HP for each Extension it causes.</t>
+          <t>Heal 2 HP. Gain 1 Water next turn.</t>
         </is>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>One note, sung twice.</t>
+          <t>Sing for the rain and it sings back.</t>
         </is>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>resonance</t>
+          <t>rain_song</t>
         </is>
       </c>
       <c r="N112" s="4" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>AFW</t>
+          <t>AWA</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Rain Song</t>
+          <t>Tempest Veil</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -7513,7 +7521,7 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -7538,17 +7546,17 @@
       <c r="J113" s="5" t="n"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>Heal 2 HP. Gain 1 Water next turn.</t>
+          <t>Gain 4 Lasting Shield.</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>Sing for the rain and it sings back.</t>
+          <t>Wrap yourself in the storm.</t>
         </is>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>rain_song</t>
+          <t>tempest_veil</t>
         </is>
       </c>
       <c r="N113" s="4" t="inlineStr"/>
@@ -7561,7 +7569,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Tempest Veil</t>
+          <t>Whirlpool</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -7580,7 +7588,7 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F114" s="5" t="n">
@@ -7594,23 +7602,23 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Durability 3</t>
         </is>
       </c>
       <c r="J114" s="5" t="n"/>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>Gain 4 Lasting Shield.</t>
+          <t>Remove all enemies' rightmost Essence. Apply 1 Weaken to all enemies. Durability 3.</t>
         </is>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>Wrap yourself in the storm.</t>
+          <t>Spins them off balance.</t>
         </is>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>tempest_veil</t>
+          <t>whirlpool</t>
         </is>
       </c>
       <c r="N114" s="4" t="inlineStr"/>
@@ -7623,12 +7631,12 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Whirlpool</t>
+          <t>Storm Front</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Air</t>
+          <t>Air → Water → Fire</t>
         </is>
       </c>
       <c r="C115" s="5">
@@ -7642,50 +7650,50 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>0</v>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="G115" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Durability 3</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J115" s="5" t="n"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>Remove all enemies' rightmost Essence. Apply 1 Weaken to all enemies. Durability 3.</t>
+          <t>Gain 5 Shield. Gain 2 Thorns this turn.</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>Spins them off balance.</t>
+          <t>Touch it and get burned.</t>
         </is>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>whirlpool</t>
+          <t>storm_front</t>
         </is>
       </c>
       <c r="N115" s="4" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>AWA</t>
+          <t>AWF</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>Storm Front</t>
+          <t>Wind Shear</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -7699,12 +7707,12 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F116" s="7" t="n">
@@ -7724,17 +7732,17 @@
       <c r="J116" s="5" t="n"/>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>Gain 5 Shield. Gain 2 Thorns this turn.</t>
+          <t>Remove an enemy's 2 rightmost Essence.</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>Touch it and get burned.</t>
+          <t>Twist them round and cut the new tail.</t>
         </is>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>storm_front</t>
+          <t>wind_shear</t>
         </is>
       </c>
       <c r="N116" s="4" t="inlineStr"/>
@@ -7747,12 +7755,12 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Wind Shear</t>
+          <t>Grave Wind</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Fire</t>
+          <t>Air → Water → Water</t>
         </is>
       </c>
       <c r="C117" s="5">
@@ -7761,7 +7769,7 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -7769,11 +7777,11 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F117" s="7" t="n">
-        <v>1</v>
+      <c r="F117" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G117" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H117" s="6" t="n">
         <v>1</v>
@@ -7786,30 +7794,30 @@
       <c r="J117" s="5" t="n"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's 2 rightmost Essence.</t>
+          <t>Execute an enemy with 3 or less Essence.</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>Twist them round and cut the new tail.</t>
+          <t>It carries away the weak.</t>
         </is>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>wind_shear</t>
+          <t>grave_wind</t>
         </is>
       </c>
       <c r="N117" s="4" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>AWF</t>
+          <t>AWW</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Grave Wind</t>
+          <t>Hush of Rain</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -7823,12 +7831,12 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F118" s="5" t="n">
@@ -7842,23 +7850,23 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>Anti-spell</t>
         </is>
       </c>
       <c r="J118" s="5" t="n"/>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>Execute an enemy with 3 or less Essence.</t>
+          <t>Heal 2 HP.</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>It carries away the weak.</t>
+          <t>Listen to the rain instead of speaking.</t>
         </is>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>grave_wind</t>
+          <t>hush_of_rain</t>
         </is>
       </c>
       <c r="N118" s="4" t="inlineStr"/>
@@ -7871,7 +7879,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Hush of Rain</t>
+          <t>Stain</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -7885,12 +7893,12 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F119" s="5" t="n">
@@ -7904,23 +7912,23 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Anti-spell</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="J119" s="5" t="n"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>Heal 2 HP.</t>
+          <t>Each turn: Repaint 1 Random.</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>Listen to the rain instead of speaking.</t>
+          <t>It never washes out.</t>
         </is>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>hush_of_rain</t>
+          <t>frailty</t>
         </is>
       </c>
       <c r="N119" s="4" t="inlineStr"/>
@@ -7933,12 +7941,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Stain</t>
+          <t>Wild Flame</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Air → Water → Water</t>
+          <t>Fire → Any → Any</t>
         </is>
       </c>
       <c r="C120" s="5">
@@ -7955,40 +7963,40 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H120" s="6" t="n">
-        <v>1</v>
+      <c r="F120" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Spell</t>
         </is>
       </c>
       <c r="J120" s="5" t="n"/>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>Each turn: Repaint 1 Random.</t>
+          <t>Apply 3 Burn to an enemy.</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>It never washes out.</t>
+          <t>Any fuel will do.</t>
         </is>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>frailty</t>
+          <t>wild_flame</t>
         </is>
       </c>
       <c r="N120" s="4" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>AWW</t>
+          <t>F??</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9367,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>Jaeler's Backup Plan</t>
+          <t>Ludwig's Backup Plan</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -9411,7 +9419,11 @@
           <t>tidal_surge</t>
         </is>
       </c>
-      <c r="N143" s="4" t="inlineStr"/>
+      <c r="N143" s="9" t="inlineStr">
+        <is>
+          <t>renamed (was Jaeler's Backup Plan)</t>
+        </is>
+      </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
           <t>W?A</t>
@@ -11659,7 +11671,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>Jaeler's Boots</t>
+          <t>Ludwig's Boots</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -11711,7 +11723,11 @@
           <t>phoenix_rite</t>
         </is>
       </c>
-      <c r="N180" s="4" t="inlineStr"/>
+      <c r="N180" s="9" t="inlineStr">
+        <is>
+          <t>renamed (was Jaeler's Boots)</t>
+        </is>
+      </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
           <t>FAFA</t>
@@ -12527,7 +12543,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>Jaeler's Hand</t>
+          <t>Ludwig's Hand</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -12579,7 +12595,11 @@
           <t>tide_thief</t>
         </is>
       </c>
-      <c r="N194" s="4" t="inlineStr"/>
+      <c r="N194" s="9" t="inlineStr">
+        <is>
+          <t>renamed (was Jaeler's Hand)</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>WAW?</t>
@@ -13087,7 +13107,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>Jaeler's Knife</t>
+          <t>Ludwig's Knife</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -13139,7 +13159,11 @@
           <t>storm_crown</t>
         </is>
       </c>
-      <c r="N203" s="4" t="inlineStr"/>
+      <c r="N203" s="9" t="inlineStr">
+        <is>
+          <t>renamed (was Jaeler's Knife)</t>
+        </is>
+      </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
           <t>AAAFF</t>
@@ -13959,7 +13983,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>Jaeler's Final Touch</t>
+          <t>Ludwig's Final Touch</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -14011,7 +14035,11 @@
           <t>maelstrom_grasp</t>
         </is>
       </c>
-      <c r="N217" s="4" t="inlineStr"/>
+      <c r="N217" s="9" t="inlineStr">
+        <is>
+          <t>renamed (was Jaeler's Final Touch)</t>
+        </is>
+      </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
           <t>WWA?WW</t>
@@ -14019,7 +14047,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="9" t="inlineStr">
+      <c r="A219" s="10" t="inlineStr">
         <is>
           <t>Effect text is taken from the game itself (SpellText.card_text). "Changed" compares with data/spells.json at commit HEAD (the previous sheet). Spells removed since then: see the Removed sheet.</t>
         </is>
@@ -14037,7 +14065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14047,156 +14075,31 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Rarity</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Chaos Meteor</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>FFAF</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>inv_chaos_meteor</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Deafening Blast</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>WAFW</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>inv_deafening_blast</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Forbidden Knowledge</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>FFFFFF</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>forbidden_f</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Forbidden Knowledge</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>WWWWWW</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>forbidden_w</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Forbidden Knowledge</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>AAAAAA</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>forbidden_a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Tornado</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>inv_tornado</t>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>(none)</t>
         </is>
       </c>
     </row>

--- a/docs/spells.xlsx
+++ b/docs/spells.xlsx
@@ -69,17 +69,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F5B7B1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00AED6F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,19 +133,19 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1035,7 +1035,11 @@
           <t>updraft</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>A</t>
@@ -1191,7 +1195,7 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
@@ -1253,7 +1257,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="5" t="n">
@@ -1317,7 +1321,7 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
@@ -1334,7 +1338,7 @@
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Cure Blind. Cure Confuse.</t>
+          <t>Cure Blind. Cure Hypnotize.</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1379,7 +1383,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="5" t="n">
@@ -1441,7 +1445,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
@@ -1503,7 +1507,7 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="5" t="n">
@@ -1565,7 +1569,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
@@ -1630,7 +1634,7 @@
       <c r="F18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="5" t="n">
@@ -1657,11 +1661,7 @@
           <t>bandage</t>
         </is>
       </c>
-      <c r="N18" s="9" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N18" s="4" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>W</t>
@@ -1696,7 +1696,7 @@
       <c r="F19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
@@ -1758,7 +1758,7 @@
       <c r="F20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="5" t="n">
@@ -1820,7 +1820,7 @@
       <c r="F21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
@@ -1882,7 +1882,7 @@
       <c r="F22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="5" t="n">
@@ -1944,7 +1944,7 @@
       <c r="F23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="G23" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="5" t="n">
@@ -2006,7 +2006,7 @@
       <c r="F24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G24" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="5" t="n">
@@ -2144,7 +2144,7 @@
       <c r="J26" s="5" t="n"/>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Remove 1 random Essence of an enemy. Then if it has 2 or fewer Essence, Execute it.</t>
+          <t>Deal 1 Random damage to an enemy. Then Execute at 2.</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2268,7 +2268,7 @@
       <c r="J28" s="5" t="n"/>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Remove all enemies' rightmost Essence (if it has 3+).</t>
+          <t>Deal 1 Right damage to all enemies (each one with 3+).</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2392,7 +2392,7 @@
       <c r="J30" s="5" t="n"/>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Cure Confuse. Gain 1 Air next turn.</t>
+          <t>Cure Hypnotize. Gain 1 Air next turn.</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2516,7 +2516,7 @@
       <c r="J32" s="5" t="n"/>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Heal 1 HP. Trinity.</t>
+          <t>Heal 1 HP.</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2529,11 +2529,7 @@
           <t>trinity_third</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
+      <c r="N32" s="4" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>AA</t>
@@ -2627,7 +2623,7 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="5" t="n">
@@ -2689,7 +2685,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
@@ -2706,7 +2702,7 @@
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Remove 1 random enemy Essence, 3 times.</t>
+          <t>Randomly deal 1 damage 3 times.</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2751,7 +2747,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="5" t="n">
@@ -2813,7 +2809,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="5" t="n">
@@ -2830,7 +2826,7 @@
       <c r="J37" s="5" t="n"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>Snipe 2. Apply 2 Vulnerable to yourself.</t>
+          <t>Snipe 2. Gain 2 Vulnerable.</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2875,7 +2871,7 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="5" t="n">
@@ -2937,7 +2933,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
@@ -2999,7 +2995,7 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="5" t="n">
@@ -3061,7 +3057,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F41" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="5" t="n">
@@ -3078,7 +3074,7 @@
       <c r="J41" s="5" t="n"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>Remove 2 random enemies' rightmost Essence.</t>
+          <t>Deal 1 Right damage to 2 random enemies.</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -3126,7 +3122,7 @@
       <c r="F42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="6" t="n">
@@ -3188,7 +3184,7 @@
       <c r="F43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G43" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="6" t="n">
@@ -3250,7 +3246,7 @@
       <c r="F44" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="8" t="n">
+      <c r="G44" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="6" t="n">
@@ -3306,13 +3302,13 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="8" t="n">
+      <c r="G45" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="6" t="n">
@@ -3371,7 +3367,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
@@ -3433,7 +3429,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="5" t="n">
@@ -3495,7 +3491,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="F48" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="5" t="n">
@@ -3512,7 +3508,7 @@
       <c r="J48" s="5" t="n"/>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's rightmost Essence. +1 if it has Burn.</t>
+          <t>Deal 1 Right damage to an enemy. +1 if it has Burn.</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3557,7 +3553,7 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="5" t="n">
@@ -3619,7 +3615,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F50" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="5" t="n">
@@ -3681,7 +3677,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F51" s="7" t="n">
+      <c r="F51" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="5" t="n">
@@ -3743,7 +3739,7 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F52" s="7" t="n">
+      <c r="F52" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G52" s="5" t="n">
@@ -3805,7 +3801,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F53" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G53" s="5" t="n">
@@ -3822,7 +3818,7 @@
       <c r="J53" s="5" t="n"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Remove a random enemy's 2 rightmost Essence.</t>
+          <t>Deal 2 Right damage to a random enemy.</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3867,7 +3863,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F54" s="7" t="n">
+      <c r="F54" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G54" s="5" t="n">
@@ -3929,7 +3925,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F55" s="7" t="n">
+      <c r="F55" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G55" s="5" t="n">
@@ -3946,7 +3942,7 @@
       <c r="J55" s="5" t="n"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's rightmost Essence.</t>
+          <t>Deal 1 Right damage to an enemy.</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3991,7 +3987,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F56" s="7" t="n">
+      <c r="F56" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G56" s="5" t="n">
@@ -4053,7 +4049,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F57" s="7" t="n">
+      <c r="F57" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G57" s="5" t="n">
@@ -4115,7 +4111,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F58" s="7" t="n">
+      <c r="F58" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G58" s="5" t="n">
@@ -4132,7 +4128,7 @@
       <c r="J58" s="5" t="n"/>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Snipe 1. Then if it has 3 or fewer Essence, Execute it.</t>
+          <t>Snipe 1. Then Execute at 3.</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -4177,7 +4173,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F59" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G59" s="5" t="n">
@@ -4194,7 +4190,7 @@
       <c r="J59" s="5" t="n"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Snipe 1. Trinity.</t>
+          <t>Snipe 1.</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -4207,11 +4203,7 @@
           <t>trinity_first</t>
         </is>
       </c>
-      <c r="N59" s="9" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
+      <c r="N59" s="4" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
           <t>FF</t>
@@ -4243,7 +4235,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F60" s="7" t="n">
+      <c r="F60" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G60" s="5" t="n">
@@ -4305,10 +4297,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F61" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="8" t="n">
+      <c r="F61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="5" t="n">
@@ -4367,10 +4359,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="8" t="n">
+      <c r="F62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="5" t="n">
@@ -4429,10 +4421,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F63" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="8" t="n">
+      <c r="F63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="5" t="n">
@@ -4488,13 +4480,13 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="8" t="n">
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="5" t="n">
@@ -4553,10 +4545,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F65" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="8" t="n">
+      <c r="F65" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="5" t="n">
@@ -4615,10 +4607,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="8" t="n">
+      <c r="F66" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="5" t="n">
@@ -4679,10 +4671,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F67" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="8" t="n">
+      <c r="F67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="5" t="n">
@@ -4743,10 +4735,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F68" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="8" t="n">
+      <c r="F68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="5" t="n">
@@ -4760,7 +4752,7 @@
       <c r="J68" s="5" t="n"/>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's rightmost Essence. Apply 1 Weaken to it.</t>
+          <t>Deal 1 Right damage and apply 1 Weaken to an enemy.</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4805,10 +4797,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F69" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="8" t="n">
+      <c r="F69" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="5" t="n">
@@ -4870,7 +4862,7 @@
       <c r="F70" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G70" s="8" t="n">
+      <c r="G70" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="6" t="n">
@@ -4932,7 +4924,7 @@
       <c r="F71" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G71" s="8" t="n">
+      <c r="G71" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="6" t="n">
@@ -4994,7 +4986,7 @@
       <c r="F72" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G72" s="8" t="n">
+      <c r="G72" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="6" t="n">
@@ -5008,7 +5000,7 @@
       <c r="J72" s="5" t="n"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>Become Ethereal this turn. Apply 3 Vulnerable to yourself. Durability 1.</t>
+          <t>Become Ethereal this turn. Gain 3 Vulnerable. Durability 1.</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -5056,7 +5048,7 @@
       <c r="F73" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="8" t="n">
+      <c r="G73" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="6" t="n">
@@ -5118,7 +5110,7 @@
       <c r="F74" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G74" s="8" t="n">
+      <c r="G74" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="6" t="n">
@@ -5145,7 +5137,11 @@
           <t>riptide</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr"/>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>WA</t>
@@ -5180,7 +5176,7 @@
       <c r="F75" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G75" s="8" t="n">
+      <c r="G75" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="6" t="n">
@@ -5242,7 +5238,7 @@
       <c r="F76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G76" s="8" t="n">
+      <c r="G76" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="6" t="n">
@@ -5304,7 +5300,7 @@
       <c r="F77" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G77" s="8" t="n">
+      <c r="G77" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="6" t="n">
@@ -5331,7 +5327,11 @@
           <t>undertow</t>
         </is>
       </c>
-      <c r="N77" s="4" t="inlineStr"/>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>WA</t>
@@ -5366,7 +5366,7 @@
       <c r="F78" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G78" s="8" t="n">
+      <c r="G78" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="6" t="n">
@@ -5427,10 +5427,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F79" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="8" t="n">
+      <c r="F79" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="5" t="n">
@@ -5489,10 +5489,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F80" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="8" t="n">
+      <c r="F80" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="5" t="n">
@@ -5551,10 +5551,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F81" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="8" t="n">
+      <c r="F81" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H81" s="5" t="n">
@@ -5613,10 +5613,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F82" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="8" t="n">
+      <c r="F82" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="5" t="n">
@@ -5675,10 +5675,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F83" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="8" t="n">
+      <c r="F83" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="5" t="n">
@@ -5740,7 +5740,7 @@
       <c r="F84" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G84" s="8" t="n">
+      <c r="G84" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H84" s="5" t="n">
@@ -5802,7 +5802,7 @@
       <c r="F85" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G85" s="8" t="n">
+      <c r="G85" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H85" s="5" t="n">
@@ -5864,7 +5864,7 @@
       <c r="F86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="8" t="n">
+      <c r="G86" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H86" s="5" t="n">
@@ -5926,7 +5926,7 @@
       <c r="F87" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G87" s="8" t="n">
+      <c r="G87" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H87" s="5" t="n">
@@ -5988,7 +5988,7 @@
       <c r="F88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="8" t="n">
+      <c r="G88" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H88" s="5" t="n">
@@ -6050,7 +6050,7 @@
       <c r="F89" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G89" s="8" t="n">
+      <c r="G89" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H89" s="5" t="n">
@@ -6112,7 +6112,7 @@
       <c r="F90" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G90" s="8" t="n">
+      <c r="G90" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H90" s="5" t="n">
@@ -6174,7 +6174,7 @@
       <c r="F91" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G91" s="8" t="n">
+      <c r="G91" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H91" s="5" t="n">
@@ -6188,7 +6188,7 @@
       <c r="J91" s="5" t="n"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Gain 1 Shield. Trinity.</t>
+          <t>Gain 1 Shield.</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -6201,11 +6201,7 @@
           <t>trinity_second</t>
         </is>
       </c>
-      <c r="N91" s="9" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
+      <c r="N91" s="4" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>WW</t>
@@ -6240,7 +6236,7 @@
       <c r="F92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G92" s="8" t="n">
+      <c r="G92" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H92" s="5" t="n">
@@ -6302,7 +6298,7 @@
       <c r="F93" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G93" s="8" t="n">
+      <c r="G93" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H93" s="5" t="n">
@@ -6606,7 +6602,7 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="F98" s="5" t="n">
@@ -6792,10 +6788,10 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Offensive</t>
-        </is>
-      </c>
-      <c r="F101" s="7" t="n">
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G101" s="5" t="n">
@@ -6812,7 +6808,7 @@
       <c r="J101" s="5" t="n"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Rearrange 2. Repaint 2 Random.</t>
+          <t>Rearrange 2.</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -6825,7 +6821,11 @@
           <t>dustdevil</t>
         </is>
       </c>
-      <c r="N101" s="4" t="inlineStr"/>
+      <c r="N101" s="7" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
           <t>AAF</t>
@@ -6857,7 +6857,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F102" s="7" t="n">
+      <c r="F102" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="5" t="n">
@@ -6874,7 +6874,7 @@
       <c r="J102" s="5" t="n"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Air from an enemy.</t>
+          <t>Deal up to 3 damage to an enemy's Air.</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -6922,7 +6922,7 @@
       <c r="F103" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="8" t="n">
+      <c r="G103" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H103" s="6" t="n">
@@ -6981,7 +6981,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F104" s="7" t="n">
+      <c r="F104" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G104" s="5" t="n">
@@ -7043,7 +7043,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F105" s="7" t="n">
+      <c r="F105" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="5" t="n">
@@ -7105,7 +7105,7 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F106" s="7" t="n">
+      <c r="F106" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G106" s="5" t="n">
@@ -7167,7 +7167,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F107" s="7" t="n">
+      <c r="F107" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G107" s="5" t="n">
@@ -7184,7 +7184,7 @@
       <c r="J107" s="5" t="n"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's 3 rightmost Essence. Durability 2.</t>
+          <t>Deal 3 Right damage to an enemy. Durability 2.</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -7229,10 +7229,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F108" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" s="8" t="n">
+      <c r="F108" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H108" s="6" t="n">
@@ -7294,7 +7294,7 @@
       <c r="F109" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="8" t="n">
+      <c r="G109" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H109" s="6" t="n">
@@ -7356,7 +7356,7 @@
       <c r="F110" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="8" t="n">
+      <c r="G110" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H110" s="6" t="n">
@@ -7418,7 +7418,7 @@
       <c r="F111" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G111" s="8" t="n">
+      <c r="G111" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H111" s="6" t="n">
@@ -7432,7 +7432,7 @@
       <c r="J111" s="5" t="n"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>Remove all enemies' rightmost Essence. Apply 1 Weaken to all enemies. Durability 3.</t>
+          <t>Deal 1 Right damage and apply 1 Weaken to all enemies. Durability 3.</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -7477,10 +7477,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F112" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G112" s="8" t="n">
+      <c r="F112" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H112" s="6" t="n">
@@ -7539,10 +7539,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F113" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" s="8" t="n">
+      <c r="F113" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H113" s="6" t="n">
@@ -7556,7 +7556,7 @@
       <c r="J113" s="5" t="n"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's 2 rightmost Essence.</t>
+          <t>Deal 2 Right damage to an enemy.</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -7604,7 +7604,7 @@
       <c r="F114" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G114" s="8" t="n">
+      <c r="G114" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H114" s="6" t="n">
@@ -7618,7 +7618,7 @@
       <c r="J114" s="5" t="n"/>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>Execute an enemy with 3 or less Essence.</t>
+          <t>Execute an enemy at 3.</t>
         </is>
       </c>
       <c r="L114" s="4" t="inlineStr">
@@ -7666,7 +7666,7 @@
       <c r="F115" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G115" s="8" t="n">
+      <c r="G115" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H115" s="6" t="n">
@@ -7728,7 +7728,7 @@
       <c r="F116" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G116" s="8" t="n">
+      <c r="G116" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H116" s="6" t="n">
@@ -7787,7 +7787,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F117" s="7" t="n">
+      <c r="F117" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="5" t="n">
@@ -7849,7 +7849,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F118" s="7" t="n">
+      <c r="F118" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G118" s="5" t="n">
@@ -7866,7 +7866,7 @@
       <c r="J118" s="5" t="n"/>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>Remove all enemies' rightmost Essence.</t>
+          <t>Deal 1 Right damage to all enemies.</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
@@ -7911,7 +7911,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F119" s="7" t="n">
+      <c r="F119" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G119" s="5" t="n">
@@ -7973,7 +7973,7 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F120" s="7" t="n">
+      <c r="F120" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="5" t="n">
@@ -7990,7 +7990,7 @@
       <c r="J120" s="5" t="n"/>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>Become Ethereal this turn. Apply 2 Vulnerable to yourself. Durability 2.</t>
+          <t>Become Ethereal this turn. Gain 2 Vulnerable. Durability 2.</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
@@ -8035,7 +8035,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F121" s="7" t="n">
+      <c r="F121" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G121" s="5" t="n">
@@ -8052,7 +8052,7 @@
       <c r="J121" s="5" t="n"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>Your Snipes remove 1 more. Snipe 1.</t>
+          <t>Your Snipes deal 1 more damage. Snipe 1.</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -8097,7 +8097,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F122" s="7" t="n">
+      <c r="F122" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G122" s="5" t="n">
@@ -8159,7 +8159,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F123" s="7" t="n">
+      <c r="F123" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G123" s="5" t="n">
@@ -8221,10 +8221,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F124" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" s="8" t="n">
+      <c r="F124" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H124" s="6" t="n">
@@ -8238,7 +8238,7 @@
       <c r="J124" s="5" t="n"/>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's 2 rightmost Essence. If it dies, heal 5 HP.</t>
+          <t>Deal 2 Right damage to an enemy. If it dies, heal 5 HP.</t>
         </is>
       </c>
       <c r="L124" s="4" t="inlineStr">
@@ -8283,10 +8283,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F125" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="8" t="n">
+      <c r="F125" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H125" s="6" t="n">
@@ -8345,10 +8345,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F126" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" s="8" t="n">
+      <c r="F126" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H126" s="6" t="n">
@@ -8407,7 +8407,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F127" s="7" t="n">
+      <c r="F127" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G127" s="5" t="n">
@@ -8424,7 +8424,7 @@
       <c r="J127" s="5" t="n"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>Execute an enemy with 4 or less Essence.</t>
+          <t>Execute an enemy at 4.</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -8469,7 +8469,7 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F128" s="7" t="n">
+      <c r="F128" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G128" s="5" t="n">
@@ -8531,7 +8531,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F129" s="7" t="n">
+      <c r="F129" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G129" s="5" t="n">
@@ -8593,7 +8593,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F130" s="7" t="n">
+      <c r="F130" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G130" s="5" t="n">
@@ -8655,10 +8655,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F131" s="7" t="n">
+      <c r="F131" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G131" s="8" t="n">
+      <c r="G131" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H131" s="5" t="n">
@@ -8717,10 +8717,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F132" s="7" t="n">
+      <c r="F132" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G132" s="8" t="n">
+      <c r="G132" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H132" s="5" t="n">
@@ -8734,7 +8734,7 @@
       <c r="J132" s="5" t="n"/>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>Apply 2 Burn to an enemy. Then if it has 4 or more Burn, apply 1 Freeze to it.</t>
+          <t>Apply 2 Burn to an enemy. Then if it has 4+ Burn, apply 1 Freeze to it.</t>
         </is>
       </c>
       <c r="L132" s="4" t="inlineStr">
@@ -8779,10 +8779,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F133" s="7" t="n">
+      <c r="F133" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G133" s="8" t="n">
+      <c r="G133" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H133" s="5" t="n">
@@ -8796,7 +8796,7 @@
       <c r="J133" s="5" t="n"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Fire from an enemy.</t>
+          <t>Deal up to 3 damage to an enemy's Fire.</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -8841,10 +8841,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F134" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" s="8" t="n">
+      <c r="F134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H134" s="6" t="n">
@@ -8903,10 +8903,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F135" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" s="8" t="n">
+      <c r="F135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H135" s="6" t="n">
@@ -8962,13 +8962,13 @@
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F136" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" s="8" t="n">
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H136" s="6" t="n">
@@ -8982,7 +8982,7 @@
       <c r="J136" s="5" t="n"/>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>Whenever an Essence is added to or removed from your chant after you Chant, remove the same Essence from a random enemy.</t>
+          <t>Whenever an Essence is added to or removed from your chant after you Chant, deal 1 damage to that Essence of a random enemy.</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
@@ -9027,10 +9027,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F137" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="8" t="n">
+      <c r="F137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H137" s="6" t="n">
@@ -9089,10 +9089,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F138" s="7" t="n">
+      <c r="F138" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G138" s="8" t="n">
+      <c r="G138" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H138" s="5" t="n">
@@ -9151,10 +9151,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F139" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" s="8" t="n">
+      <c r="F139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H139" s="5" t="n">
@@ -9216,7 +9216,7 @@
       <c r="F140" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G140" s="8" t="n">
+      <c r="G140" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H140" s="6" t="n">
@@ -9278,7 +9278,7 @@
       <c r="F141" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G141" s="8" t="n">
+      <c r="G141" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H141" s="5" t="n">
@@ -9340,7 +9340,7 @@
       <c r="F142" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G142" s="8" t="n">
+      <c r="G142" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H142" s="6" t="n">
@@ -9399,10 +9399,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F143" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="8" t="n">
+      <c r="F143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H143" s="6" t="n">
@@ -9464,7 +9464,7 @@
       <c r="F144" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G144" s="8" t="n">
+      <c r="G144" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H144" s="6" t="n">
@@ -9493,11 +9493,7 @@
           <t>frostbite</t>
         </is>
       </c>
-      <c r="N144" s="9" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N144" s="4" t="inlineStr"/>
       <c r="O144" s="2" t="inlineStr">
         <is>
           <t>WAW</t>
@@ -9532,7 +9528,7 @@
       <c r="F145" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G145" s="8" t="n">
+      <c r="G145" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H145" s="6" t="n">
@@ -9594,7 +9590,7 @@
       <c r="F146" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G146" s="8" t="n">
+      <c r="G146" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H146" s="6" t="n">
@@ -9653,10 +9649,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F147" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" s="8" t="n">
+      <c r="F147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H147" s="6" t="n">
@@ -9670,7 +9666,7 @@
       <c r="J147" s="5" t="n"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>Remove 1 random enemy Essence, 3 times.</t>
+          <t>Randomly deal 1 damage 3 times.</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -9712,13 +9708,13 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F148" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" s="8" t="n">
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H148" s="6" t="n">
@@ -9777,10 +9773,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F149" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" s="8" t="n">
+      <c r="F149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H149" s="6" t="n">
@@ -9794,7 +9790,7 @@
       <c r="J149" s="5" t="n"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>Remove 2 leftmost Essence of 2 enemies.</t>
+          <t>Deal 2 Left damage to 2 different enemies.</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -9839,10 +9835,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F150" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" s="8" t="n">
+      <c r="F150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H150" s="6" t="n">
@@ -9901,10 +9897,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F151" s="7" t="n">
+      <c r="F151" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G151" s="8" t="n">
+      <c r="G151" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H151" s="5" t="n">
@@ -9918,7 +9914,7 @@
       <c r="J151" s="5" t="n"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>Remove up to 3 Fire from an enemy.</t>
+          <t>Deal up to 3 damage to an enemy's Fire.</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -9963,10 +9959,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F152" s="7" t="n">
+      <c r="F152" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G152" s="8" t="n">
+      <c r="G152" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H152" s="5" t="n">
@@ -10025,10 +10021,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F153" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" s="8" t="n">
+      <c r="F153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H153" s="5" t="n">
@@ -10087,10 +10083,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F154" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" s="8" t="n">
+      <c r="F154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H154" s="5" t="n">
@@ -10152,7 +10148,7 @@
       <c r="F155" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G155" s="8" t="n">
+      <c r="G155" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H155" s="6" t="n">
@@ -10214,7 +10210,7 @@
       <c r="F156" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G156" s="8" t="n">
+      <c r="G156" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H156" s="6" t="n">
@@ -10228,7 +10224,7 @@
       <c r="J156" s="5" t="n"/>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>Remove 3 random Essence of an enemy. Apply 1 Freeze to it. Durability 1.</t>
+          <t>Deal 3 Random damage and apply 1 Freeze to an enemy. Durability 1.</t>
         </is>
       </c>
       <c r="L156" s="4" t="inlineStr">
@@ -10276,7 +10272,7 @@
       <c r="F157" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G157" s="8" t="n">
+      <c r="G157" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H157" s="6" t="n">
@@ -10290,7 +10286,7 @@
       <c r="J157" s="5" t="n"/>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>Cleanse all your debuffs. Gain 4 Lasting Shield for each one cleansed.</t>
+          <t>Cleanse all your debuffs. Gain 4 Lasting Shield for each one.</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -10335,10 +10331,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F158" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" s="8" t="n">
+      <c r="F158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H158" s="5" t="n">
@@ -10352,7 +10348,7 @@
       <c r="J158" s="5" t="n"/>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>Remove 2 random Essence of an enemy. If it intends to attack, apply 1 Weaken to it.</t>
+          <t>Deal 2 Random damage to an enemy. If it's attacking, apply 1 Weaken to it.</t>
         </is>
       </c>
       <c r="L158" s="4" t="inlineStr">
@@ -10400,7 +10396,7 @@
       <c r="F159" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G159" s="8" t="n">
+      <c r="G159" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H159" s="5" t="n">
@@ -10462,7 +10458,7 @@
       <c r="F160" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G160" s="8" t="n">
+      <c r="G160" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H160" s="5" t="n">
@@ -10524,7 +10520,7 @@
       <c r="F161" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G161" s="8" t="n">
+      <c r="G161" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H161" s="5" t="n">
@@ -10583,10 +10579,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F162" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G162" s="8" t="n">
+      <c r="F162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H162" s="5" t="n">
@@ -10600,7 +10596,7 @@
       <c r="J162" s="5" t="n"/>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>Apply 3 Weaken to an enemy. Apply 2 Dazed to it. Durability 1.</t>
+          <t>Apply 3 Weaken and apply 2 Dazed to an enemy. Durability 1.</t>
         </is>
       </c>
       <c r="L162" s="4" t="inlineStr">
@@ -10613,11 +10609,7 @@
           <t>deluge</t>
         </is>
       </c>
-      <c r="N162" s="9" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N162" s="4" t="inlineStr"/>
       <c r="O162" s="2" t="inlineStr">
         <is>
           <t>?W?F</t>
@@ -10649,7 +10641,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F163" s="7" t="n">
+      <c r="F163" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G163" s="5" t="n">
@@ -10666,7 +10658,7 @@
       <c r="J163" s="5" t="n"/>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>Remove all enemies' 2 leftmost Essence.</t>
+          <t>Deal 2 Left damage to all enemies.</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
@@ -10728,7 +10720,7 @@
       <c r="J164" s="5" t="n"/>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>Remove all enemies' 3 rightmost Essence.</t>
+          <t>Deal 3 Right damage to all enemies.</t>
         </is>
       </c>
       <c r="L164" s="4" t="inlineStr">
@@ -10773,7 +10765,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F165" s="7" t="n">
+      <c r="F165" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G165" s="5" t="n">
@@ -10790,7 +10782,7 @@
       <c r="J165" s="5" t="n"/>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>Remove 1 random enemy Essence, 4 times.</t>
+          <t>Randomly deal 1 damage 4 times.</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
@@ -10838,7 +10830,7 @@
       <c r="F166" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G166" s="8" t="n">
+      <c r="G166" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H166" s="6" t="n">
@@ -10900,7 +10892,7 @@
       <c r="F167" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G167" s="8" t="n">
+      <c r="G167" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H167" s="6" t="n">
@@ -10962,7 +10954,7 @@
       <c r="F168" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G168" s="8" t="n">
+      <c r="G168" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H168" s="6" t="n">
@@ -11021,7 +11013,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F169" s="7" t="n">
+      <c r="F169" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G169" s="5" t="n">
@@ -11083,7 +11075,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F170" s="7" t="n">
+      <c r="F170" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G170" s="5" t="n">
@@ -11115,11 +11107,7 @@
           <t>gust_front</t>
         </is>
       </c>
-      <c r="N170" s="9" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N170" s="4" t="inlineStr"/>
       <c r="O170" s="2" t="inlineStr">
         <is>
           <t>AFAF</t>
@@ -11151,7 +11139,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F171" s="7" t="n">
+      <c r="F171" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G171" s="5" t="n">
@@ -11168,7 +11156,7 @@
       <c r="J171" s="5" t="n"/>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's leftmost Essence.</t>
+          <t>Deal 1 Left damage to an enemy.</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
@@ -11213,10 +11201,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F172" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G172" s="8" t="n">
+      <c r="F172" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H172" s="6" t="n">
@@ -11278,7 +11266,7 @@
       <c r="F173" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G173" s="8" t="n">
+      <c r="G173" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H173" s="6" t="n">
@@ -11337,7 +11325,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F174" s="7" t="n">
+      <c r="F174" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G174" s="5" t="n">
@@ -11399,7 +11387,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F175" s="7" t="n">
+      <c r="F175" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G175" s="5" t="n">
@@ -11461,7 +11449,7 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F176" s="7" t="n">
+      <c r="F176" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G176" s="5" t="n">
@@ -11523,7 +11511,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F177" s="7" t="n">
+      <c r="F177" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G177" s="5" t="n">
@@ -11540,7 +11528,7 @@
       <c r="J177" s="5" t="n"/>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>Remove all enemies' 2 rightmost Essence.</t>
+          <t>Deal 2 Right damage to all enemies.</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
@@ -11585,7 +11573,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F178" s="7" t="n">
+      <c r="F178" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G178" s="5" t="n">
@@ -11647,7 +11635,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F179" s="7" t="n">
+      <c r="F179" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G179" s="5" t="n">
@@ -11709,7 +11697,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F180" s="7" t="n">
+      <c r="F180" s="8" t="n">
         <v>4</v>
       </c>
       <c r="G180" s="5" t="n">
@@ -11726,7 +11714,7 @@
       <c r="J180" s="5" t="n"/>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's 5 rightmost Essence.</t>
+          <t>Deal 5 Right damage to an enemy.</t>
         </is>
       </c>
       <c r="L180" s="4" t="inlineStr">
@@ -11771,10 +11759,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F181" s="7" t="n">
+      <c r="F181" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G181" s="8" t="n">
+      <c r="G181" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H181" s="5" t="n">
@@ -11788,7 +11776,7 @@
       <c r="J181" s="5" t="n"/>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>Remove 2 leftmost Essence of 2 enemies.</t>
+          <t>Deal 2 Left damage to 2 different enemies.</t>
         </is>
       </c>
       <c r="L181" s="4" t="inlineStr">
@@ -11833,10 +11821,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F182" s="7" t="n">
+      <c r="F182" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G182" s="8" t="n">
+      <c r="G182" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H182" s="5" t="n">
@@ -11895,10 +11883,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F183" s="7" t="n">
+      <c r="F183" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G183" s="8" t="n">
+      <c r="G183" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H183" s="6" t="n">
@@ -11954,13 +11942,13 @@
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F184" s="7" t="n">
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="F184" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G184" s="8" t="n">
+      <c r="G184" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H184" s="5" t="n">
@@ -12019,10 +12007,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F185" s="7" t="n">
+      <c r="F185" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G185" s="8" t="n">
+      <c r="G185" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H185" s="5" t="n">
@@ -12036,7 +12024,7 @@
       <c r="J185" s="5" t="n"/>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's 3 rightmost Essence. Gain 5 Shield. Apply 2 Burn to it.</t>
+          <t>Deal 3 Right damage to an enemy. Gain 5 Shield. Apply 2 Burn to it.</t>
         </is>
       </c>
       <c r="L185" s="4" t="inlineStr">
@@ -12081,10 +12069,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F186" s="7" t="n">
+      <c r="F186" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G186" s="8" t="n">
+      <c r="G186" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H186" s="5" t="n">
@@ -12098,7 +12086,7 @@
       <c r="J186" s="5" t="n"/>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>Remove all enemies' 2 rightmost Essence.</t>
+          <t>Deal 2 Right damage to all enemies.</t>
         </is>
       </c>
       <c r="L186" s="4" t="inlineStr">
@@ -12146,7 +12134,7 @@
       <c r="F187" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G187" s="8" t="n">
+      <c r="G187" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H187" s="6" t="n">
@@ -12205,10 +12193,10 @@
           <t>Defensive</t>
         </is>
       </c>
-      <c r="F188" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G188" s="8" t="n">
+      <c r="F188" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H188" s="6" t="n">
@@ -12270,7 +12258,7 @@
       <c r="F189" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G189" s="8" t="n">
+      <c r="G189" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H189" s="6" t="n">
@@ -12332,7 +12320,7 @@
       <c r="F190" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G190" s="8" t="n">
+      <c r="G190" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H190" s="6" t="n">
@@ -12394,7 +12382,7 @@
       <c r="F191" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G191" s="8" t="n">
+      <c r="G191" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H191" s="6" t="n">
@@ -12456,7 +12444,7 @@
       <c r="F192" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G192" s="8" t="n">
+      <c r="G192" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H192" s="6" t="n">
@@ -12515,10 +12503,10 @@
           <t>Utility</t>
         </is>
       </c>
-      <c r="F193" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G193" s="8" t="n">
+      <c r="F193" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H193" s="6" t="n">
@@ -12580,7 +12568,7 @@
       <c r="F194" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G194" s="8" t="n">
+      <c r="G194" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H194" s="6" t="n">
@@ -12609,11 +12597,7 @@
           <t>frozen_tomb</t>
         </is>
       </c>
-      <c r="N194" s="9" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N194" s="4" t="inlineStr"/>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>WWAW</t>
@@ -12648,7 +12632,7 @@
       <c r="F195" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G195" s="8" t="n">
+      <c r="G195" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H195" s="6" t="n">
@@ -12710,7 +12694,7 @@
       <c r="F196" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G196" s="8" t="n">
+      <c r="G196" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H196" s="5" t="n">
@@ -12786,7 +12770,7 @@
       <c r="J197" s="5" t="n"/>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>Gain 1 Random next turn. Remove a random enemy's rightmost Essence.</t>
+          <t>Gain 1 Random next turn. Deal 1 Right damage to a random enemy.</t>
         </is>
       </c>
       <c r="L197" s="4" t="inlineStr">
@@ -12834,7 +12818,7 @@
       <c r="F198" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G198" s="8" t="n">
+      <c r="G198" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H198" s="6" t="n">
@@ -12890,10 +12874,10 @@
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
-        </is>
-      </c>
-      <c r="F199" s="7" t="n">
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="F199" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G199" s="5" t="n">
@@ -12955,7 +12939,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F200" s="7" t="n">
+      <c r="F200" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G200" s="5" t="n">
@@ -13022,7 +13006,7 @@
       <c r="F201" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G201" s="8" t="n">
+      <c r="G201" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H201" s="6" t="n">
@@ -13081,7 +13065,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F202" s="7" t="n">
+      <c r="F202" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G202" s="5" t="n">
@@ -13143,10 +13127,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F203" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G203" s="8" t="n">
+      <c r="F203" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H203" s="6" t="n">
@@ -13160,7 +13144,7 @@
       <c r="J203" s="5" t="n"/>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>Remove 1 random enemy Essence, 6 times.</t>
+          <t>Randomly deal 1 damage 6 times.</t>
         </is>
       </c>
       <c r="L203" s="4" t="inlineStr">
@@ -13205,7 +13189,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F204" s="7" t="n">
+      <c r="F204" s="8" t="n">
         <v>4</v>
       </c>
       <c r="G204" s="5" t="n">
@@ -13222,7 +13206,7 @@
       <c r="J204" s="5" t="n"/>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>Remove all enemies' 3 rightmost Essence. Apply 3 Burn to all enemies. Durability 2.</t>
+          <t>Deal 3 Right damage and apply 3 Burn to all enemies. Durability 2.</t>
         </is>
       </c>
       <c r="L204" s="4" t="inlineStr">
@@ -13267,7 +13251,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F205" s="7" t="n">
+      <c r="F205" s="8" t="n">
         <v>4</v>
       </c>
       <c r="G205" s="5" t="n">
@@ -13329,7 +13313,7 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F206" s="7" t="n">
+      <c r="F206" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G206" s="5" t="n">
@@ -13348,7 +13332,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>Remove all enemies' 3 rightmost Essence. Apply 4 Burn to all enemies. Cooldown 3.</t>
+          <t>Deal 3 Right damage and apply 4 Burn to all enemies. Cooldown 3.</t>
         </is>
       </c>
       <c r="L206" s="4" t="inlineStr">
@@ -13393,10 +13377,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F207" s="7" t="n">
+      <c r="F207" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G207" s="8" t="n">
+      <c r="G207" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H207" s="5" t="n">
@@ -13410,7 +13394,7 @@
       <c r="J207" s="5" t="n"/>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>Remove an enemy's 5 rightmost Essence. Durability 2.</t>
+          <t>Deal 5 Right damage to an enemy. Durability 2.</t>
         </is>
       </c>
       <c r="L207" s="4" t="inlineStr">
@@ -13458,7 +13442,7 @@
       <c r="F208" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G208" s="8" t="n">
+      <c r="G208" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H208" s="6" t="n">
@@ -13520,7 +13504,7 @@
       <c r="F209" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G209" s="8" t="n">
+      <c r="G209" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H209" s="6" t="n">
@@ -13576,13 +13560,13 @@
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>Offensive</t>
         </is>
       </c>
       <c r="F210" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G210" s="8" t="n">
+      <c r="G210" s="9" t="n">
         <v>5</v>
       </c>
       <c r="H210" s="5" t="n">
@@ -13596,7 +13580,7 @@
       <c r="J210" s="5" t="n"/>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>Remove every Fire from an enemy.</t>
+          <t>Deal 1 damage to every Fire of an enemy.</t>
         </is>
       </c>
       <c r="L210" s="4" t="inlineStr">
@@ -13641,10 +13625,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F211" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G211" s="8" t="n">
+      <c r="F211" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H211" s="6" t="n">
@@ -13658,7 +13642,7 @@
       <c r="J211" s="5" t="n"/>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>Remove all enemies' 5 rightmost Essence. Apply 3 Burn to all enemies. Durability 1.</t>
+          <t>Deal 5 Right damage and apply 3 Burn to all enemies. Durability 1.</t>
         </is>
       </c>
       <c r="L211" s="4" t="inlineStr">
@@ -13671,11 +13655,7 @@
           <t>worlds_end</t>
         </is>
       </c>
-      <c r="N211" s="9" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
+      <c r="N211" s="4" t="inlineStr"/>
       <c r="O211" s="2" t="inlineStr">
         <is>
           <t>FWA?AW</t>
@@ -13707,10 +13687,10 @@
           <t>Offensive</t>
         </is>
       </c>
-      <c r="F212" s="7" t="n">
+      <c r="F212" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G212" s="8" t="n">
+      <c r="G212" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H212" s="6" t="n">
@@ -13772,7 +13752,7 @@
       <c r="F213" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G213" s="8" t="n">
+      <c r="G213" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H213" s="6" t="n">
@@ -13809,7 +13789,7 @@
     <row r="215">
       <c r="A215" s="10" t="inlineStr">
         <is>
-          <t>Effect text is taken from the game itself (SpellText.card_text). "Changed" compares with data/spells.json at commit be614ab (the previous sheet). Spells removed since then: see the Removed sheet.</t>
+          <t>Effect text is taken from the game itself (SpellText.card_text). "Changed" compares with data/spells.json at commit 7e75388 (the previous sheet). Spells removed since then: see the Removed sheet.</t>
         </is>
       </c>
     </row>
@@ -13825,7 +13805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13859,154 +13839,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Blight Wind</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>WAA</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>blight_wind</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Brine</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>WW</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>brine</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Miasma</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>miasma</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Scalding Rain</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>scalding_rain</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Steam Vent</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>WF</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>steam_vent</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Taint</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>taint</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Venom Coat</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>AAF</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>venom_coat</t>
+          <t>(none)</t>
         </is>
       </c>
     </row>
